--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -3800,6 +3800,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32.8" customHeight="1" s="23">
       <c r="A4" s="30" t="inlineStr">
         <is>
@@ -3930,10 +3931,14 @@
       </c>
       <c r="L5" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M5" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M5" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="N5" s="44" t="n"/>
     </row>
     <row r="6" ht="283" customHeight="1" s="23">
@@ -3995,11 +4000,19 @@
       </c>
       <c r="L6" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M6" s="38" t="n"/>
-      <c r="N6" s="44" t="n"/>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="M6" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="N6" s="44" t="inlineStr">
+        <is>
+          <t>静态审查完成；两台电脑实测与 V1–V3 结论待 N08 测试环境</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="329.5" customHeight="1" s="23">
       <c r="A7" s="47" t="n">
@@ -4061,10 +4074,14 @@
       </c>
       <c r="L7" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M7" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M7" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="N7" s="44" t="inlineStr">
         <is>
           <t>原 T26（多机多显卡）已并入本任务</t>
@@ -4131,10 +4148,14 @@
       </c>
       <c r="L8" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M8" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M8" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="N8" s="44" t="n"/>
     </row>
     <row r="9" ht="298.5" customHeight="1" s="23">
@@ -4196,10 +4217,14 @@
       </c>
       <c r="L9" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M9" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M9" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="N9" s="44" t="n"/>
     </row>
     <row r="10" ht="345" customHeight="1" s="23">
@@ -4262,10 +4287,14 @@
       </c>
       <c r="L10" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M10" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M10" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N10" s="44" t="n"/>
     </row>
     <row r="11" ht="298.5" customHeight="1" s="23">
@@ -4327,10 +4356,14 @@
       </c>
       <c r="L11" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M11" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M11" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N11" s="44" t="inlineStr">
         <is>
           <t>尽早完成，之后的新功能直接双语开发</t>
@@ -4396,10 +4429,14 @@
       </c>
       <c r="L12" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M12" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M12" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N12" s="44" t="n"/>
     </row>
     <row r="13" ht="298.5" customHeight="1" s="23">
@@ -4461,10 +4498,14 @@
       </c>
       <c r="L13" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M13" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M13" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N13" s="44" t="n"/>
     </row>
     <row r="14" ht="283" customHeight="1" s="23">
@@ -4526,10 +4567,14 @@
       </c>
       <c r="L14" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M14" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M14" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N14" s="44" t="n"/>
     </row>
     <row r="15" ht="283" customHeight="1" s="23">
@@ -4591,10 +4636,14 @@
       </c>
       <c r="L15" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M15" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M15" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N15" s="44" t="inlineStr">
         <is>
           <t>原 T03（模板选择界面）已并入本任务</t>
@@ -4661,10 +4710,14 @@
       </c>
       <c r="L16" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M16" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M16" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N16" s="44" t="n"/>
     </row>
     <row r="17" ht="252" customHeight="1" s="23">
@@ -4726,10 +4779,14 @@
       </c>
       <c r="L17" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M17" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M17" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N17" s="44" t="n"/>
     </row>
     <row r="18" ht="221" customHeight="1" s="23">
@@ -4790,10 +4847,14 @@
       </c>
       <c r="L18" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M18" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M18" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N18" s="44" t="inlineStr">
         <is>
           <t>原“卖点图”与“商品展示视频”移到后续（T50、T51）</t>
@@ -4859,11 +4920,19 @@
       </c>
       <c r="L19" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M19" s="38" t="n"/>
-      <c r="N19" s="44" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M19" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N19" s="44" t="inlineStr">
+        <is>
+          <t>本机服务实测 2 商品 × 1 模板：结果、CSV/HTML 报告与 --compare 对比通过</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="329.5" customHeight="1" s="23">
       <c r="A20" s="47" t="n">
@@ -4925,10 +4994,14 @@
       </c>
       <c r="L20" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M20" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M20" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N20" s="44" t="inlineStr">
         <is>
           <t>会修改需求文档规则，务必审阅</t>
@@ -4994,10 +5067,14 @@
       </c>
       <c r="L21" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M21" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M21" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N21" s="44" t="n"/>
     </row>
     <row r="22" ht="314" customHeight="1" s="23">
@@ -5060,10 +5137,14 @@
       </c>
       <c r="L22" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M22" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M22" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N22" s="44" t="n"/>
     </row>
     <row r="23" ht="283" customHeight="1" s="23">
@@ -5125,10 +5206,14 @@
       </c>
       <c r="L23" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M23" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M23" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N23" s="44" t="n"/>
     </row>
     <row r="24" ht="283" customHeight="1" s="23">
@@ -5190,10 +5275,14 @@
       </c>
       <c r="L24" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M24" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M24" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N24" s="44" t="n"/>
     </row>
     <row r="25" ht="205.5" customHeight="1" s="23">
@@ -5254,10 +5343,14 @@
       </c>
       <c r="L25" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M25" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M25" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N25" s="44" t="n"/>
     </row>
     <row r="26" ht="252" customHeight="1" s="23">
@@ -5319,10 +5412,14 @@
       </c>
       <c r="L26" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M26" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M26" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N26" s="44" t="n"/>
     </row>
     <row r="27" ht="205.5" customHeight="1" s="23">
@@ -5383,10 +5480,14 @@
       </c>
       <c r="L27" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M27" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M27" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N27" s="44" t="n"/>
     </row>
     <row r="28" ht="236.5" customHeight="1" s="23">
@@ -5448,11 +5549,19 @@
       </c>
       <c r="L28" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M28" s="38" t="n"/>
-      <c r="N28" s="44" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M28" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N28" s="44" t="inlineStr">
+        <is>
+          <t>全新数据目录的第二实例验证了向导各步数据源；界面走查可在部署时复查</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="267.5" customHeight="1" s="23">
       <c r="A29" s="47" t="n">
@@ -5513,11 +5622,19 @@
       </c>
       <c r="L29" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M29" s="38" t="n"/>
-      <c r="N29" s="44" t="n"/>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="M29" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N29" s="44" t="inlineStr">
+        <is>
+          <t>代码与自动检查完成；Android Chrome / iOS Safari 真机实测待做</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="221" customHeight="1" s="23">
       <c r="A30" s="47" t="n">
@@ -5577,10 +5694,14 @@
       </c>
       <c r="L30" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M30" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M30" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N30" s="44" t="n"/>
     </row>
     <row r="31" ht="252" customHeight="1" s="23">
@@ -5642,10 +5763,14 @@
       </c>
       <c r="L31" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M31" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M31" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N31" s="44" t="n"/>
     </row>
     <row r="32" ht="236.5" customHeight="1" s="23">
@@ -5707,11 +5832,19 @@
       </c>
       <c r="L32" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M32" s="38" t="n"/>
-      <c r="N32" s="44" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M32" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N32" s="44" t="inlineStr">
+        <is>
+          <t>备份、恢复、防篡改与无确认拦截均已在本机服务实测</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="190" customHeight="1" s="23">
       <c r="A33" s="47" t="n">
@@ -5771,10 +5904,14 @@
       </c>
       <c r="L33" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M33" s="38" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M33" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N33" s="44" t="n"/>
     </row>
     <row r="34" ht="221" customHeight="1" s="23">
@@ -5835,11 +5972,19 @@
       </c>
       <c r="L34" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M34" s="38" t="n"/>
-      <c r="N34" s="44" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M34" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N34" s="44" t="inlineStr">
+        <is>
+          <t>效果对比图与演示视频为占位，图片视频稍后提供</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="267.5" customHeight="1" s="23">
       <c r="A35" s="47" t="n">
@@ -7285,6 +7430,7 @@
       <c r="M56" s="38" t="n"/>
       <c r="N56" s="44" t="n"/>
     </row>
+    <row r="57"/>
     <row r="58" ht="32" customHeight="1" s="23">
       <c r="A58" s="40" t="inlineStr">
         <is>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -690,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="22" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="B3" s="42" t="inlineStr">
         <is>
-          <t>48 项功能，按 6 个阶段排列，其中 MVP（A 平台底座、B 电商出图、C 易用与运维）27 项；“功能状态”根据开发任务自动计算，不用手填</t>
+          <t>54 项功能，按 7 个阶段排列，其中 MVP（A 平台底座、B 电商出图、C 易用与运维）27 项、简易模式改版 v3（F52–F57）6 项已确认待开发；“功能状态”根据开发任务自动计算，不用手填</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B4" s="42" t="inlineStr">
         <is>
-          <t>52 个可直接交给 Claude Code 的任务（MVP 30 个），按“顺序”列执行；每个任务都有涉及文件、依赖、验收标准、测试方式和可直接粘贴的提示词</t>
+          <t>58 个可直接交给 Claude Code 的任务（MVP 30 个），按“顺序”列执行；每个任务都有涉及文件、依赖、验收标准、测试方式和可直接粘贴的提示词</t>
         </is>
       </c>
     </row>
@@ -827,189 +827,201 @@
       </c>
     </row>
     <row r="13" ht="19.5" customHeight="1" s="23">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>简易模式改版需求</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>docs/EcomCraft 简易模式改版需求.zh-CN.md（英文版 docs/EcomCraft Simple Mode Redesign.md）：简易模式 v3 改版（上传四入口、产品类型、双语提示词、20 张上限、出图提速、工作流自动生成）的需求定稿；交互原型 docs/EcomCraft 简易模式改版原型.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="19.4" customHeight="1" s="23">
+      <c r="A14" s="43" t="inlineStr">
         <is>
           <t>本表位置</t>
         </is>
       </c>
-      <c r="B13" s="42" t="inlineStr">
+      <c r="B14" s="42" t="inlineStr">
         <is>
           <t>docs/EcomCraft 开发总表.xlsx，随仓库提交到 dev 分支</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="19.4" customHeight="1" s="23">
-      <c r="A14" s="25" t="inlineStr">
+    <row r="15" ht="19.5" customHeight="1" s="23">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>填写约定</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="19.5" customHeight="1" s="23">
-      <c r="A15" s="43" t="inlineStr">
-        <is>
-          <t>黄色单元格</t>
-        </is>
-      </c>
-      <c r="B15" s="42" t="inlineStr">
-        <is>
-          <t>由你填写；“状态”列从下拉菜单选择（未开始 / 进行中 / 已完成 / 暂缓）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" s="23">
       <c r="A16" s="43" t="inlineStr">
         <is>
+          <t>黄色单元格</t>
+        </is>
+      </c>
+      <c r="B16" s="42" t="inlineStr">
+        <is>
+          <t>由你填写；“状态”列从下拉菜单选择（未开始 / 进行中 / 已完成 / 暂缓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="19.4" customHeight="1" s="23">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
           <t>编号规则</t>
         </is>
       </c>
-      <c r="B16" s="42" t="inlineStr">
+      <c r="B17" s="42" t="inlineStr">
         <is>
           <t>F = 功能，T = 开发任务，N = 非开发事项，S = 痛点解决方案；编号不复用，合并或取消的项在备注中说明</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="19.4" customHeight="1" s="23">
-      <c r="A17" s="25" t="inlineStr">
+    <row r="18" ht="19.5" customHeight="1" s="23">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>用 Claude Code 开发的流程</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="19.5" customHeight="1" s="23">
-      <c r="A18" s="43" t="inlineStr">
-        <is>
-          <t>第 1 步</t>
-        </is>
-      </c>
-      <c r="B18" s="42" t="inlineStr">
-        <is>
-          <t>先做 T00：在仓库根目录建 CLAUDE.md，并用 @AGENTS.md 导入现有规则</t>
         </is>
       </c>
     </row>
     <row r="19" ht="19.5" customHeight="1" s="23">
       <c r="A19" s="43" t="inlineStr">
         <is>
-          <t>第 2 步</t>
+          <t>第 1 步</t>
         </is>
       </c>
       <c r="B19" s="42" t="inlineStr">
         <is>
-          <t>按“顺序”列一次只做一个任务；每个任务开一个新会话，避免上下文混在一起</t>
+          <t>先做 T00：在仓库根目录建 CLAUDE.md，并用 @AGENTS.md 导入现有规则</t>
         </is>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" s="23">
       <c r="A20" s="43" t="inlineStr">
         <is>
-          <t>第 3 步</t>
+          <t>第 2 步</t>
         </is>
       </c>
       <c r="B20" s="42" t="inlineStr">
         <is>
-          <t>复制该任务的“Claude Code 提示词”粘贴进去；大多数提示词会让 Claude 先进入计划模式出方案，你看过确认后再让它写代码</t>
+          <t>按“顺序”列一次只做一个任务；每个任务开一个新会话，避免上下文混在一起</t>
         </is>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1" s="23">
       <c r="A21" s="43" t="inlineStr">
         <is>
-          <t>第 4 步</t>
+          <t>第 3 步</t>
         </is>
       </c>
       <c r="B21" s="42" t="inlineStr">
         <is>
-          <t>Claude 完成后，按“测试方式”列自己验证；涉及 GPU 生成的效果必须实际跑一遍，涉及多机的要在两台电脑上验证</t>
+          <t>复制该任务的“Claude Code 提示词”粘贴进去；大多数提示词会让 Claude 先进入计划模式出方案，你看过确认后再让它写代码</t>
         </is>
       </c>
     </row>
     <row r="22" ht="19.5" customHeight="1" s="23">
       <c r="A22" s="43" t="inlineStr">
         <is>
-          <t>第 5 步</t>
+          <t>第 4 步</t>
         </is>
       </c>
       <c r="B22" s="42" t="inlineStr">
         <is>
-          <t>验证通过后一个任务做一次提交（dev 分支），再把任务状态改为“已完成”</t>
+          <t>Claude 完成后，按“测试方式”列自己验证；涉及 GPU 生成的效果必须实际跑一遍，涉及多机的要在两台电脑上验证</t>
         </is>
       </c>
     </row>
     <row r="23" ht="19.5" customHeight="1" s="23">
       <c r="A23" s="43" t="inlineStr">
         <is>
-          <t>第 6 步</t>
+          <t>第 5 步</t>
         </is>
       </c>
       <c r="B23" s="42" t="inlineStr">
         <is>
-          <t>“依赖”列中的任务未完成前不要开始；N 开头的依赖是非开发事项</t>
+          <t>验证通过后一个任务做一次提交（dev 分支），再把任务状态改为“已完成”</t>
         </is>
       </c>
     </row>
     <row r="24" ht="19.5" customHeight="1" s="23">
       <c r="A24" s="43" t="inlineStr">
         <is>
+          <t>第 6 步</t>
+        </is>
+      </c>
+      <c r="B24" s="42" t="inlineStr">
+        <is>
+          <t>“依赖”列中的任务未完成前不要开始；N 开头的依赖是非开发事项</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19.4" customHeight="1" s="23">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
           <t>第 7 步</t>
         </is>
       </c>
-      <c r="B24" s="42" t="inlineStr">
+      <c r="B25" s="42" t="inlineStr">
         <is>
           <t>每个任务涉及的文档都要中英文同步更新</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="19.4" customHeight="1" s="23">
-      <c r="A25" s="25" t="inlineStr">
+    <row r="26" ht="35" customHeight="1" s="23">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t>注意事项</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="35" customHeight="1" s="23">
-      <c r="A26" s="43" t="inlineStr">
-        <is>
-          <t>重新构建</t>
-        </is>
-      </c>
-      <c r="B26" s="42" t="inlineStr">
-        <is>
-          <t>修改 src/Extensions/EcomCraft/ 的 C# 代码后，需按 AGENTS.md 重新构建扩展，否则会加载旧程序集</t>
         </is>
       </c>
     </row>
     <row r="27" ht="19.5" customHeight="1" s="23">
       <c r="A27" s="43" t="inlineStr">
         <is>
-          <t>用户数据</t>
+          <t>重新构建</t>
         </is>
       </c>
       <c r="B27" s="42" t="inlineStr">
         <is>
-          <t>不要让 Claude 修改 Data/、Models/、Output/ 中的内容</t>
+          <t>修改 src/Extensions/EcomCraft/ 的 C# 代码后，需按 AGENTS.md 重新构建扩展，否则会加载旧程序集</t>
         </is>
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1" s="23">
       <c r="A28" s="43" t="inlineStr">
         <is>
-          <t>规则变更</t>
+          <t>用户数据</t>
         </is>
       </c>
       <c r="B28" s="42" t="inlineStr">
         <is>
-          <t>T08、T09、T29 会修改需求文档或 AGENTS.md 中的规则，务必自己审阅后再同意</t>
+          <t>不要让 Claude 修改 Data/、Models/、Output/ 中的内容</t>
         </is>
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1" s="23">
       <c r="A29" s="43" t="inlineStr">
         <is>
+          <t>规则变更</t>
+        </is>
+      </c>
+      <c r="B29" s="42" t="inlineStr">
+        <is>
+          <t>T08、T09、T29 会修改需求文档或 AGENTS.md 中的规则，务必自己审阅后再同意</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
           <t>范围变更</t>
         </is>
       </c>
-      <c r="B29" s="42" t="inlineStr">
+      <c r="B30" s="42" t="inlineStr">
         <is>
           <t>先改架构文档和需求文档（中英文），再改本表，最后改代码</t>
         </is>
@@ -1028,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="22" min="1" max="1"/>
@@ -3744,6 +3756,326 @@
       </c>
       <c r="L52" s="44" t="n"/>
       <c r="M52" s="44" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>F52</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>改版：简易模式 v3</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>上传四入口（本机、拍照、商品库、画廊选图）</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>本机、拍照保留；商品库折叠入口提升为并列按钮并弹窗选择；新增从画廊选已生成作品图作商品图（客户端压缩到 5 MB，质量检查生效，缩略图标来源）</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Studio/simple.js、index.html；画廊与商品库接口复用</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>运营友好</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>简易模式改版需求文档 v3</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>T54</t>
+        </is>
+      </c>
+      <c r="J53">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A53)</f>
+        <v/>
+      </c>
+      <c r="K53">
+        <f>IF(J53=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A53,开发任务!$L$5:$L$200,"已完成")=J53,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A53,开发任务!$L$5:$L$200,"未开始")=J53,"未开始","进行中")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>F53</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>改版：简易模式 v3</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>产品类型两级选择、可选风格与模特勾选</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>「风格」改为大类→子类产品类型（初版 4 大类，重点个护美妆：洗发水、护手霜等），子类英文片段进提示词；视觉风格改为可选第二行；新增与白底主图互斥的「需要模特」勾选</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>新增 Templates/product-types.json；Prompting/、Studio/simple.js</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>运营友好</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>简易模式改版需求文档 v3</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>T55</t>
+        </is>
+      </c>
+      <c r="J54">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A54)</f>
+        <v/>
+      </c>
+      <c r="K54">
+        <f>IF(J54=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A54,开发任务!$L$5:$L$200,"已完成")=J54,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A54,开发任务!$L$5:$L$200,"未开始")=J54,"未开始","进行中")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>F54</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>改版：简易模式 v3</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>双语提示词与 AI 扩写</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>「AI 扩写」按面板语言生成并回填双语提示词；中英文都可编辑：中文修改提交时自动翻译成英文发送（以用户改稿为准），英文修改直接发送；任务卡片显示实际使用提示词；引擎提示词固定英文</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Prompting/PromptService.cs、Studio/simple.js、MagicPrompt</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>运营友好</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>简易模式改版需求文档 v3</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>T56</t>
+        </is>
+      </c>
+      <c r="J55">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A55)</f>
+        <v/>
+      </c>
+      <c r="K55">
+        <f>IF(J55=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A55,开发任务!$L$5:$L$200,"已完成")=J55,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A55,开发任务!$L$5:$L$200,"未开始")=J55,"未开始","进行中")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>F55</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>改版：简易模式 v3</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>候选张数手动输入与 20 张总上限</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>下拉改为数字输入，仅 1–20 正整数；单次出图与一键出整套统一「总张数 ≤ 20」，服务端同步校验；整套预计张数（商品×类型×张数）实时提示；两个出图按钮的区分提示文案</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Studio/simple.js、StudioApi.cs、Generation/BatchService.cs</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>简易模式改版需求文档 v3</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>T57</t>
+        </is>
+      </c>
+      <c r="J56">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A56)</f>
+        <v/>
+      </c>
+      <c r="K56">
+        <f>IF(J56=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A56,开发任务!$L$5:$L$200,"已完成")=J56,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A56,开发任务!$L$5:$L$200,"未开始")=J56,"未开始","进行中")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>F56</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>改版：简易模式 v3</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>出图链路提速（提交即入队）</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>提交立即入队返回任务号，提示词组合/翻译移到后台完成（45 秒上限保留）；已扩写未改或改英文时跳过模型调用；状态三段：生成提示词→排队/执行（含服务器名）→完成；降级不阻塞；一键出整套同样改造</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>StudioApi.cs、Generation/</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>运营友好</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>简易模式改版需求文档 v3</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>T58</t>
+        </is>
+      </c>
+      <c r="J57">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A57)</f>
+        <v/>
+      </c>
+      <c r="K57">
+        <f>IF(J57=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A57,开发任务!$L$5:$L$200,"已完成")=J57,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A57,开发任务!$L$5:$L$200,"未开始")=J57,"未开始","进行中")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>F57</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>改版：简易模式 v3</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>标准工作流自动生成</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>服务端蓝图生成器按图片类型生成标准 ComfyUI 工作流，以「系统生成」来源经 WorkflowReview 注册发布、可下架；启动自动检查补建 + 管理员设置页初始化按钮与状态清单；默认大模型管理员指定并复用依赖检查；初版覆盖场景、细节与含模特场景</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Templates/、WorkflowReview*.cs、StudioApi.cs、设置页</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>简易模式改版需求文档 v3</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>T59</t>
+        </is>
+      </c>
+      <c r="J58">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A58)</f>
+        <v/>
+      </c>
+      <c r="K58">
+        <f>IF(J58=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A58,开发任务!$L$5:$L$200,"已完成")=J58,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A58,开发任务!$L$5:$L$200,"未开始")=J58,"未开始","进行中")))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:M31"/>
@@ -3767,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="22" min="1" max="1"/>
@@ -3800,7 +4132,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32.8" customHeight="1" s="23">
       <c r="A4" s="30" t="inlineStr">
         <is>
@@ -7430,9 +7761,393 @@
       <c r="M56" s="38" t="n"/>
       <c r="N56" s="44" t="n"/>
     </row>
-    <row r="57"/>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>T55</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>改版：简易模式 v3</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>F53</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>简易模式第 2 步：产品类型两级选择、可选风格与模特勾选</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>新增 Templates/product-types.json；Prompting/PromptService.cs、Studio/simple.js、index.html、lang/en.js、Tests</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>大类/子类两级选择、可选视觉风格（“自动”卡片）与“需要模特”勾选（白底主图互斥）状态正确联动并进入提示词组合；product-types.json 结构校验、无效条目跳过并记日志；选择记入浏览器；中英文界面完整</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>node --test studio-i18n / simple-mode 测试；启动服务，浏览器中英文各验证一遍</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+简易模式改版需求以 docs/EcomCraft 简易模式改版需求.zh-CN.md 为准（交互原型：docs/EcomCraft 简易模式改版原型.html），需求有变化先改该文档（中英文）。
+任务：按需求文档第 3 节实现 F53：新增 product-types.json（4 大类、个护美妆含洗发水/护手霜/身体乳/口红/香水）与服务端读取校验；简易模式第 2 步把风格改为两级产品类型，视觉风格改为可选第二行，新增与白底主图互斥的“需要模特”勾选；子类与模特英文片段并入提示词组合。布局对照交互原型，沿用现有三步卡片网格。
+先进入计划模式列出改动文件、数据结构和风险，我确认后再实现。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+    </row>
     <row r="58" ht="32" customHeight="1" s="23">
-      <c r="A58" s="40" t="inlineStr">
+      <c r="A58" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>T57</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>改版：简易模式 v3</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>F55</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>候选张数手动输入、20 张总上限与出图按钮文案</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Studio/simple.js、index.html、lang/en.js、StudioApi.cs、Generation/BatchService.cs、SetRules.cs</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>T55</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>数字输入仅接受 1–20 正整数，非法即时提示并禁用按钮；单次出图与一键出整套统一「总张数 ≤ 20」且服务端校验同步；整套预计张数=商品×类型×张数实时提示；两个按钮的区分文案正确；白底主图 1 张提示保持</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>边界输入（0、2.5、abc、21）手动验证；服务端超限请求返回错误；界面中英文</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+简易模式改版需求以 docs/EcomCraft 简易模式改版需求.zh-CN.md 为准（交互原型：docs/EcomCraft 简易模式改版原型.html），需求有变化先改该文档（中英文）。
+任务：按需求文档第 5 节实现 F55：候选张数改数字输入并校验正整数 1–20；单次与整套统一总张数 ≤ 20（服务端同步放宽单批上限并加总张数校验）；「一键出整套」预计张数实时计算、超限禁用并说明原因；「开始出图/一键出整套」提示文案按需求更新。
+先进入计划模式列出改动文件、数据结构和风险，我确认后再实现。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>T56</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>改版：简易模式 v3</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>F54</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>双语提示词面板与 AI 扩写</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Prompting/PromptService.cs、Studio/simple.js、index.html、lang/en.js、MagicPrompt</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>T55</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>「AI 扩写」按面板语言生成并回填双语提示词；中文修改后提交自动翻译成英文（以用户改稿为准，译文回填英文页签）；英文修改直接发送；状态标签三态正确；任务卡片显示实际使用提示词；模型不可用降级提示且不阻塞出图</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>翻译测试 + 浏览器中英文验证；模拟 MagicPrompt 不可用走降级</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+简易模式改版需求以 docs/EcomCraft 简易模式改版需求.zh-CN.md 为准（交互原型：docs/EcomCraft 简易模式改版原型.html），需求有变化先改该文档（中英文）。
+任务：按需求文档第 4 节实现 F54：提示词服务增加扩写/翻译调用；简易模式加「AI 扩写」按钮与中文/English 双语页签面板（都可编辑）；实现发送规则：英文修改直发、中文修改提交时翻译成英文（绝不用旧版本）、引擎提示词固定英文；状态标签与任务卡片的实际提示词展示。
+先进入计划模式列出改动文件、数据结构和风险，我确认后再实现。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>T58</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>改版：简易模式 v3</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>F56</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>出图链路提速：提交即入队</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>StudioApi.cs、Generation/、Studio/simple.js</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>T56</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>提交立即返回任务号并入队，无最长 45 秒同步等待；提示词组合/翻译在后台完成（45 秒上限保留）；已扩写未改或改英文时跳过模型调用；状态三段（生成提示词→排队/执行含服务器名→完成）；降级用默认提示词不阻塞；一键出整套同样改造</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>手动提交观察状态流转；断开 MagicPrompt 验证降级出图</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+简易模式改版需求以 docs/EcomCraft 简易模式改版需求.zh-CN.md 为准（交互原型：docs/EcomCraft 简易模式改版原型.html），需求有变化先改该文档（中英文）。
+任务：按需求文档第 6 节实现 F56：把 EcomCraftStudioGenerate 与 EcomCraftStudioGenerateSet 提交路径上的提示词组合移到后台任务；提交立即入队返回任务号；满足跳过条件（已扩写未改/改英文）时不调模型；前端状态三段显示；保留降级与超时。
+先进入计划模式列出改动文件、数据结构和风险，我确认后再实现。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>T59</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>改版：简易模式 v3</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>F57</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>标准工作流自动生成（蓝图生成器）</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Templates/、WorkflowReview*.cs、StudioApi.cs、EcomCraft.cs、设置页</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>T58；N01</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>蓝图生成器按图片类型生成标准工作流 JSON，以「系统生成」来源经 WorkflowReview 发布、可下架；启动自动检查补建 + 管理员设置页「初始化标准工作流」按钮与状态清单；使用管理员指定的默认大模型并复用 F08 依赖检查（缺模型不注册并提示）；初版覆盖场景、细节与含模特场景；普通用户仍只能提交工作流 ID</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>全新环境（登记执行服务器+装默认模型）不手工建工作流完成场景/细节出图；审核列表可见系统来源并可下架；缺模型时提示且不注册</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+简易模式改版需求以 docs/EcomCraft 简易模式改版需求.zh-CN.md 为准（交互原型：docs/EcomCraft 简易模式改版原型.html），需求有变化先改该文档（中英文）。
+任务：按需求文档第 7 节实现 F57：新增工作流蓝图生成器（默认大模型+采样器+解码+保存；保真模板带商品图输入节点）；注册走 WorkflowReview 标记“系统生成”并自动发布、可下架；服务启动自动检查补建 + 管理员设置页初始化按钮与状态清单；设置中指定默认大模型并复用依赖检查。安全边界不变：客户端仍只提交工作流 ID。
+先进入计划模式列出改动文件、数据结构和风险，我确认后再实现。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>T54</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>改版：简易模式 v3</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>F52</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>上传四入口：本机、拍照、商品库与画廊选图</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Studio/simple.js、index.html、lang/en.js、StudioApi.cs（画廊/商品库接口复用）</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>T55</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>四个入口并列；商品库与画廊弹窗选择（画廊标注已生成作品）；画廊选图客户端压缩到 5 MB；F38 质量检查对画廊选图生效；缩略图显示来源标识；入库、重命名、删除与普通上传一致</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>四入口各上传一次手动验证（含大于 5 MB 的画廊图压缩）；中英文界面</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+简易模式改版需求以 docs/EcomCraft 简易模式改版需求.zh-CN.md 为准（交互原型：docs/EcomCraft 简易模式改版原型.html），需求有变化先改该文档（中英文）。
+任务：按需求文档第 2 节实现 F52：第 1 步四个并列入口；商品库折叠入口改为并列按钮弹窗；新增画廊选图弹窗（复用作品列表接口），选图压缩到 5 MB 再用，质量检查与入库规则同普通上传，缩略图标注来源。
+先进入计划模式列出改动文件、数据结构和风险，我确认后再实现。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+    </row>
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" s="40" t="inlineStr">
         <is>
           <t>规模：S 约半天以内，M 约 1–2 天，L 3 天以上（含你的验证时间，仅供粗略估计）。原 T03、T26 已分别并入 T13、T34。</t>
         </is>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -827,12 +827,12 @@
       </c>
     </row>
     <row r="13" ht="19.5" customHeight="1" s="23">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>简易模式改版需求</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>docs/EcomCraft 简易模式改版需求.zh-CN.md（英文版 docs/EcomCraft Simple Mode Redesign.md）：简易模式 v3 改版（上传四入口、产品类型、双语提示词、20 张上限、出图提速、工作流自动生成）的需求定稿；交互原型 docs/EcomCraft 简易模式改版原型.html</t>
         </is>
@@ -3758,321 +3758,321 @@
       <c r="M52" s="44" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="22" t="inlineStr">
         <is>
           <t>F52</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="22" t="inlineStr">
         <is>
           <t>改版：简易模式 v3</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="22" t="inlineStr">
         <is>
           <t>上传四入口（本机、拍照、商品库、画廊选图）</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="22" t="inlineStr">
         <is>
           <t>本机、拍照保留；商品库折叠入口提升为并列按钮并弹窗选择；新增从画廊选已生成作品图作商品图（客户端压缩到 5 MB，质量检查生效，缩略图标来源）</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="22" t="inlineStr">
         <is>
           <t>Studio/simple.js、index.html；画廊与商品库接口复用</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="22" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="22" t="inlineStr">
         <is>
           <t>运营友好</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="22" t="inlineStr">
         <is>
           <t>简易模式改版需求文档 v3</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" s="22" t="inlineStr">
         <is>
           <t>T54</t>
         </is>
       </c>
-      <c r="J53">
+      <c r="J53" s="22">
         <f>COUNTIF(开发任务!$D$5:$D$200,A53)</f>
         <v/>
       </c>
-      <c r="K53">
+      <c r="K53" s="22">
         <f>IF(J53=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A53,开发任务!$L$5:$L$200,"已完成")=J53,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A53,开发任务!$L$5:$L$200,"未开始")=J53,"未开始","进行中")))</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="22" t="inlineStr">
         <is>
           <t>F53</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="22" t="inlineStr">
         <is>
           <t>改版：简易模式 v3</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="22" t="inlineStr">
         <is>
           <t>产品类型两级选择、可选风格与模特勾选</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="22" t="inlineStr">
         <is>
           <t>「风格」改为大类→子类产品类型（初版 4 大类，重点个护美妆：洗发水、护手霜等），子类英文片段进提示词；视觉风格改为可选第二行；新增与白底主图互斥的「需要模特」勾选</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="22" t="inlineStr">
         <is>
           <t>新增 Templates/product-types.json；Prompting/、Studio/simple.js</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="22" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="22" t="inlineStr">
         <is>
           <t>运营友好</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" s="22" t="inlineStr">
         <is>
           <t>简易模式改版需求文档 v3</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" s="22" t="inlineStr">
         <is>
           <t>T55</t>
         </is>
       </c>
-      <c r="J54">
+      <c r="J54" s="22">
         <f>COUNTIF(开发任务!$D$5:$D$200,A54)</f>
         <v/>
       </c>
-      <c r="K54">
+      <c r="K54" s="22">
         <f>IF(J54=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A54,开发任务!$L$5:$L$200,"已完成")=J54,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A54,开发任务!$L$5:$L$200,"未开始")=J54,"未开始","进行中")))</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="22" t="inlineStr">
         <is>
           <t>F54</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="22" t="inlineStr">
         <is>
           <t>改版：简易模式 v3</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="22" t="inlineStr">
         <is>
           <t>双语提示词与 AI 扩写</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="22" t="inlineStr">
         <is>
           <t>「AI 扩写」按面板语言生成并回填双语提示词；中英文都可编辑：中文修改提交时自动翻译成英文发送（以用户改稿为准），英文修改直接发送；任务卡片显示实际使用提示词；引擎提示词固定英文</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="22" t="inlineStr">
         <is>
           <t>Prompting/PromptService.cs、Studio/simple.js、MagicPrompt</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="22" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="22" t="inlineStr">
         <is>
           <t>运营友好</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="22" t="inlineStr">
         <is>
           <t>简易模式改版需求文档 v3</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I55" s="22" t="inlineStr">
         <is>
           <t>T56</t>
         </is>
       </c>
-      <c r="J55">
+      <c r="J55" s="22">
         <f>COUNTIF(开发任务!$D$5:$D$200,A55)</f>
         <v/>
       </c>
-      <c r="K55">
+      <c r="K55" s="22">
         <f>IF(J55=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A55,开发任务!$L$5:$L$200,"已完成")=J55,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A55,开发任务!$L$5:$L$200,"未开始")=J55,"未开始","进行中")))</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="22" t="inlineStr">
         <is>
           <t>F55</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="22" t="inlineStr">
         <is>
           <t>改版：简易模式 v3</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="22" t="inlineStr">
         <is>
           <t>候选张数手动输入与 20 张总上限</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="22" t="inlineStr">
         <is>
           <t>下拉改为数字输入，仅 1–20 正整数；单次出图与一键出整套统一「总张数 ≤ 20」，服务端同步校验；整套预计张数（商品×类型×张数）实时提示；两个出图按钮的区分提示文案</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="22" t="inlineStr">
         <is>
           <t>Studio/simple.js、StudioApi.cs、Generation/BatchService.cs</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="22" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" s="22" t="inlineStr">
         <is>
           <t>简易模式改版需求文档 v3</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I56" s="22" t="inlineStr">
         <is>
           <t>T57</t>
         </is>
       </c>
-      <c r="J56">
+      <c r="J56" s="22">
         <f>COUNTIF(开发任务!$D$5:$D$200,A56)</f>
         <v/>
       </c>
-      <c r="K56">
+      <c r="K56" s="22">
         <f>IF(J56=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A56,开发任务!$L$5:$L$200,"已完成")=J56,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A56,开发任务!$L$5:$L$200,"未开始")=J56,"未开始","进行中")))</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="22" t="inlineStr">
         <is>
           <t>F56</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="22" t="inlineStr">
         <is>
           <t>改版：简易模式 v3</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="22" t="inlineStr">
         <is>
           <t>出图链路提速（提交即入队）</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="22" t="inlineStr">
         <is>
           <t>提交立即入队返回任务号，提示词组合/翻译移到后台完成（45 秒上限保留）；已扩写未改或改英文时跳过模型调用；状态三段：生成提示词→排队/执行（含服务器名）→完成；降级不阻塞；一键出整套同样改造</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="22" t="inlineStr">
         <is>
           <t>StudioApi.cs、Generation/</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="22" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="22" t="inlineStr">
         <is>
           <t>运营友好</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" s="22" t="inlineStr">
         <is>
           <t>简易模式改版需求文档 v3</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" s="22" t="inlineStr">
         <is>
           <t>T58</t>
         </is>
       </c>
-      <c r="J57">
+      <c r="J57" s="22">
         <f>COUNTIF(开发任务!$D$5:$D$200,A57)</f>
         <v/>
       </c>
-      <c r="K57">
+      <c r="K57" s="22">
         <f>IF(J57=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A57,开发任务!$L$5:$L$200,"已完成")=J57,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A57,开发任务!$L$5:$L$200,"未开始")=J57,"未开始","进行中")))</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="22" t="inlineStr">
         <is>
           <t>F57</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="22" t="inlineStr">
         <is>
           <t>改版：简易模式 v3</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="22" t="inlineStr">
         <is>
           <t>标准工作流自动生成</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="22" t="inlineStr">
         <is>
           <t>服务端蓝图生成器按图片类型生成标准 ComfyUI 工作流，以「系统生成」来源经 WorkflowReview 注册发布、可下架；启动自动检查补建 + 管理员设置页初始化按钮与状态清单；默认大模型管理员指定并复用依赖检查；初版覆盖场景、细节与含模特场景</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="22" t="inlineStr">
         <is>
           <t>Templates/、WorkflowReview*.cs、StudioApi.cs、设置页</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="22" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" s="22" t="inlineStr">
         <is>
           <t>简易模式改版需求文档 v3</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I58" s="22" t="inlineStr">
         <is>
           <t>T59</t>
         </is>
       </c>
-      <c r="J58">
+      <c r="J58" s="22">
         <f>COUNTIF(开发任务!$D$5:$D$200,A58)</f>
         <v/>
       </c>
-      <c r="K58">
+      <c r="K58" s="22">
         <f>IF(J58=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A58,开发任务!$L$5:$L$200,"已完成")=J58,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A58,开发任务!$L$5:$L$200,"未开始")=J58,"未开始","进行中")))</f>
         <v/>
       </c>
@@ -7762,55 +7762,55 @@
       <c r="N56" s="44" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" t="n">
+      <c r="A57" s="22" t="n">
         <v>53</v>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="22" t="inlineStr">
         <is>
           <t>T55</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="22" t="inlineStr">
         <is>
           <t>改版：简易模式 v3</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="22" t="inlineStr">
         <is>
           <t>F53</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="22" t="inlineStr">
         <is>
           <t>简易模式第 2 步：产品类型两级选择、可选风格与模特勾选</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="22" t="inlineStr">
         <is>
           <t>新增 Templates/product-types.json；Prompting/PromptService.cs、Studio/simple.js、index.html、lang/en.js、Tests</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" s="22" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" s="22" t="inlineStr">
         <is>
           <t>大类/子类两级选择、可选视觉风格（“自动”卡片）与“需要模特”勾选（白底主图互斥）状态正确联动并进入提示词组合；product-types.json 结构校验、无效条目跳过并记日志；选择记入浏览器；中英文界面完整</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J57" s="22" t="inlineStr">
         <is>
           <t>node --test studio-i18n / simple-mode 测试；启动服务，浏览器中英文各验证一遍</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K57" s="22" t="inlineStr">
         <is>
           <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
 简易模式改版需求以 docs/EcomCraft 简易模式改版需求.zh-CN.md 为准（交互原型：docs/EcomCraft 简易模式改版原型.html），需求有变化先改该文档（中英文）。
@@ -7819,62 +7819,72 @@
 完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>未开始</t>
+      <c r="L57" s="22" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>提交 467c036d；服务已重启部署（扩展程序集含该提交哈希）；浏览器人工验收待做</t>
         </is>
       </c>
     </row>
     <row r="58" ht="32" customHeight="1" s="23">
-      <c r="A58" t="n">
+      <c r="A58" s="22" t="n">
         <v>54</v>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="22" t="inlineStr">
         <is>
           <t>T57</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="22" t="inlineStr">
         <is>
           <t>改版：简易模式 v3</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="22" t="inlineStr">
         <is>
           <t>F55</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="22" t="inlineStr">
         <is>
           <t>候选张数手动输入、20 张总上限与出图按钮文案</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="22" t="inlineStr">
         <is>
           <t>Studio/simple.js、index.html、lang/en.js、StudioApi.cs、Generation/BatchService.cs、SetRules.cs</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="22" t="inlineStr">
         <is>
           <t>T55</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" s="22" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I58" s="22" t="inlineStr">
         <is>
           <t>数字输入仅接受 1–20 正整数，非法即时提示并禁用按钮；单次出图与一键出整套统一「总张数 ≤ 20」且服务端校验同步；整套预计张数=商品×类型×张数实时提示；两个按钮的区分文案正确；白底主图 1 张提示保持</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J58" s="22" t="inlineStr">
         <is>
           <t>边界输入（0、2.5、abc、21）手动验证；服务端超限请求返回错误；界面中英文</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K58" s="22" t="inlineStr">
         <is>
           <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
 简易模式改版需求以 docs/EcomCraft 简易模式改版需求.zh-CN.md 为准（交互原型：docs/EcomCraft 简易模式改版原型.html），需求有变化先改该文档（中英文）。
@@ -7883,62 +7893,72 @@
 完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>未开始</t>
+      <c r="L58" s="22" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>提交 0e7c6b3e；服务已重启部署（扩展程序集含该提交哈希）；浏览器人工验收待做</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
+      <c r="A59" s="22" t="n">
         <v>55</v>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="22" t="inlineStr">
         <is>
           <t>T56</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="22" t="inlineStr">
         <is>
           <t>改版：简易模式 v3</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="22" t="inlineStr">
         <is>
           <t>F54</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="22" t="inlineStr">
         <is>
           <t>双语提示词面板与 AI 扩写</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="22" t="inlineStr">
         <is>
           <t>Prompting/PromptService.cs、Studio/simple.js、index.html、lang/en.js、MagicPrompt</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" s="22" t="inlineStr">
         <is>
           <t>T55</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H59" s="22" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I59" s="22" t="inlineStr">
         <is>
           <t>「AI 扩写」按面板语言生成并回填双语提示词；中文修改后提交自动翻译成英文（以用户改稿为准，译文回填英文页签）；英文修改直接发送；状态标签三态正确；任务卡片显示实际使用提示词；模型不可用降级提示且不阻塞出图</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J59" s="22" t="inlineStr">
         <is>
           <t>翻译测试 + 浏览器中英文验证；模拟 MagicPrompt 不可用走降级</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K59" s="22" t="inlineStr">
         <is>
           <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
 简易模式改版需求以 docs/EcomCraft 简易模式改版需求.zh-CN.md 为准（交互原型：docs/EcomCraft 简易模式改版原型.html），需求有变化先改该文档（中英文）。
@@ -7947,62 +7967,62 @@
 完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="L59" s="22" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
+      <c r="A60" s="22" t="n">
         <v>56</v>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="22" t="inlineStr">
         <is>
           <t>T58</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="22" t="inlineStr">
         <is>
           <t>改版：简易模式 v3</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="22" t="inlineStr">
         <is>
           <t>F56</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" s="22" t="inlineStr">
         <is>
           <t>出图链路提速：提交即入队</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="22" t="inlineStr">
         <is>
           <t>StudioApi.cs、Generation/、Studio/simple.js</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" s="22" t="inlineStr">
         <is>
           <t>T56</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H60" s="22" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I60" s="22" t="inlineStr">
         <is>
           <t>提交立即返回任务号并入队，无最长 45 秒同步等待；提示词组合/翻译在后台完成（45 秒上限保留）；已扩写未改或改英文时跳过模型调用；状态三段（生成提示词→排队/执行含服务器名→完成）；降级用默认提示词不阻塞；一键出整套同样改造</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J60" s="22" t="inlineStr">
         <is>
           <t>手动提交观察状态流转；断开 MagicPrompt 验证降级出图</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K60" s="22" t="inlineStr">
         <is>
           <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
 简易模式改版需求以 docs/EcomCraft 简易模式改版需求.zh-CN.md 为准（交互原型：docs/EcomCraft 简易模式改版原型.html），需求有变化先改该文档（中英文）。
@@ -8011,62 +8031,62 @@
 完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="L60" s="22" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
+      <c r="A61" s="22" t="n">
         <v>57</v>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="22" t="inlineStr">
         <is>
           <t>T59</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="22" t="inlineStr">
         <is>
           <t>改版：简易模式 v3</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="22" t="inlineStr">
         <is>
           <t>F57</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="22" t="inlineStr">
         <is>
           <t>标准工作流自动生成（蓝图生成器）</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="22" t="inlineStr">
         <is>
           <t>Templates/、WorkflowReview*.cs、StudioApi.cs、EcomCraft.cs、设置页</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="22" t="inlineStr">
         <is>
           <t>T58；N01</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" s="22" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I61" s="22" t="inlineStr">
         <is>
           <t>蓝图生成器按图片类型生成标准工作流 JSON，以「系统生成」来源经 WorkflowReview 发布、可下架；启动自动检查补建 + 管理员设置页「初始化标准工作流」按钮与状态清单；使用管理员指定的默认大模型并复用 F08 依赖检查（缺模型不注册并提示）；初版覆盖场景、细节与含模特场景；普通用户仍只能提交工作流 ID</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J61" s="22" t="inlineStr">
         <is>
           <t>全新环境（登记执行服务器+装默认模型）不手工建工作流完成场景/细节出图；审核列表可见系统来源并可下架；缺模型时提示且不注册</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K61" s="22" t="inlineStr">
         <is>
           <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
 简易模式改版需求以 docs/EcomCraft 简易模式改版需求.zh-CN.md 为准（交互原型：docs/EcomCraft 简易模式改版原型.html），需求有变化先改该文档（中英文）。
@@ -8075,62 +8095,62 @@
 完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="L61" s="22" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
+      <c r="A62" s="22" t="n">
         <v>58</v>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="22" t="inlineStr">
         <is>
           <t>T54</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="22" t="inlineStr">
         <is>
           <t>改版：简易模式 v3</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="22" t="inlineStr">
         <is>
           <t>F52</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" s="22" t="inlineStr">
         <is>
           <t>上传四入口：本机、拍照、商品库与画廊选图</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="22" t="inlineStr">
         <is>
           <t>Studio/simple.js、index.html、lang/en.js、StudioApi.cs（画廊/商品库接口复用）</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" s="22" t="inlineStr">
         <is>
           <t>T55</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H62" s="22" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I62" s="22" t="inlineStr">
         <is>
           <t>四个入口并列；商品库与画廊弹窗选择（画廊标注已生成作品）；画廊选图客户端压缩到 5 MB；F38 质量检查对画廊选图生效；缩略图显示来源标识；入库、重命名、删除与普通上传一致</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J62" s="22" t="inlineStr">
         <is>
           <t>四入口各上传一次手动验证（含大于 5 MB 的画廊图压缩）；中英文界面</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K62" s="22" t="inlineStr">
         <is>
           <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
 简易模式改版需求以 docs/EcomCraft 简易模式改版需求.zh-CN.md 为准（交互原型：docs/EcomCraft 简易模式改版原型.html），需求有变化先改该文档（中英文）。
@@ -8139,7 +8159,7 @@
 完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="L62" s="22" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="B3" s="42" t="inlineStr">
         <is>
-          <t>54 项功能，按 7 个阶段排列，其中 MVP（A 平台底座、B 电商出图、C 易用与运维）27 项、简易模式改版 v3（F52–F57）6 项已确认待开发；“功能状态”根据开发任务自动计算，不用手填</t>
+          <t>54 项功能，按 7 个阶段排列，其中 MVP（A 平台底座、B 电商出图、C 易用与运维）27 项；简易模式改版 v3（F52–F57）6 项中 5 项代码已完成、F57 暂缓；后续增强中 F25、F12、F47 代码已完成，F04 服务端已完成。“功能状态”根据开发任务自动计算，不用手填</t>
         </is>
       </c>
     </row>
@@ -4132,6 +4132,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32.8" customHeight="1" s="23">
       <c r="A4" s="30" t="inlineStr">
         <is>
@@ -6376,13 +6377,17 @@
       </c>
       <c r="L35" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M35" s="38" t="n"/>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="M35" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N35" s="44" t="inlineStr">
         <is>
-          <t>MVP 后优先</t>
+          <t>代码已提交（2115b794），开发机无 .NET SDK 未编译；待编译部署与人工验收。分镜放在简易模式第 2 步，最多 8 张；分镜只保存在当前页面</t>
         </is>
       </c>
     </row>
@@ -6449,7 +6454,11 @@
         </is>
       </c>
       <c r="M36" s="38" t="n"/>
-      <c r="N36" s="44" t="n"/>
+      <c r="N36" s="44" t="inlineStr">
+        <is>
+          <t>依赖 N09（确定主攻品类），未开始</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="252" customHeight="1" s="23">
       <c r="A37" s="47" t="n">
@@ -6510,11 +6519,19 @@
       </c>
       <c r="L37" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M37" s="38" t="n"/>
-      <c r="N37" s="44" t="n"/>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="M37" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N37" s="44" t="inlineStr">
+        <is>
+          <t>代码已提交（1edc7338），开发机无 .NET SDK 未编译；待编译部署与人工验收。按个人隔离；Logo 只传给声明槽位的模板；现有内置模板未声明槽位，只有品牌色和背景生效</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="267.5" customHeight="1" s="23">
       <c r="A38" s="47" t="n">
@@ -6575,13 +6592,17 @@
       </c>
       <c r="L38" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M38" s="38" t="n"/>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="M38" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N38" s="44" t="inlineStr">
         <is>
-          <t>会修改 AGENTS.md 规则，务必审阅</t>
+          <t>代码已提交（5964e936），开发机无 .NET SDK 未编译；待编译部署与人工验收。保存提示词（用户确认），AGENTS.md 已补充规则；界面见 T10</t>
         </is>
       </c>
     </row>
@@ -6709,11 +6730,19 @@
       </c>
       <c r="L40" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M40" s="38" t="n"/>
-      <c r="N40" s="44" t="n"/>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="M40" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N40" s="44" t="inlineStr">
+        <is>
+          <t>代码已提交（91db91d6），开发机无 .NET SDK 未编译；待编译部署与人工验收。思源黑体（OFL 1.1）随仓库附带；重点检查中英文字体渲染</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="221" customHeight="1" s="23">
       <c r="A41" s="47" t="n">
@@ -7824,12 +7853,12 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="M57" s="22" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="N57" s="22" t="inlineStr">
         <is>
           <t>提交 467c036d；服务已重启部署（扩展程序集含该提交哈希）；浏览器人工验收待做</t>
         </is>
@@ -7898,12 +7927,12 @@
           <t>已完成</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="M58" s="22" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="N58" s="22" t="inlineStr">
         <is>
           <t>提交 0e7c6b3e；服务已重启部署（扩展程序集含该提交哈希）；浏览器人工验收待做</t>
         </is>
@@ -7969,7 +7998,17 @@
       </c>
       <c r="L59" s="22" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>代码已提交（8124a752），开发机无 .NET SDK 未编译；待编译部署与人工验收。AI 扩写与双语提示词面板</t>
         </is>
       </c>
     </row>
@@ -8033,7 +8072,17 @@
       </c>
       <c r="L60" s="22" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>代码已提交（aee5a0bd），开发机无 .NET SDK 未编译；待编译部署与人工验收。提交即返回、后台生成提示词、三段任务状态</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8146,12 @@
       </c>
       <c r="L61" s="22" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>暂缓</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>用户 2026-10-28 决定暂缓：等 N01 选定可商用默认大模型后再做</t>
         </is>
       </c>
     </row>
@@ -8161,7 +8215,17 @@
       </c>
       <c r="L62" s="22" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>代码已提交（01c120e7，只改前端）；待人工验收。上传四入口、画廊选图压缩</t>
         </is>
       </c>
     </row>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -4132,7 +4132,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="32.8" customHeight="1" s="23">
       <c r="A4" s="30" t="inlineStr">
         <is>
@@ -8001,12 +8000,12 @@
           <t>进行中</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="M59" s="22" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="N59" s="22" t="inlineStr">
         <is>
           <t>代码已提交（8124a752），开发机无 .NET SDK 未编译；待编译部署与人工验收。AI 扩写与双语提示词面板</t>
         </is>
@@ -8075,12 +8074,12 @@
           <t>进行中</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="M60" s="22" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="N60" s="22" t="inlineStr">
         <is>
           <t>代码已提交（aee5a0bd），开发机无 .NET SDK 未编译；待编译部署与人工验收。提交即返回、后台生成提示词、三段任务状态</t>
         </is>
@@ -8146,12 +8145,12 @@
       </c>
       <c r="L61" s="22" t="inlineStr">
         <is>
-          <t>暂缓</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>用户 2026-10-28 决定暂缓：等 N01 选定可商用默认大模型后再做</t>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N61" s="22" t="inlineStr">
+        <is>
+          <t>N01 已完成（2026-10-28，默认模型见非开发事项 N01），取消暂缓；初版只做文生图，图生图见 N10</t>
         </is>
       </c>
     </row>
@@ -8218,12 +8217,12 @@
           <t>进行中</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="M62" s="22" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="N62" s="22" t="inlineStr">
         <is>
           <t>代码已提交（01c120e7，只改前端）；待人工验收。上传四入口、画廊选图压缩</t>
         </is>
@@ -8264,7 +8263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="22" min="1" max="1"/>
@@ -8349,11 +8348,15 @@
       </c>
       <c r="E5" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F5" s="44" t="n"/>
-      <c r="G5" s="44" t="n"/>
+      <c r="G5" s="44" t="inlineStr">
+        <is>
+          <t>2026-10-28 选定（用户已在执行服务器部署并试用）：UNet qwen-image-2.1-UC-Q4_K_M.gguf（GGUF 量化，需 ComfyUI-GGUF 节点）、文本编码器 qwen3vl_8b_int8_convrot.safetensors、VAE qwen_image_2.1_vae_bf16.safetensors；先用于文生图。该具体版本的商用许可待对照模型发布页核对。</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="50.5" customHeight="1" s="23">
       <c r="A6" s="47" t="inlineStr">
@@ -8594,6 +8597,39 @@
       </c>
       <c r="F13" s="44" t="n"/>
       <c r="G13" s="44" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="47" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>确定图生图方案（TODO）</t>
+        </is>
+      </c>
+      <c r="C14" s="40" t="inlineStr">
+        <is>
+          <t>为需要参考商品图的模板（图生图、局部重绘、商品融合）选定可商用模型和工作流；当前默认模型只用于文生图</t>
+        </is>
+      </c>
+      <c r="D14" s="42" t="inlineStr">
+        <is>
+          <t>T59 后续、T07 商品保真效果</t>
+        </is>
+      </c>
+      <c r="E14" s="46" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="F14" s="44" t="n"/>
+      <c r="G14" s="44" t="inlineStr">
+        <is>
+          <t>2026-10-28 用户：图生图暂无好方案，先放待办</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E5:E100">

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -1040,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="22" min="1" max="1"/>
@@ -1184,11 +1184,15 @@
         <v/>
       </c>
       <c r="K5" s="33">
-        <f>IF(J5=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A5,开发任务!$L$5:$L$200,"已完成")=J5,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A5,开发任务!$L$5:$L$200,"未开始")=J5,"未开始","进行中")))</f>
+        <f>IF(J5=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A5,开发任务!$L$5:$L$200,"暂缓")=J5,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A5,开发任务!$L$5:$L$200,"未开始")=J5,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A5,开发任务!$L$5:$L$200,"已完成")=J5,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A5,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A5,开发任务!$L$5:$L$200,"暂缓")=J5,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L5" s="44" t="n"/>
-      <c r="M5" s="44" t="n"/>
+      <c r="M5" s="44" t="inlineStr">
+        <is>
+          <t>A10（2026-10-28）：多机实测暂缓，等客户需求或 N08 环境；架构与代码支持保留</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="50.5" customHeight="1" s="23">
       <c r="A6" s="47" t="inlineStr">
@@ -1237,7 +1241,7 @@
         <v/>
       </c>
       <c r="K6" s="33">
-        <f>IF(J6=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A6,开发任务!$L$5:$L$200,"已完成")=J6,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A6,开发任务!$L$5:$L$200,"未开始")=J6,"未开始","进行中")))</f>
+        <f>IF(J6=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A6,开发任务!$L$5:$L$200,"暂缓")=J6,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A6,开发任务!$L$5:$L$200,"未开始")=J6,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A6,开发任务!$L$5:$L$200,"已完成")=J6,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A6,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A6,开发任务!$L$5:$L$200,"暂缓")=J6,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L6" s="44" t="n"/>
@@ -1294,7 +1298,7 @@
         <v/>
       </c>
       <c r="K7" s="33">
-        <f>IF(J7=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A7,开发任务!$L$5:$L$200,"已完成")=J7,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A7,开发任务!$L$5:$L$200,"未开始")=J7,"未开始","进行中")))</f>
+        <f>IF(J7=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A7,开发任务!$L$5:$L$200,"暂缓")=J7,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A7,开发任务!$L$5:$L$200,"未开始")=J7,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A7,开发任务!$L$5:$L$200,"已完成")=J7,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A7,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A7,开发任务!$L$5:$L$200,"暂缓")=J7,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L7" s="44" t="n"/>
@@ -1347,7 +1351,7 @@
         <v/>
       </c>
       <c r="K8" s="33">
-        <f>IF(J8=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A8,开发任务!$L$5:$L$200,"已完成")=J8,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A8,开发任务!$L$5:$L$200,"未开始")=J8,"未开始","进行中")))</f>
+        <f>IF(J8=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A8,开发任务!$L$5:$L$200,"暂缓")=J8,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A8,开发任务!$L$5:$L$200,"未开始")=J8,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A8,开发任务!$L$5:$L$200,"已完成")=J8,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A8,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A8,开发任务!$L$5:$L$200,"暂缓")=J8,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L8" s="44" t="n"/>
@@ -1404,7 +1408,7 @@
         <v/>
       </c>
       <c r="K9" s="33">
-        <f>IF(J9=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A9,开发任务!$L$5:$L$200,"已完成")=J9,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A9,开发任务!$L$5:$L$200,"未开始")=J9,"未开始","进行中")))</f>
+        <f>IF(J9=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A9,开发任务!$L$5:$L$200,"暂缓")=J9,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A9,开发任务!$L$5:$L$200,"未开始")=J9,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A9,开发任务!$L$5:$L$200,"已完成")=J9,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A9,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A9,开发任务!$L$5:$L$200,"暂缓")=J9,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L9" s="44" t="n"/>
@@ -1461,7 +1465,7 @@
         <v/>
       </c>
       <c r="K10" s="33">
-        <f>IF(J10=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A10,开发任务!$L$5:$L$200,"已完成")=J10,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A10,开发任务!$L$5:$L$200,"未开始")=J10,"未开始","进行中")))</f>
+        <f>IF(J10=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A10,开发任务!$L$5:$L$200,"暂缓")=J10,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A10,开发任务!$L$5:$L$200,"未开始")=J10,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A10,开发任务!$L$5:$L$200,"已完成")=J10,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A10,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A10,开发任务!$L$5:$L$200,"暂缓")=J10,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L10" s="44" t="n"/>
@@ -1514,7 +1518,7 @@
         <v/>
       </c>
       <c r="K11" s="33">
-        <f>IF(J11=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A11,开发任务!$L$5:$L$200,"已完成")=J11,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A11,开发任务!$L$5:$L$200,"未开始")=J11,"未开始","进行中")))</f>
+        <f>IF(J11=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A11,开发任务!$L$5:$L$200,"暂缓")=J11,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A11,开发任务!$L$5:$L$200,"未开始")=J11,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A11,开发任务!$L$5:$L$200,"已完成")=J11,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A11,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A11,开发任务!$L$5:$L$200,"暂缓")=J11,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L11" s="44" t="n"/>
@@ -1571,7 +1575,7 @@
         <v/>
       </c>
       <c r="K12" s="33">
-        <f>IF(J12=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A12,开发任务!$L$5:$L$200,"已完成")=J12,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A12,开发任务!$L$5:$L$200,"未开始")=J12,"未开始","进行中")))</f>
+        <f>IF(J12=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A12,开发任务!$L$5:$L$200,"暂缓")=J12,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A12,开发任务!$L$5:$L$200,"未开始")=J12,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A12,开发任务!$L$5:$L$200,"已完成")=J12,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A12,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A12,开发任务!$L$5:$L$200,"暂缓")=J12,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L12" s="44" t="n"/>
@@ -1628,7 +1632,7 @@
         <v/>
       </c>
       <c r="K13" s="33">
-        <f>IF(J13=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A13,开发任务!$L$5:$L$200,"已完成")=J13,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A13,开发任务!$L$5:$L$200,"未开始")=J13,"未开始","进行中")))</f>
+        <f>IF(J13=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A13,开发任务!$L$5:$L$200,"暂缓")=J13,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A13,开发任务!$L$5:$L$200,"未开始")=J13,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A13,开发任务!$L$5:$L$200,"已完成")=J13,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A13,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A13,开发任务!$L$5:$L$200,"暂缓")=J13,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L13" s="44" t="n"/>
@@ -1681,7 +1685,7 @@
         <v/>
       </c>
       <c r="K14" s="33">
-        <f>IF(J14=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A14,开发任务!$L$5:$L$200,"已完成")=J14,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A14,开发任务!$L$5:$L$200,"未开始")=J14,"未开始","进行中")))</f>
+        <f>IF(J14=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A14,开发任务!$L$5:$L$200,"暂缓")=J14,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A14,开发任务!$L$5:$L$200,"未开始")=J14,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A14,开发任务!$L$5:$L$200,"已完成")=J14,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A14,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A14,开发任务!$L$5:$L$200,"暂缓")=J14,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L14" s="44" t="n"/>
@@ -1738,7 +1742,7 @@
         <v/>
       </c>
       <c r="K15" s="33">
-        <f>IF(J15=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A15,开发任务!$L$5:$L$200,"已完成")=J15,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A15,开发任务!$L$5:$L$200,"未开始")=J15,"未开始","进行中")))</f>
+        <f>IF(J15=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A15,开发任务!$L$5:$L$200,"暂缓")=J15,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A15,开发任务!$L$5:$L$200,"未开始")=J15,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A15,开发任务!$L$5:$L$200,"已完成")=J15,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A15,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A15,开发任务!$L$5:$L$200,"暂缓")=J15,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L15" s="44" t="n"/>
@@ -1795,7 +1799,7 @@
         <v/>
       </c>
       <c r="K16" s="33">
-        <f>IF(J16=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A16,开发任务!$L$5:$L$200,"已完成")=J16,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A16,开发任务!$L$5:$L$200,"未开始")=J16,"未开始","进行中")))</f>
+        <f>IF(J16=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A16,开发任务!$L$5:$L$200,"暂缓")=J16,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A16,开发任务!$L$5:$L$200,"未开始")=J16,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A16,开发任务!$L$5:$L$200,"已完成")=J16,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A16,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A16,开发任务!$L$5:$L$200,"暂缓")=J16,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L16" s="44" t="n"/>
@@ -1852,7 +1856,7 @@
         <v/>
       </c>
       <c r="K17" s="33">
-        <f>IF(J17=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A17,开发任务!$L$5:$L$200,"已完成")=J17,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A17,开发任务!$L$5:$L$200,"未开始")=J17,"未开始","进行中")))</f>
+        <f>IF(J17=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A17,开发任务!$L$5:$L$200,"暂缓")=J17,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A17,开发任务!$L$5:$L$200,"未开始")=J17,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A17,开发任务!$L$5:$L$200,"已完成")=J17,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A17,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A17,开发任务!$L$5:$L$200,"暂缓")=J17,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L17" s="44" t="n"/>
@@ -1909,7 +1913,7 @@
         <v/>
       </c>
       <c r="K18" s="33">
-        <f>IF(J18=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A18,开发任务!$L$5:$L$200,"已完成")=J18,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A18,开发任务!$L$5:$L$200,"未开始")=J18,"未开始","进行中")))</f>
+        <f>IF(J18=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A18,开发任务!$L$5:$L$200,"暂缓")=J18,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A18,开发任务!$L$5:$L$200,"未开始")=J18,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A18,开发任务!$L$5:$L$200,"已完成")=J18,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A18,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A18,开发任务!$L$5:$L$200,"暂缓")=J18,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L18" s="44" t="n"/>
@@ -1966,7 +1970,7 @@
         <v/>
       </c>
       <c r="K19" s="33">
-        <f>IF(J19=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A19,开发任务!$L$5:$L$200,"已完成")=J19,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A19,开发任务!$L$5:$L$200,"未开始")=J19,"未开始","进行中")))</f>
+        <f>IF(J19=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A19,开发任务!$L$5:$L$200,"暂缓")=J19,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A19,开发任务!$L$5:$L$200,"未开始")=J19,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A19,开发任务!$L$5:$L$200,"已完成")=J19,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A19,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A19,开发任务!$L$5:$L$200,"暂缓")=J19,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L19" s="44" t="n"/>
@@ -2019,7 +2023,7 @@
         <v/>
       </c>
       <c r="K20" s="33">
-        <f>IF(J20=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A20,开发任务!$L$5:$L$200,"已完成")=J20,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A20,开发任务!$L$5:$L$200,"未开始")=J20,"未开始","进行中")))</f>
+        <f>IF(J20=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A20,开发任务!$L$5:$L$200,"暂缓")=J20,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A20,开发任务!$L$5:$L$200,"未开始")=J20,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A20,开发任务!$L$5:$L$200,"已完成")=J20,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A20,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A20,开发任务!$L$5:$L$200,"暂缓")=J20,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L20" s="44" t="n"/>
@@ -2072,7 +2076,7 @@
         <v/>
       </c>
       <c r="K21" s="33">
-        <f>IF(J21=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A21,开发任务!$L$5:$L$200,"已完成")=J21,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A21,开发任务!$L$5:$L$200,"未开始")=J21,"未开始","进行中")))</f>
+        <f>IF(J21=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A21,开发任务!$L$5:$L$200,"暂缓")=J21,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A21,开发任务!$L$5:$L$200,"未开始")=J21,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A21,开发任务!$L$5:$L$200,"已完成")=J21,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A21,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A21,开发任务!$L$5:$L$200,"暂缓")=J21,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L21" s="44" t="n"/>
@@ -2129,7 +2133,7 @@
         <v/>
       </c>
       <c r="K22" s="33">
-        <f>IF(J22=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A22,开发任务!$L$5:$L$200,"已完成")=J22,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A22,开发任务!$L$5:$L$200,"未开始")=J22,"未开始","进行中")))</f>
+        <f>IF(J22=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A22,开发任务!$L$5:$L$200,"暂缓")=J22,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A22,开发任务!$L$5:$L$200,"未开始")=J22,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A22,开发任务!$L$5:$L$200,"已完成")=J22,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A22,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A22,开发任务!$L$5:$L$200,"暂缓")=J22,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L22" s="44" t="n"/>
@@ -2186,7 +2190,7 @@
         <v/>
       </c>
       <c r="K23" s="33">
-        <f>IF(J23=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A23,开发任务!$L$5:$L$200,"已完成")=J23,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A23,开发任务!$L$5:$L$200,"未开始")=J23,"未开始","进行中")))</f>
+        <f>IF(J23=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A23,开发任务!$L$5:$L$200,"暂缓")=J23,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A23,开发任务!$L$5:$L$200,"未开始")=J23,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A23,开发任务!$L$5:$L$200,"已完成")=J23,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A23,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A23,开发任务!$L$5:$L$200,"暂缓")=J23,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L23" s="44" t="n"/>
@@ -2239,7 +2243,7 @@
         <v/>
       </c>
       <c r="K24" s="33">
-        <f>IF(J24=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A24,开发任务!$L$5:$L$200,"已完成")=J24,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A24,开发任务!$L$5:$L$200,"未开始")=J24,"未开始","进行中")))</f>
+        <f>IF(J24=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A24,开发任务!$L$5:$L$200,"暂缓")=J24,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A24,开发任务!$L$5:$L$200,"未开始")=J24,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A24,开发任务!$L$5:$L$200,"已完成")=J24,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A24,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A24,开发任务!$L$5:$L$200,"暂缓")=J24,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L24" s="44" t="n"/>
@@ -2296,7 +2300,7 @@
         <v/>
       </c>
       <c r="K25" s="33">
-        <f>IF(J25=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A25,开发任务!$L$5:$L$200,"已完成")=J25,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A25,开发任务!$L$5:$L$200,"未开始")=J25,"未开始","进行中")))</f>
+        <f>IF(J25=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A25,开发任务!$L$5:$L$200,"暂缓")=J25,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A25,开发任务!$L$5:$L$200,"未开始")=J25,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A25,开发任务!$L$5:$L$200,"已完成")=J25,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A25,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A25,开发任务!$L$5:$L$200,"暂缓")=J25,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L25" s="44" t="n"/>
@@ -2353,7 +2357,7 @@
         <v/>
       </c>
       <c r="K26" s="33">
-        <f>IF(J26=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A26,开发任务!$L$5:$L$200,"已完成")=J26,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A26,开发任务!$L$5:$L$200,"未开始")=J26,"未开始","进行中")))</f>
+        <f>IF(J26=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A26,开发任务!$L$5:$L$200,"暂缓")=J26,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A26,开发任务!$L$5:$L$200,"未开始")=J26,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A26,开发任务!$L$5:$L$200,"已完成")=J26,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A26,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A26,开发任务!$L$5:$L$200,"暂缓")=J26,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L26" s="44" t="n"/>
@@ -2410,7 +2414,7 @@
         <v/>
       </c>
       <c r="K27" s="33">
-        <f>IF(J27=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A27,开发任务!$L$5:$L$200,"已完成")=J27,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A27,开发任务!$L$5:$L$200,"未开始")=J27,"未开始","进行中")))</f>
+        <f>IF(J27=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A27,开发任务!$L$5:$L$200,"暂缓")=J27,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A27,开发任务!$L$5:$L$200,"未开始")=J27,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A27,开发任务!$L$5:$L$200,"已完成")=J27,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A27,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A27,开发任务!$L$5:$L$200,"暂缓")=J27,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L27" s="44" t="n"/>
@@ -2467,7 +2471,7 @@
         <v/>
       </c>
       <c r="K28" s="33">
-        <f>IF(J28=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A28,开发任务!$L$5:$L$200,"已完成")=J28,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A28,开发任务!$L$5:$L$200,"未开始")=J28,"未开始","进行中")))</f>
+        <f>IF(J28=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A28,开发任务!$L$5:$L$200,"暂缓")=J28,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A28,开发任务!$L$5:$L$200,"未开始")=J28,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A28,开发任务!$L$5:$L$200,"已完成")=J28,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A28,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A28,开发任务!$L$5:$L$200,"暂缓")=J28,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L28" s="44" t="n"/>
@@ -2520,7 +2524,7 @@
         <v/>
       </c>
       <c r="K29" s="33">
-        <f>IF(J29=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A29,开发任务!$L$5:$L$200,"已完成")=J29,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A29,开发任务!$L$5:$L$200,"未开始")=J29,"未开始","进行中")))</f>
+        <f>IF(J29=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A29,开发任务!$L$5:$L$200,"暂缓")=J29,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A29,开发任务!$L$5:$L$200,"未开始")=J29,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A29,开发任务!$L$5:$L$200,"已完成")=J29,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A29,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A29,开发任务!$L$5:$L$200,"暂缓")=J29,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L29" s="44" t="n"/>
@@ -2573,7 +2577,7 @@
         <v/>
       </c>
       <c r="K30" s="33">
-        <f>IF(J30=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A30,开发任务!$L$5:$L$200,"已完成")=J30,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A30,开发任务!$L$5:$L$200,"未开始")=J30,"未开始","进行中")))</f>
+        <f>IF(J30=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A30,开发任务!$L$5:$L$200,"暂缓")=J30,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A30,开发任务!$L$5:$L$200,"未开始")=J30,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A30,开发任务!$L$5:$L$200,"已完成")=J30,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A30,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A30,开发任务!$L$5:$L$200,"暂缓")=J30,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L30" s="44" t="n"/>
@@ -2626,7 +2630,7 @@
         <v/>
       </c>
       <c r="K31" s="33">
-        <f>IF(J31=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A31,开发任务!$L$5:$L$200,"已完成")=J31,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A31,开发任务!$L$5:$L$200,"未开始")=J31,"未开始","进行中")))</f>
+        <f>IF(J31=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A31,开发任务!$L$5:$L$200,"暂缓")=J31,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A31,开发任务!$L$5:$L$200,"未开始")=J31,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A31,开发任务!$L$5:$L$200,"已完成")=J31,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A31,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A31,开发任务!$L$5:$L$200,"暂缓")=J31,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L31" s="44" t="n"/>
@@ -2679,7 +2683,7 @@
         <v/>
       </c>
       <c r="K32" s="33">
-        <f>IF(J32=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A32,开发任务!$L$5:$L$200,"已完成")=J32,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A32,开发任务!$L$5:$L$200,"未开始")=J32,"未开始","进行中")))</f>
+        <f>IF(J32=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A32,开发任务!$L$5:$L$200,"暂缓")=J32,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A32,开发任务!$L$5:$L$200,"未开始")=J32,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A32,开发任务!$L$5:$L$200,"已完成")=J32,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A32,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A32,开发任务!$L$5:$L$200,"暂缓")=J32,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L32" s="44" t="n"/>
@@ -2732,7 +2736,7 @@
         <v/>
       </c>
       <c r="K33" s="33">
-        <f>IF(J33=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A33,开发任务!$L$5:$L$200,"已完成")=J33,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A33,开发任务!$L$5:$L$200,"未开始")=J33,"未开始","进行中")))</f>
+        <f>IF(J33=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A33,开发任务!$L$5:$L$200,"暂缓")=J33,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A33,开发任务!$L$5:$L$200,"未开始")=J33,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A33,开发任务!$L$5:$L$200,"已完成")=J33,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A33,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A33,开发任务!$L$5:$L$200,"暂缓")=J33,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L33" s="44" t="n"/>
@@ -2785,7 +2789,7 @@
         <v/>
       </c>
       <c r="K34" s="33">
-        <f>IF(J34=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A34,开发任务!$L$5:$L$200,"已完成")=J34,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A34,开发任务!$L$5:$L$200,"未开始")=J34,"未开始","进行中")))</f>
+        <f>IF(J34=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A34,开发任务!$L$5:$L$200,"暂缓")=J34,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A34,开发任务!$L$5:$L$200,"未开始")=J34,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A34,开发任务!$L$5:$L$200,"已完成")=J34,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A34,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A34,开发任务!$L$5:$L$200,"暂缓")=J34,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L34" s="44" t="n"/>
@@ -2838,7 +2842,7 @@
         <v/>
       </c>
       <c r="K35" s="33">
-        <f>IF(J35=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A35,开发任务!$L$5:$L$200,"已完成")=J35,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A35,开发任务!$L$5:$L$200,"未开始")=J35,"未开始","进行中")))</f>
+        <f>IF(J35=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A35,开发任务!$L$5:$L$200,"暂缓")=J35,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A35,开发任务!$L$5:$L$200,"未开始")=J35,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A35,开发任务!$L$5:$L$200,"已完成")=J35,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A35,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A35,开发任务!$L$5:$L$200,"暂缓")=J35,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L35" s="44" t="n"/>
@@ -2895,7 +2899,7 @@
         <v/>
       </c>
       <c r="K36" s="33">
-        <f>IF(J36=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A36,开发任务!$L$5:$L$200,"已完成")=J36,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A36,开发任务!$L$5:$L$200,"未开始")=J36,"未开始","进行中")))</f>
+        <f>IF(J36=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A36,开发任务!$L$5:$L$200,"暂缓")=J36,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A36,开发任务!$L$5:$L$200,"未开始")=J36,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A36,开发任务!$L$5:$L$200,"已完成")=J36,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A36,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A36,开发任务!$L$5:$L$200,"暂缓")=J36,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L36" s="44" t="n"/>
@@ -2948,7 +2952,7 @@
         <v/>
       </c>
       <c r="K37" s="33">
-        <f>IF(J37=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A37,开发任务!$L$5:$L$200,"已完成")=J37,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A37,开发任务!$L$5:$L$200,"未开始")=J37,"未开始","进行中")))</f>
+        <f>IF(J37=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A37,开发任务!$L$5:$L$200,"暂缓")=J37,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A37,开发任务!$L$5:$L$200,"未开始")=J37,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A37,开发任务!$L$5:$L$200,"已完成")=J37,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A37,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A37,开发任务!$L$5:$L$200,"暂缓")=J37,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L37" s="44" t="n"/>
@@ -3005,7 +3009,7 @@
         <v/>
       </c>
       <c r="K38" s="33">
-        <f>IF(J38=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A38,开发任务!$L$5:$L$200,"已完成")=J38,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A38,开发任务!$L$5:$L$200,"未开始")=J38,"未开始","进行中")))</f>
+        <f>IF(J38=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A38,开发任务!$L$5:$L$200,"暂缓")=J38,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A38,开发任务!$L$5:$L$200,"未开始")=J38,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A38,开发任务!$L$5:$L$200,"已完成")=J38,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A38,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A38,开发任务!$L$5:$L$200,"暂缓")=J38,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L38" s="44" t="n"/>
@@ -3058,7 +3062,7 @@
         <v/>
       </c>
       <c r="K39" s="33">
-        <f>IF(J39=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A39,开发任务!$L$5:$L$200,"已完成")=J39,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A39,开发任务!$L$5:$L$200,"未开始")=J39,"未开始","进行中")))</f>
+        <f>IF(J39=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A39,开发任务!$L$5:$L$200,"暂缓")=J39,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A39,开发任务!$L$5:$L$200,"未开始")=J39,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A39,开发任务!$L$5:$L$200,"已完成")=J39,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A39,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A39,开发任务!$L$5:$L$200,"暂缓")=J39,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L39" s="44" t="n"/>
@@ -3111,7 +3115,7 @@
         <v/>
       </c>
       <c r="K40" s="33">
-        <f>IF(J40=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A40,开发任务!$L$5:$L$200,"已完成")=J40,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A40,开发任务!$L$5:$L$200,"未开始")=J40,"未开始","进行中")))</f>
+        <f>IF(J40=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A40,开发任务!$L$5:$L$200,"暂缓")=J40,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A40,开发任务!$L$5:$L$200,"未开始")=J40,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A40,开发任务!$L$5:$L$200,"已完成")=J40,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A40,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A40,开发任务!$L$5:$L$200,"暂缓")=J40,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L40" s="44" t="n"/>
@@ -3164,7 +3168,7 @@
         <v/>
       </c>
       <c r="K41" s="33">
-        <f>IF(J41=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A41,开发任务!$L$5:$L$200,"已完成")=J41,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A41,开发任务!$L$5:$L$200,"未开始")=J41,"未开始","进行中")))</f>
+        <f>IF(J41=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A41,开发任务!$L$5:$L$200,"暂缓")=J41,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A41,开发任务!$L$5:$L$200,"未开始")=J41,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A41,开发任务!$L$5:$L$200,"已完成")=J41,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A41,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A41,开发任务!$L$5:$L$200,"暂缓")=J41,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L41" s="44" t="n"/>
@@ -3217,7 +3221,7 @@
         <v/>
       </c>
       <c r="K42" s="33">
-        <f>IF(J42=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A42,开发任务!$L$5:$L$200,"已完成")=J42,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A42,开发任务!$L$5:$L$200,"未开始")=J42,"未开始","进行中")))</f>
+        <f>IF(J42=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A42,开发任务!$L$5:$L$200,"暂缓")=J42,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A42,开发任务!$L$5:$L$200,"未开始")=J42,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A42,开发任务!$L$5:$L$200,"已完成")=J42,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A42,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A42,开发任务!$L$5:$L$200,"暂缓")=J42,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L42" s="44" t="n"/>
@@ -3270,7 +3274,7 @@
         <v/>
       </c>
       <c r="K43" s="33">
-        <f>IF(J43=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A43,开发任务!$L$5:$L$200,"已完成")=J43,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A43,开发任务!$L$5:$L$200,"未开始")=J43,"未开始","进行中")))</f>
+        <f>IF(J43=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A43,开发任务!$L$5:$L$200,"暂缓")=J43,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A43,开发任务!$L$5:$L$200,"未开始")=J43,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A43,开发任务!$L$5:$L$200,"已完成")=J43,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A43,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A43,开发任务!$L$5:$L$200,"暂缓")=J43,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L43" s="44" t="n"/>
@@ -3327,7 +3331,7 @@
         <v/>
       </c>
       <c r="K44" s="33">
-        <f>IF(J44=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A44,开发任务!$L$5:$L$200,"已完成")=J44,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A44,开发任务!$L$5:$L$200,"未开始")=J44,"未开始","进行中")))</f>
+        <f>IF(J44=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A44,开发任务!$L$5:$L$200,"暂缓")=J44,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A44,开发任务!$L$5:$L$200,"未开始")=J44,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A44,开发任务!$L$5:$L$200,"已完成")=J44,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A44,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A44,开发任务!$L$5:$L$200,"暂缓")=J44,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L44" s="44" t="n"/>
@@ -3380,7 +3384,7 @@
         <v/>
       </c>
       <c r="K45" s="33">
-        <f>IF(J45=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A45,开发任务!$L$5:$L$200,"已完成")=J45,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A45,开发任务!$L$5:$L$200,"未开始")=J45,"未开始","进行中")))</f>
+        <f>IF(J45=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A45,开发任务!$L$5:$L$200,"暂缓")=J45,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A45,开发任务!$L$5:$L$200,"未开始")=J45,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A45,开发任务!$L$5:$L$200,"已完成")=J45,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A45,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A45,开发任务!$L$5:$L$200,"暂缓")=J45,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L45" s="44" t="n"/>
@@ -3433,7 +3437,7 @@
         <v/>
       </c>
       <c r="K46" s="33">
-        <f>IF(J46=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A46,开发任务!$L$5:$L$200,"已完成")=J46,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A46,开发任务!$L$5:$L$200,"未开始")=J46,"未开始","进行中")))</f>
+        <f>IF(J46=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A46,开发任务!$L$5:$L$200,"暂缓")=J46,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A46,开发任务!$L$5:$L$200,"未开始")=J46,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A46,开发任务!$L$5:$L$200,"已完成")=J46,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A46,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A46,开发任务!$L$5:$L$200,"暂缓")=J46,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L46" s="44" t="n"/>
@@ -3486,7 +3490,7 @@
         <v/>
       </c>
       <c r="K47" s="33">
-        <f>IF(J47=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A47,开发任务!$L$5:$L$200,"已完成")=J47,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A47,开发任务!$L$5:$L$200,"未开始")=J47,"未开始","进行中")))</f>
+        <f>IF(J47=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A47,开发任务!$L$5:$L$200,"暂缓")=J47,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A47,开发任务!$L$5:$L$200,"未开始")=J47,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A47,开发任务!$L$5:$L$200,"已完成")=J47,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A47,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A47,开发任务!$L$5:$L$200,"暂缓")=J47,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L47" s="44" t="n"/>
@@ -3539,7 +3543,7 @@
         <v/>
       </c>
       <c r="K48" s="33">
-        <f>IF(J48=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A48,开发任务!$L$5:$L$200,"已完成")=J48,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A48,开发任务!$L$5:$L$200,"未开始")=J48,"未开始","进行中")))</f>
+        <f>IF(J48=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A48,开发任务!$L$5:$L$200,"暂缓")=J48,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A48,开发任务!$L$5:$L$200,"未开始")=J48,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A48,开发任务!$L$5:$L$200,"已完成")=J48,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A48,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A48,开发任务!$L$5:$L$200,"暂缓")=J48,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L48" s="44" t="n"/>
@@ -3592,7 +3596,7 @@
         <v/>
       </c>
       <c r="K49" s="33">
-        <f>IF(J49=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A49,开发任务!$L$5:$L$200,"已完成")=J49,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A49,开发任务!$L$5:$L$200,"未开始")=J49,"未开始","进行中")))</f>
+        <f>IF(J49=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A49,开发任务!$L$5:$L$200,"暂缓")=J49,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A49,开发任务!$L$5:$L$200,"未开始")=J49,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A49,开发任务!$L$5:$L$200,"已完成")=J49,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A49,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A49,开发任务!$L$5:$L$200,"暂缓")=J49,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L49" s="44" t="n"/>
@@ -3645,7 +3649,7 @@
         <v/>
       </c>
       <c r="K50" s="33">
-        <f>IF(J50=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A50,开发任务!$L$5:$L$200,"已完成")=J50,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A50,开发任务!$L$5:$L$200,"未开始")=J50,"未开始","进行中")))</f>
+        <f>IF(J50=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A50,开发任务!$L$5:$L$200,"暂缓")=J50,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A50,开发任务!$L$5:$L$200,"未开始")=J50,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A50,开发任务!$L$5:$L$200,"已完成")=J50,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A50,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A50,开发任务!$L$5:$L$200,"暂缓")=J50,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L50" s="44" t="n"/>
@@ -3698,7 +3702,7 @@
         <v/>
       </c>
       <c r="K51" s="33">
-        <f>IF(J51=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A51,开发任务!$L$5:$L$200,"已完成")=J51,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A51,开发任务!$L$5:$L$200,"未开始")=J51,"未开始","进行中")))</f>
+        <f>IF(J51=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A51,开发任务!$L$5:$L$200,"暂缓")=J51,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A51,开发任务!$L$5:$L$200,"未开始")=J51,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A51,开发任务!$L$5:$L$200,"已完成")=J51,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A51,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A51,开发任务!$L$5:$L$200,"暂缓")=J51,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L51" s="44" t="n"/>
@@ -3751,7 +3755,7 @@
         <v/>
       </c>
       <c r="K52" s="33">
-        <f>IF(J52=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A52,开发任务!$L$5:$L$200,"已完成")=J52,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A52,开发任务!$L$5:$L$200,"未开始")=J52,"未开始","进行中")))</f>
+        <f>IF(J52=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A52,开发任务!$L$5:$L$200,"暂缓")=J52,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A52,开发任务!$L$5:$L$200,"未开始")=J52,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A52,开发任务!$L$5:$L$200,"已完成")=J52,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A52,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A52,开发任务!$L$5:$L$200,"暂缓")=J52,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
       <c r="L52" s="44" t="n"/>
@@ -3808,7 +3812,7 @@
         <v/>
       </c>
       <c r="K53" s="22">
-        <f>IF(J53=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A53,开发任务!$L$5:$L$200,"已完成")=J53,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A53,开发任务!$L$5:$L$200,"未开始")=J53,"未开始","进行中")))</f>
+        <f>IF(J53=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A53,开发任务!$L$5:$L$200,"暂缓")=J53,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A53,开发任务!$L$5:$L$200,"未开始")=J53,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A53,开发任务!$L$5:$L$200,"已完成")=J53,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A53,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A53,开发任务!$L$5:$L$200,"暂缓")=J53,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
     </row>
@@ -3863,7 +3867,7 @@
         <v/>
       </c>
       <c r="K54" s="22">
-        <f>IF(J54=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A54,开发任务!$L$5:$L$200,"已完成")=J54,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A54,开发任务!$L$5:$L$200,"未开始")=J54,"未开始","进行中")))</f>
+        <f>IF(J54=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A54,开发任务!$L$5:$L$200,"暂缓")=J54,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A54,开发任务!$L$5:$L$200,"未开始")=J54,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A54,开发任务!$L$5:$L$200,"已完成")=J54,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A54,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A54,开发任务!$L$5:$L$200,"暂缓")=J54,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
     </row>
@@ -3918,7 +3922,7 @@
         <v/>
       </c>
       <c r="K55" s="22">
-        <f>IF(J55=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A55,开发任务!$L$5:$L$200,"已完成")=J55,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A55,开发任务!$L$5:$L$200,"未开始")=J55,"未开始","进行中")))</f>
+        <f>IF(J55=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A55,开发任务!$L$5:$L$200,"暂缓")=J55,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A55,开发任务!$L$5:$L$200,"未开始")=J55,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A55,开发任务!$L$5:$L$200,"已完成")=J55,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A55,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A55,开发任务!$L$5:$L$200,"暂缓")=J55,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
     </row>
@@ -3968,7 +3972,7 @@
         <v/>
       </c>
       <c r="K56" s="22">
-        <f>IF(J56=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A56,开发任务!$L$5:$L$200,"已完成")=J56,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A56,开发任务!$L$5:$L$200,"未开始")=J56,"未开始","进行中")))</f>
+        <f>IF(J56=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A56,开发任务!$L$5:$L$200,"暂缓")=J56,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A56,开发任务!$L$5:$L$200,"未开始")=J56,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A56,开发任务!$L$5:$L$200,"已完成")=J56,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A56,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A56,开发任务!$L$5:$L$200,"暂缓")=J56,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
     </row>
@@ -4023,7 +4027,7 @@
         <v/>
       </c>
       <c r="K57" s="22">
-        <f>IF(J57=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A57,开发任务!$L$5:$L$200,"已完成")=J57,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A57,开发任务!$L$5:$L$200,"未开始")=J57,"未开始","进行中")))</f>
+        <f>IF(J57=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A57,开发任务!$L$5:$L$200,"暂缓")=J57,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A57,开发任务!$L$5:$L$200,"未开始")=J57,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A57,开发任务!$L$5:$L$200,"已完成")=J57,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A57,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A57,开发任务!$L$5:$L$200,"暂缓")=J57,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
     </row>
@@ -4073,8 +4077,63 @@
         <v/>
       </c>
       <c r="K58" s="22">
-        <f>IF(J58=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A58,开发任务!$L$5:$L$200,"已完成")=J58,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A58,开发任务!$L$5:$L$200,"未开始")=J58,"未开始","进行中")))</f>
-        <v/>
+        <f>IF(J58=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A58,开发任务!$L$5:$L$200,"暂缓")=J58,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A58,开发任务!$L$5:$L$200,"未开始")=J58,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A58,开发任务!$L$5:$L$200,"已完成")=J58,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A58,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A58,开发任务!$L$5:$L$200,"暂缓")=J58,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="22" t="inlineStr">
+        <is>
+          <t>F58</t>
+        </is>
+      </c>
+      <c r="B59" s="22" t="inlineStr">
+        <is>
+          <t>后续：功能增强</t>
+        </is>
+      </c>
+      <c r="C59" s="22" t="inlineStr">
+        <is>
+          <t>平台预设槽位化</t>
+        </is>
+      </c>
+      <c r="D59" s="22" t="inlineStr">
+        <is>
+          <t>按槽位定义各平台图片规格：多槽位尺寸与比例、白底位置与张数、主体占比下限、单张大小上限（导出自动压缩）、禁用内容、AI 标识策略；套图按平台槽位组合模板；附 N06 规范核对清单</t>
+        </is>
+      </c>
+      <c r="E59" s="22" t="inlineStr">
+        <is>
+          <t>Templates/platforms.json；Studio/Export/；EcomTemplate.cs</t>
+        </is>
+      </c>
+      <c r="F59" s="22" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H59" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-28 平台差异讨论（与决策 A10 同期）</t>
+        </is>
+      </c>
+      <c r="I59" s="22" t="inlineStr">
+        <is>
+          <t>T60</t>
+        </is>
+      </c>
+      <c r="J59" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A59)</f>
+        <v/>
+      </c>
+      <c r="K59" s="22">
+        <f>IF(J59=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A59,开发任务!$L$5:$L$200,"暂缓")=J59,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A59,开发任务!$L$5:$L$200,"未开始")=J59,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A59,开发任务!$L$5:$L$200,"已完成")=J59,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A59,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A59,开发任务!$L$5:$L$200,"暂缓")=J59,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>设计稿见 docs/EcomCraft 平台预设槽位设计.zh-CN.md；规范数值待 N06 逐项核对官方最新规则后置 verified</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4331,17 +4390,13 @@
       </c>
       <c r="L6" s="46" t="inlineStr">
         <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="M6" s="38" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
+          <t>暂缓</t>
+        </is>
+      </c>
+      <c r="M6" s="38" t="n"/>
       <c r="N6" s="44" t="inlineStr">
         <is>
-          <t>静态审查完成；两台电脑实测与 V1–V3 结论待 N08 测试环境</t>
+          <t>静态审查完成。2026-10-28 决策 A10：单服务器先行，多机实测暂缓，等客户提出需求或 N08 环境就绪再启动（V1–V5 结论一并补）</t>
         </is>
       </c>
     </row>
@@ -8228,7 +8283,76 @@
         </is>
       </c>
     </row>
-    <row r="63"/>
+    <row r="63">
+      <c r="A63" s="22" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>T60</t>
+        </is>
+      </c>
+      <c r="C63" s="22" t="inlineStr">
+        <is>
+          <t>后续：功能增强</t>
+        </is>
+      </c>
+      <c r="D63" s="22" t="inlineStr">
+        <is>
+          <t>F58</t>
+        </is>
+      </c>
+      <c r="E63" s="22" t="inlineStr">
+        <is>
+          <t>平台预设槽位化：槽位 schema v3、套图槽位映射与导出压缩</t>
+        </is>
+      </c>
+      <c r="F63" s="22" t="inlineStr">
+        <is>
+          <t>Templates/platforms.json、ExportRules.cs、ExportService.cs、EcomTemplate.cs、simple.js、lang/en.js、Tests</t>
+        </is>
+      </c>
+      <c r="G63" s="22" t="inlineStr">
+        <is>
+          <t>T11；N06</t>
+        </is>
+      </c>
+      <c r="H63" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I63" s="22" t="inlineStr">
+        <is>
+          <t>选淘宝 / 京东等平台后套图按各自槽位组合（白底位置与张数、比例）；导出文件不超过槽位大小上限；主体占比与禁用内容作为提示；旧 platforms.json（v2）仍可读取；N06 核对后的预设可置 verified</t>
+        </is>
+      </c>
+      <c r="J63" s="22" t="inlineStr">
+        <is>
+          <t>C# 测试槽位解析与压缩上限；node 测试平台选择界面；中英文界面检查</t>
+        </is>
+      </c>
+      <c r="K63" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+设计以 docs/EcomCraft 平台预设槽位设计.zh-CN.md 为准，需求有变化先改该文档（中英文）。
+任务：实现平台预设槽位化（F58）：platforms.json 升级为多槽位结构（尺寸比例、白底位置与张数、主体占比、单张大小上限、禁用内容、AI 标识策略），套图按平台槽位组合模板，导出按槽位规格处理并按大小上限自动压缩；保持 v2 读取兼容；客户端仍只提交平台 ID。
+先进入计划模式列出改动文件、数据结构和风险，我确认后再实现。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L63" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="M63" s="22" t="n"/>
+      <c r="N63" s="22" t="inlineStr">
+        <is>
+          <t>设计稿已写（docs/EcomCraft 平台预设槽位设计.zh-CN.md）；先确认方案再动代码</t>
+        </is>
+      </c>
+    </row>
     <row r="64">
       <c r="A64" s="40" t="inlineStr">
         <is>
@@ -8263,7 +8387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="22" min="1" max="1"/>
@@ -8509,7 +8633,11 @@
         </is>
       </c>
       <c r="F10" s="44" t="n"/>
-      <c r="G10" s="44" t="n"/>
+      <c r="G10" s="44" t="inlineStr">
+        <is>
+          <t>核对清单见 docs/EcomCraft 平台预设槽位设计.zh-CN.md 第 4 节（F58 落地前完成）</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="35" customHeight="1" s="23">
       <c r="A11" s="47" t="inlineStr">
@@ -8563,11 +8691,15 @@
       </c>
       <c r="E12" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>暂缓</t>
         </is>
       </c>
       <c r="F12" s="44" t="n"/>
-      <c r="G12" s="44" t="n"/>
+      <c r="G12" s="44" t="inlineStr">
+        <is>
+          <t>2026-10-28 决策 A10：单服务器先行，测试环境暂缓，等客户提出多服务器需求再准备</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="35" customHeight="1" s="23">
       <c r="A13" s="47" t="inlineStr">
@@ -8631,6 +8763,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
   </sheetData>
   <conditionalFormatting sqref="E5:E100">
     <cfRule type="expression" priority="1" dxfId="7">

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -4130,9 +4130,9 @@
         <f>IF(J59=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A59,开发任务!$L$5:$L$200,"暂缓")=J59,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A59,开发任务!$L$5:$L$200,"未开始")=J59,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A59,开发任务!$L$5:$L$200,"已完成")=J59,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A59,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A59,开发任务!$L$5:$L$200,"暂缓")=J59,"已完成（暂缓）","进行中")))))</f>
         <v/>
       </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>设计稿见 docs/EcomCraft 平台预设槽位设计.zh-CN.md；规范数值待 N06 逐项核对官方最新规则后置 verified</t>
+      <c r="M59" s="22" t="inlineStr">
+        <is>
+          <t>设计方案已确认（2026-10-28，见 docs/EcomCraft 平台预设槽位设计.zh-CN.md 第 6 节）；规范数值待 N06 逐项核对官方最新规则后置 verified</t>
         </is>
       </c>
     </row>
@@ -8349,7 +8349,7 @@
       <c r="M63" s="22" t="n"/>
       <c r="N63" s="22" t="inlineStr">
         <is>
-          <t>设计稿已写（docs/EcomCraft 平台预设槽位设计.zh-CN.md）；先确认方案再动代码</t>
+          <t>设计已确认（2026-10-28：占比仅导出提示、压缩超限继续导出并说明、视频封面只记录规格、品类规则等 N09，见设计文档第 6 节）；规范数值待 N06 核对；T60 可开发</t>
         </is>
       </c>
     </row>
@@ -8387,7 +8387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="22" min="1" max="1"/>
@@ -8763,7 +8763,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
   </sheetData>
   <conditionalFormatting sqref="E5:E100">
     <cfRule type="expression" priority="1" dxfId="7">

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -8343,13 +8343,17 @@
       </c>
       <c r="L63" s="22" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M63" s="22" t="n"/>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="M63" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N63" s="22" t="inlineStr">
         <is>
-          <t>设计已确认（2026-10-28：占比仅导出提示、压缩超限继续导出并说明、视频封面只记录规格、品类规则等 N09，见设计文档第 6 节）；规范数值待 N06 核对；T60 可开发</t>
+          <t>代码完成：159 项 C# 测试与 node 测试全部通过；待重启部署后浏览器人工验收（中英文各一遍）；规范数值待 N06 核对；同类型可选槽位不重复生成，只作额外导出目标</t>
         </is>
       </c>
     </row>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -1040,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="22" min="1" max="1"/>
@@ -4133,6 +4133,66 @@
       <c r="M59" s="22" t="inlineStr">
         <is>
           <t>设计方案已确认（2026-10-28，见 docs/EcomCraft 平台预设槽位设计.zh-CN.md 第 6 节）；规范数值待 N06 逐项核对官方最新规则后置 verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>F59</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>后续：功能增强</t>
+        </is>
+      </c>
+      <c r="C60" s="22" t="inlineStr">
+        <is>
+          <t>参考图（一张参考出一张图）</t>
+        </is>
+      </c>
+      <c r="D60" s="22" t="inlineStr">
+        <is>
+          <t>上传多张参考图（如竞品成品图，最多 8 张），每张参考一对一生成对应效果图：默认“借鉴构图”（视觉模型读图并入该任务提示词），可选“画面参考”（图生图，需另装模型）；只还原感觉不复刻；与分镜互斥；参考图临时使用不落盘</t>
+        </is>
+      </c>
+      <c r="E60" s="22" t="inlineStr">
+        <is>
+          <t>Studio/simple.js；Prompting/PromptService.cs；Generation/BatchService.cs；MagicPrompt；EcomTemplate.cs</t>
+        </is>
+      </c>
+      <c r="F60" s="22" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G60" s="22" t="inlineStr">
+        <is>
+          <t>运营友好</t>
+        </is>
+      </c>
+      <c r="H60" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-28 需求讨论（决策 A11）</t>
+        </is>
+      </c>
+      <c r="I60" s="22" t="inlineStr">
+        <is>
+          <t>T61、T62</t>
+        </is>
+      </c>
+      <c r="J60" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A60)</f>
+        <v/>
+      </c>
+      <c r="K60" s="22">
+        <f>IF(J60=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A60,开发任务!$L$5:$L$200,"暂缓")=J60,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A60,开发任务!$L$5:$L$200,"未开始")=J60,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A60,开发任务!$L$5:$L$200,"已完成")=J60,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A60,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A60,开发任务!$L$5:$L$200,"暂缓")=J60,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M60" s="22" t="inlineStr">
+        <is>
+          <t>需求见 docs/EcomCraft 参考图需求.zh-CN.md；P2（T62）依赖 N10</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:N66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="22" min="1" max="1"/>
@@ -8358,7 +8418,143 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="40" t="inlineStr">
+      <c r="A64" s="22" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="22" t="inlineStr">
+        <is>
+          <t>T61</t>
+        </is>
+      </c>
+      <c r="C64" s="22" t="inlineStr">
+        <is>
+          <t>后续：功能增强</t>
+        </is>
+      </c>
+      <c r="D64" s="22" t="inlineStr">
+        <is>
+          <t>F59</t>
+        </is>
+      </c>
+      <c r="E64" s="22" t="inlineStr">
+        <is>
+          <t>参考图 P1：上传与“一张参考出一张图”（借鉴构图）</t>
+        </is>
+      </c>
+      <c r="F64" s="22" t="inlineStr">
+        <is>
+          <t>Studio/simple.js、index.html、lang/en.js、Prompting/PromptService.cs、StudioApi.cs、Generation/BatchService.cs、Tests</t>
+        </is>
+      </c>
+      <c r="G64" s="22" t="inlineStr">
+        <is>
+          <t>T56；T58</t>
+        </is>
+      </c>
+      <c r="H64" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I64" s="22" t="inlineStr">
+        <is>
+          <t>上传 1–8 张参考图（第 9 张拒绝并提示）；单次与套图按 商品 × 参考 展开任务并受 20 张总上限；与分镜互斥（同时使用提示二选一）；任务卡片显示对应参考缩略图与实际提示词；vision 未开启时提示原因且不阻断出图；参考图不落盘、重启不留痕；海外平台加强版权提示；中英文界面完整</t>
+        </is>
+      </c>
+      <c r="J64" s="22" t="inlineStr">
+        <is>
+          <t>node --test studio-i18n / simple-mode；C# 展开与校验测试；浏览器中英文人工验收</t>
+        </is>
+      </c>
+      <c r="K64" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+参考图需求以 docs/EcomCraft 参考图需求.zh-CN.md 为准，需求有变化先改该文档（中英文）。
+任务：实现参考图 P1（F59）：第 2 步参考图上传（最多 8 张、客户端压缩、版权与海外平台提示）；EcomCraftStudioGenerate / GenerateSet 接受 reference_images 与 reference_mode，按一张参考一个任务展开（套图走商品×参考，与 shots 互斥返回 invalid_parameters）；借鉴构图由后台逐任务读图并入提示词（F56 流程，vision 关闭时跳过并提示）；任务带 reference_index；参考图只存内存批次，不写入 Data/。先进入计划模式列出改动文件、数据结构和风险，我确认后再实现。完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档（含 AGENTS.md 参考图规则），并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L64" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="M64" s="22" t="n"/>
+      <c r="N64" s="22" t="inlineStr">
+        <is>
+          <t>需求第 4、5、9 节；实现时在 AGENTS.md 补参考图规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>T62</t>
+        </is>
+      </c>
+      <c r="C65" s="22" t="inlineStr">
+        <is>
+          <t>后续：功能增强</t>
+        </is>
+      </c>
+      <c r="D65" s="22" t="inlineStr">
+        <is>
+          <t>F59</t>
+        </is>
+      </c>
+      <c r="E65" s="22" t="inlineStr">
+        <is>
+          <t>参考图 P2：画面参考（图生图）</t>
+        </is>
+      </c>
+      <c r="F65" s="22" t="inlineStr">
+        <is>
+          <t>Templates/（reference 槽位）、EcomTemplate.cs、TemplateValidator、图生图模板（N02 / F57 扩展）、Tests</t>
+        </is>
+      </c>
+      <c r="G65" s="22" t="inlineStr">
+        <is>
+          <t>N10；T61</t>
+        </is>
+      </c>
+      <c r="H65" s="22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I65" s="22" t="inlineStr">
+        <is>
+          <t>模板声明 reference 图片槽位并通过校验（不与品牌槽位同参数）；每个任务把自己的参考图填入图生图输入；缺图生图模型时模板隐藏、选项置灰并说明原因；重绘幅度由模板固化在偏低区间</t>
+        </is>
+      </c>
+      <c r="J65" s="22" t="inlineStr">
+        <is>
+          <t>C# 槽位校验测试；真机图生图生成验证（依赖 N10 模型安装）</t>
+        </is>
+      </c>
+      <c r="K65" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+参考图需求以 docs/EcomCraft 参考图需求.zh-CN.md 为准，需求有变化先改该文档（中英文）。
+任务：实现参考图 P2（F59）：模板新增 reference 槽位声明（指向快照图片参数、不与 brand_kit 槽位重复，模板校验）；生成时每个任务把自己的参考图填入对应参数（服务端填参，白名单不变）；界面“画面参考”选项按模板槽位与模型依赖（F08）决定可用性；配套图生图模板由 N02 专家制作或 F57 生成器扩展。先进入计划模式列出改动文件、数据结构和风险，我确认后再实现。完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L65" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="M65" s="22" t="n"/>
+      <c r="N65" s="22" t="inlineStr">
+        <is>
+          <t>依赖 N10（图生图方案未定）；工作流需 N02 或 F57 扩展</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="40" t="inlineStr">
         <is>
           <t>规模：S 约半天以内，M 约 1–2 天，L 3 天以上（含你的验证时间，仅供粗略估计）。原 T03、T26 已分别并入 T13、T34。</t>
         </is>
@@ -8752,7 +8948,7 @@
       </c>
       <c r="D14" s="42" t="inlineStr">
         <is>
-          <t>T59 后续、T07 商品保真效果</t>
+          <t>T59 后续、T07 商品保真效果、T62</t>
         </is>
       </c>
       <c r="E14" s="46" t="inlineStr">

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D60" s="22" t="inlineStr">
         <is>
-          <t>上传多张参考图（如竞品成品图，最多 8 张），每张参考一对一生成对应效果图：默认“借鉴构图”（视觉模型读图并入该任务提示词），可选“画面参考”（图生图，需另装模型）；只还原感觉不复刻；与分镜互斥；参考图临时使用不落盘</t>
+          <t>上传多张参考图（如竞品成品图，最多 8 张）进入独立参考模式：图片类型、视觉风格、需要模特、品牌资料包、一句话描述、候选张数和卖点分镜均不生效；逐张展示可编辑提示词（视觉模型生成，英文可改、以改稿为准）；每张参考固定出 1 张；画面参考（图生图）为 P2，需另装模型；只还原感觉不复刻；参考图临时使用不落盘</t>
         </is>
       </c>
       <c r="E60" s="22" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="E64" s="22" t="inlineStr">
         <is>
-          <t>参考图 P1：上传与“一张参考出一张图”（借鉴构图）</t>
+          <t>参考图 P1：独立参考模式（上传、逐张可编辑提示词、按参考出图）</t>
         </is>
       </c>
       <c r="F64" s="22" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="I64" s="22" t="inlineStr">
         <is>
-          <t>上传 1–8 张参考图（第 9 张拒绝并提示）；单次与套图按 商品 × 参考 展开任务并受 20 张总上限；与分镜互斥（同时使用提示二选一）；任务卡片显示对应参考缩略图与实际提示词；vision 未开启时提示原因且不阻断出图；参考图不落盘、重启不留痕；海外平台加强版权提示；中英文界面完整</t>
+          <t>上传 1–8 张参考图（第 9 张拒绝并提示）即进入参考模式：图片类型、视觉风格、模特、品牌资料包、描述、候选张数、分镜停用并标注；每张参考的英文提示词可编辑且以改稿为准（任务卡片 prompt_used 可查）；按 商品 × 参考 每张出 1 张并受 20 张上限；与 shots 互斥；vision 未开启时参考模式不可用、普通出图不受影响；任务卡片显示参考缩略图；参考图不落盘、重启不留痕；海外平台加强版权提示；中英文界面完整</t>
         </is>
       </c>
       <c r="J64" s="22" t="inlineStr">
@@ -8469,8 +8469,8 @@
       <c r="K64" s="22" t="inlineStr">
         <is>
           <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
-参考图需求以 docs/EcomCraft 参考图需求.zh-CN.md 为准，需求有变化先改该文档（中英文）。
-任务：实现参考图 P1（F59）：第 2 步参考图上传（最多 8 张、客户端压缩、版权与海外平台提示）；EcomCraftStudioGenerate / GenerateSet 接受 reference_images 与 reference_mode，按一张参考一个任务展开（套图走商品×参考，与 shots 互斥返回 invalid_parameters）；借鉴构图由后台逐任务读图并入提示词（F56 流程，vision 关闭时跳过并提示）；任务带 reference_index；参考图只存内存批次，不写入 Data/。先进入计划模式列出改动文件、数据结构和风险，我确认后再实现。完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档（含 AGENTS.md 参考图规则），并列出改动文件和你做过的验证。</t>
+参考图需求以 docs/EcomCraft 参考图需求.zh-CN.md 为准（v1.2 独立参考模式），需求有变化先改该文档（中英文）。
+任务：实现参考图 P1（F59）：第 2 步参考图上传（最多 8 张、客户端压缩、版权与海外平台提示），上传后其余第 2 步选项停用；新增 EcomCraftStudioReferenceDescribe 逐张生成英文构图描述与中文译文；界面逐张展示提示词（英文可编辑、中文只读）；EcomCraftStudioGenerateSet 参考模式按 商品 × 参考 每张出 1 张（固定保真场景模板、reference_prompts 逐张必填并清理、与 shots 互斥返回 invalid_parameters、20 张上限）；任务带 reference_index；参考图只存内存批次，不写入 Data/。先进入计划模式列出改动文件、数据结构和风险，我确认后再实现。完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档（含 AGENTS.md 参考图规则），并列出改动文件和你做过的验证。</t>
         </is>
       </c>
       <c r="L64" s="22" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="E65" s="22" t="inlineStr">
         <is>
-          <t>参考图 P2：画面参考（图生图）</t>
+          <t>参考图 P2：画面参考（参考模式改用图生图工作流）</t>
         </is>
       </c>
       <c r="F65" s="22" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="I65" s="22" t="inlineStr">
         <is>
-          <t>模板声明 reference 图片槽位并通过校验（不与品牌槽位同参数）；每个任务把自己的参考图填入图生图输入；缺图生图模型时模板隐藏、选项置灰并说明原因；重绘幅度由模板固化在偏低区间</t>
+          <t>参考模式下改用图生图：模板声明 reference 图片槽位并通过校验（不与品牌槽位同参数）；每个任务把自己的参考图填入图生图输入；缺图生图模型时选项置灰并说明原因；重绘幅度由模板固化在偏低区间</t>
         </is>
       </c>
       <c r="J65" s="22" t="inlineStr">

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -8475,13 +8475,17 @@
       </c>
       <c r="L64" s="22" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M64" s="22" t="n"/>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="M64" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="N64" s="22" t="inlineStr">
         <is>
-          <t>需求第 4、5、9 节；实现时在 AGENTS.md 补参考图规则</t>
+          <t>P1 代码完成：160 项 C# 测试与 35 项 node 测试全部通过；待重启部署后浏览器人工验收（含 vision 开启实测）；参考任务提示词按原文发送（raw_prompt 不带模板前后缀）；AGENTS.md 已补参考图规则</t>
         </is>
       </c>
     </row>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -8485,7 +8485,7 @@
       </c>
       <c r="N64" s="22" t="inlineStr">
         <is>
-          <t>P1 代码完成：160 项 C# 测试与 35 项 node 测试全部通过；待重启部署后浏览器人工验收（含 vision 开启实测）；参考任务提示词按原文发送（raw_prompt 不带模板前后缀）；AGENTS.md 已补参考图规则</t>
+          <t>P1 代码完成：160 项 C# 测试与 35 项 node 测试全部通过；待重启部署后浏览器人工验收（含 vision 开启实测）；参考任务提示词按原文发送（raw_prompt 不带模板前后缀）；AGENTS.md 已补参考图规则；验收中发现看图描述无前端开关，已在提示词优化设置弹窗补上（勾选后保存即调 EcomCraftPromptSettings，显示当前视觉模型），并补齐提示词指南英文版</t>
         </is>
       </c>
     </row>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -1040,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="22" min="1" max="1"/>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="D45" s="40" t="inlineStr">
         <is>
-          <t>在已有 EcomCraft 权限上预置管理员、设计师、运营、审核等角色</t>
+          <t>不做（决策 A12）：按软件销售、按账号数收费，不做复杂角色与权限；账号只分管理员和普通账号。原计划：预置管理员、设计师、运营、审核等角色</t>
         </is>
       </c>
       <c r="E45" s="40" t="inlineStr">
@@ -3388,7 +3388,11 @@
         <v/>
       </c>
       <c r="L45" s="44" t="n"/>
-      <c r="M45" s="44" t="n"/>
+      <c r="M45" s="44" t="inlineStr">
+        <is>
+          <t>2026-10-29 决策 A12 取消；T23 暂缓</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="35" customHeight="1" s="23">
       <c r="A46" s="47" t="inlineStr">
@@ -3413,7 +3417,7 @@
       </c>
       <c r="E46" s="40" t="inlineStr">
         <is>
-          <t>依赖 F11</t>
+          <t>原依赖 F11（已按 A12 取消）；如做，审核人由管理员担任</t>
         </is>
       </c>
       <c r="F46" s="33" t="inlineStr">
@@ -3615,12 +3619,12 @@
       </c>
       <c r="C50" s="40" t="inlineStr">
         <is>
-          <t>付费功能授权机制</t>
+          <t>按账号数授权</t>
         </is>
       </c>
       <c r="D50" s="40" t="inlineStr">
         <is>
-          <t>许可证密钥或独立闭源扩展，与开源核心分开</t>
+          <t>按软件销售、按账号数收费（A12）：离线可校验的许可证限制可创建的账号数量，不按功能分级</t>
         </is>
       </c>
       <c r="E50" s="40" t="inlineStr">
@@ -3653,7 +3657,11 @@
         <v/>
       </c>
       <c r="L50" s="44" t="n"/>
-      <c r="M50" s="44" t="n"/>
+      <c r="M50" s="44" t="inlineStr">
+        <is>
+          <t>2026-10-29 按决策 A12 改为按账号数授权</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="50.5" customHeight="1" s="23">
       <c r="A51" s="47" t="inlineStr">
@@ -4136,7 +4144,7 @@
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="60" s="23">
       <c r="A60" s="22" t="inlineStr">
         <is>
           <t>F59</t>
@@ -4195,6 +4203,62 @@
           <t>需求见 docs/EcomCraft 参考图需求.zh-CN.md；P2（T62）依赖 N10</t>
         </is>
       </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="inlineStr">
+        <is>
+          <t>F60</t>
+        </is>
+      </c>
+      <c r="B61" s="22" t="inlineStr">
+        <is>
+          <t>后续：功能增强</t>
+        </is>
+      </c>
+      <c r="C61" s="22" t="inlineStr">
+        <is>
+          <t>专业模式向所有账号开放</t>
+        </is>
+      </c>
+      <c r="D61" s="22" t="inlineStr">
+        <is>
+          <t>平面设计人员用专业模式调整模型、采样器、LoRA、步数等参数（决策 A2）：任何账号都可以从导航切换到专业模式，默认仍进入简易模式；管理视图仍只对管理员可见</t>
+        </is>
+      </c>
+      <c r="E61" s="22" t="inlineStr">
+        <is>
+          <t>Studio/studio.js；Studio/simple.js；StudioApi.cs</t>
+        </is>
+      </c>
+      <c r="F61" s="22" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G61" s="22" t="inlineStr">
+        <is>
+          <t>设计友好</t>
+        </is>
+      </c>
+      <c r="H61" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-29 目标用户讨论（决策 A2、A12）</t>
+        </is>
+      </c>
+      <c r="I61" s="22" t="inlineStr">
+        <is>
+          <t>T63</t>
+        </is>
+      </c>
+      <c r="J61" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A61)</f>
+        <v/>
+      </c>
+      <c r="K61" s="22">
+        <f>IF(J61=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A61,开发任务!$L$5:$L$200,"暂缓")=J61,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A61,开发任务!$L$5:$L$200,"未开始")=J61,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A61,开发任务!$L$5:$L$200,"已完成")=J61,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A61,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A61,开发任务!$L$5:$L$200,"暂缓")=J61,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M61" s="22" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:M31"/>
@@ -4218,7 +4282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N66"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="22" min="1" max="1"/>
@@ -7436,11 +7500,15 @@
       </c>
       <c r="L49" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>暂缓</t>
         </is>
       </c>
       <c r="M49" s="38" t="n"/>
-      <c r="N49" s="44" t="n"/>
+      <c r="N49" s="44" t="inlineStr">
+        <is>
+          <t>2026-10-29 决策 A12：不做复杂角色与权限，账号只分管理员和普通账号；本任务不再开发</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="221" customHeight="1" s="23">
       <c r="A50" s="47" t="n">
@@ -7725,17 +7793,17 @@
       </c>
       <c r="E54" s="40" t="inlineStr">
         <is>
-          <t>付费功能授权机制</t>
+          <t>按账号数授权</t>
         </is>
       </c>
       <c r="F54" s="42" t="inlineStr">
         <is>
-          <t>新增授权模块或独立闭源扩展</t>
+          <t>新增授权模块；src/Accounts（创建账号处校验）</t>
         </is>
       </c>
       <c r="G54" s="42" t="inlineStr">
         <is>
-          <t>T23</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H54" s="47" t="inlineStr">
@@ -7745,18 +7813,18 @@
       </c>
       <c r="I54" s="42" t="inlineStr">
         <is>
-          <t>付费功能在没有有效许可证时不可用并有明确提示；开源核心可独立运行</t>
+          <t>没有有效许可证或账号数已达上限时不能再创建普通账号，并有明确提示；已有账号与全部功能照常使用，不按功能分级；许可证离线可校验</t>
         </is>
       </c>
       <c r="J54" s="40" t="inlineStr">
         <is>
-          <t>C# 测试许可证校验（离线签名）</t>
+          <t>C# 测试许可证校验（离线签名）与账号数上限</t>
         </is>
       </c>
       <c r="K54" s="40" t="inlineStr">
         <is>
           <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
-任务：设计开源核心 + 付费团队版的拆分方式：比较“独立闭源扩展”与“许可证密钥开关”两种方案的利弊，推荐一种并实现离线可校验的许可证机制。开源核心必须能在没有付费部分的情况下完整运行。
+任务：实现按账号数授权（决策 A12：按软件销售、按账号数收费，不做复杂角色与权限，不按功能分级）。设计离线可校验的许可证（签名、授权账号数、有效期），在创建账号时校验账号数上限；超限时给出白话提示，不影响已有账号和功能。
 请先进入计划模式给出设计方案（改哪些文件、数据结构、接口、风险），我确认后再实现。
 完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
         </is>
@@ -7767,7 +7835,11 @@
         </is>
       </c>
       <c r="M54" s="38" t="n"/>
-      <c r="N54" s="44" t="n"/>
+      <c r="N54" s="44" t="inlineStr">
+        <is>
+          <t>2026-10-29 按决策 A12 改为按账号数授权，不再依赖 T23</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="298.5" customHeight="1" s="23">
       <c r="A55" s="47" t="n">
@@ -8489,7 +8561,7 @@
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" s="23">
       <c r="A65" s="22" t="n">
         <v>61</v>
       </c>
@@ -8558,7 +8630,76 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="40" t="inlineStr">
+      <c r="A66" s="22" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="22" t="inlineStr">
+        <is>
+          <t>T63</t>
+        </is>
+      </c>
+      <c r="C66" s="22" t="inlineStr">
+        <is>
+          <t>后续：功能增强</t>
+        </is>
+      </c>
+      <c r="D66" s="22" t="inlineStr">
+        <is>
+          <t>F60</t>
+        </is>
+      </c>
+      <c r="E66" s="22" t="inlineStr">
+        <is>
+          <t>专业模式向所有账号开放</t>
+        </is>
+      </c>
+      <c r="F66" s="22" t="inlineStr">
+        <is>
+          <t>Studio/studio.js、Studio/simple.js、StudioApi.cs（专业模式用到的接口权限）、Tests/simple-mode.test.cjs</t>
+        </is>
+      </c>
+      <c r="G66" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I66" s="22" t="inlineStr">
+        <is>
+          <t>普通账号导航出现“专业模式”并能打开 #create 正常出图；默认仍进入简易模式；简易模式仍没有专业参数；专业模式生成仍只走已登记执行服务器和服务端校验；审核、服务器、存储、设置向导等管理视图仍只对管理员可见</t>
+        </is>
+      </c>
+      <c r="J66" s="22" t="inlineStr">
+        <is>
+          <t>node --test studio-i18n / simple-mode；普通账号与管理员账号各登录一次手动验证</t>
+        </is>
+      </c>
+      <c r="K66" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+任务：按决策 A2 把专业模式开放给所有账号（平面设计人员在专业模式里调整模型、采样器、LoRA、步数等参数）。去掉 studio.js / simple.js 里“专业模式只给管理员”的前端限制，核对专业模式用到的 SwarmUI 与 EcomCraft 接口对普通账号的权限是否足够，只放开出图所需的权限，不放开服务器设置、后端管理等管理员功能。同步 README（中英文）、工作台界面设计文档（中英文）和 ecomcraft-studio-ui 技能。
+请先进入计划模式给出设计方案（改哪些文件、权限变化、风险），我确认后再实现。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L66" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="M66" s="22" t="n"/>
+      <c r="N66" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-29 新增（决策 A2、A12）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="40" t="inlineStr">
         <is>
           <t>规模：S 约半天以内，M 约 1–2 天，L 3 天以上（含你的验证时间，仅供粗略估计）。原 T03、T26 已分别并入 T13、T34。</t>
         </is>
@@ -10335,7 +10476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="22" min="1" max="1"/>
@@ -10384,7 +10525,7 @@
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>前期靠部署服务和团队版授权收费；将来云端额度先用团队预算和每人额度管理</t>
+          <t>按软件销售、按账号数收费（A12）；将来云端额度先用团队预算和每人额度管理</t>
         </is>
       </c>
     </row>
@@ -10433,6 +10574,18 @@
       <c r="B10" s="40" t="inlineStr">
         <is>
           <t>当前不考虑；改为 MVP 发布后找种子团队试用（N07）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="19.5" customHeight="1" s="23">
+      <c r="A11" s="40" t="inlineStr">
+        <is>
+          <t>复杂的角色与权限体系、按功能分级收费</t>
+        </is>
+      </c>
+      <c r="B11" s="40" t="inlineStr">
+        <is>
+          <t>按账号数收费即可（A12）；账号只分管理员和普通账号，任何账号都可用专业模式（A2）</t>
         </is>
       </c>
     </row>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -1040,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="22" min="1" max="1"/>
@@ -4204,7 +4204,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" s="23">
       <c r="A61" s="22" t="inlineStr">
         <is>
           <t>F60</t>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>后续：功能增强</t>
+          <t>改版：界面 v4</t>
         </is>
       </c>
       <c r="C61" s="22" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
-          <t>平面设计人员用专业模式调整模型、采样器、LoRA、步数等参数（决策 A2）：任何账号都可以从导航切换到专业模式，默认仍进入简易模式；管理视图仍只对管理员可见</t>
+          <t>平面设计人员用专业模式调整模型、采样器、LoRA、步数等参数（决策 A2）：任何账号都可以从导航切换到专业模式，默认仍进入简易模式；管理视图仍只对管理员可见；设计师可在专业模式里上传 ComfyUI 工作流 JSON，进入工作流审核，管理员发布后才能用（决策 A13）</t>
         </is>
       </c>
       <c r="E61" s="22" t="inlineStr">
@@ -4259,6 +4259,414 @@
         <v/>
       </c>
       <c r="M61" s="22" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>F61</t>
+        </is>
+      </c>
+      <c r="B62" s="22" t="inlineStr">
+        <is>
+          <t>改版：界面 v4</t>
+        </is>
+      </c>
+      <c r="C62" s="22" t="inlineStr">
+        <is>
+          <t>简易模式先选任务</t>
+        </is>
+      </c>
+      <c r="D62" s="22" t="inlineStr">
+        <is>
+          <t>顶部三个任务卡片：照参考图做（默认）、做一张图、出一整套；第 2 步按任务只显示需要的选项；风格、模特、品牌资料包、描述与提示词收进“更多选项”</t>
+        </is>
+      </c>
+      <c r="E62" s="22" t="inlineStr">
+        <is>
+          <t>Studio/simple.js；index.html；studio.css</t>
+        </is>
+      </c>
+      <c r="F62" s="22" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G62" s="22" t="inlineStr">
+        <is>
+          <t>运营友好</t>
+        </is>
+      </c>
+      <c r="H62" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-29 界面改版讨论（决策 A13）</t>
+        </is>
+      </c>
+      <c r="I62" s="22" t="inlineStr">
+        <is>
+          <t>T64</t>
+        </is>
+      </c>
+      <c r="J62" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A62)</f>
+        <v/>
+      </c>
+      <c r="K62" s="22">
+        <f>IF(J62=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A62,开发任务!$L$5:$L$200,"暂缓")=J62,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A62,开发任务!$L$5:$L$200,"未开始")=J62,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A62,开发任务!$L$5:$L$200,"已完成")=J62,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A62,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A62,开发任务!$L$5:$L$200,"暂缓")=J62,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M62" s="22" t="inlineStr">
+        <is>
+          <t>需求见 docs/EcomCraft 界面改版需求.zh-CN.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>F62</t>
+        </is>
+      </c>
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>改版：界面 v4</t>
+        </is>
+      </c>
+      <c r="C63" s="22" t="inlineStr">
+        <is>
+          <t>导航、管理菜单与用词统一</t>
+        </is>
+      </c>
+      <c r="D63" s="22" t="inlineStr">
+        <is>
+          <t>顶栏：出图 / 专业模式 / 画廊 / 队列；管理员的“管理”菜单收纳工作流审核、设置向导、提示词设置、存储与备份、原生引擎；按需求文档第 3 节统一用词</t>
+        </is>
+      </c>
+      <c r="E63" s="22" t="inlineStr">
+        <is>
+          <t>Studio/index.html；studio.js；lang/en.js</t>
+        </is>
+      </c>
+      <c r="F63" s="22" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G63" s="22" t="n"/>
+      <c r="H63" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-29 界面改版讨论（决策 A13）</t>
+        </is>
+      </c>
+      <c r="I63" s="22" t="inlineStr">
+        <is>
+          <t>T65</t>
+        </is>
+      </c>
+      <c r="J63" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A63)</f>
+        <v/>
+      </c>
+      <c r="K63" s="22">
+        <f>IF(J63=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A63,开发任务!$L$5:$L$200,"暂缓")=J63,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A63,开发任务!$L$5:$L$200,"未开始")=J63,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A63,开发任务!$L$5:$L$200,"已完成")=J63,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A63,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A63,开发任务!$L$5:$L$200,"暂缓")=J63,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M63" s="22" t="inlineStr">
+        <is>
+          <t>需求见 docs/EcomCraft 界面改版需求.zh-CN.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>F63</t>
+        </is>
+      </c>
+      <c r="B64" s="22" t="inlineStr">
+        <is>
+          <t>改版：界面 v4</t>
+        </is>
+      </c>
+      <c r="C64" s="22" t="inlineStr">
+        <is>
+          <t>手机只做简易模式</t>
+        </is>
+      </c>
+      <c r="D64" s="22" t="inlineStr">
+        <is>
+          <t>窄屏不显示专业模式入口，打开 #create 时提示到电脑上操作；简易模式、画廊、队列在手机上可用</t>
+        </is>
+      </c>
+      <c r="E64" s="22" t="inlineStr">
+        <is>
+          <t>Studio/studio.css；studio.js</t>
+        </is>
+      </c>
+      <c r="F64" s="22" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G64" s="22" t="inlineStr">
+        <is>
+          <t>运营友好</t>
+        </is>
+      </c>
+      <c r="H64" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-29 界面改版讨论（决策 A13）</t>
+        </is>
+      </c>
+      <c r="I64" s="22" t="inlineStr">
+        <is>
+          <t>T66</t>
+        </is>
+      </c>
+      <c r="J64" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A64)</f>
+        <v/>
+      </c>
+      <c r="K64" s="22">
+        <f>IF(J64=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A64,开发任务!$L$5:$L$200,"暂缓")=J64,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A64,开发任务!$L$5:$L$200,"未开始")=J64,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A64,开发任务!$L$5:$L$200,"已完成")=J64,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A64,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A64,开发任务!$L$5:$L$200,"暂缓")=J64,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M64" s="22" t="inlineStr">
+        <is>
+          <t>需求见 docs/EcomCraft 界面改版需求.zh-CN.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="inlineStr">
+        <is>
+          <t>F64</t>
+        </is>
+      </c>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>改版：界面 v4</t>
+        </is>
+      </c>
+      <c r="C65" s="22" t="inlineStr">
+        <is>
+          <t>简易模式到专业模式单向衔接</t>
+        </is>
+      </c>
+      <c r="D65" s="22" t="inlineStr">
+        <is>
+          <t>候选图“在专业模式里精修”：带上这张图和实际发送的英文提示词进入专业模式；不回写简易模式</t>
+        </is>
+      </c>
+      <c r="E65" s="22" t="inlineStr">
+        <is>
+          <t>Studio/simple.js；studio.js</t>
+        </is>
+      </c>
+      <c r="F65" s="22" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G65" s="22" t="inlineStr">
+        <is>
+          <t>设计友好</t>
+        </is>
+      </c>
+      <c r="H65" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-29 界面改版讨论（决策 A13）</t>
+        </is>
+      </c>
+      <c r="I65" s="22" t="inlineStr">
+        <is>
+          <t>T67</t>
+        </is>
+      </c>
+      <c r="J65" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A65)</f>
+        <v/>
+      </c>
+      <c r="K65" s="22">
+        <f>IF(J65=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A65,开发任务!$L$5:$L$200,"暂缓")=J65,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A65,开发任务!$L$5:$L$200,"未开始")=J65,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A65,开发任务!$L$5:$L$200,"已完成")=J65,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A65,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A65,开发任务!$L$5:$L$200,"暂缓")=J65,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M65" s="22" t="inlineStr">
+        <is>
+          <t>需求见 docs/EcomCraft 界面改版需求.zh-CN.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="22" t="inlineStr">
+        <is>
+          <t>F65</t>
+        </is>
+      </c>
+      <c r="B66" s="22" t="inlineStr">
+        <is>
+          <t>改版：界面 v4</t>
+        </is>
+      </c>
+      <c r="C66" s="22" t="inlineStr">
+        <is>
+          <t>候选图收藏（初筛）</t>
+        </is>
+      </c>
+      <c r="D66" s="22" t="inlineStr">
+        <is>
+          <t>候选图上的收藏按钮复用画廊收藏（ToggleImageStarred）；收藏的图不被候选清理</t>
+        </is>
+      </c>
+      <c r="E66" s="22" t="inlineStr">
+        <is>
+          <t>Studio/simple.js；Generation/（候选清理）</t>
+        </is>
+      </c>
+      <c r="F66" s="22" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G66" s="22" t="inlineStr">
+        <is>
+          <t>运营友好</t>
+        </is>
+      </c>
+      <c r="H66" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-29 界面改版讨论（决策 A13）</t>
+        </is>
+      </c>
+      <c r="I66" s="22" t="inlineStr">
+        <is>
+          <t>T68</t>
+        </is>
+      </c>
+      <c r="J66" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A66)</f>
+        <v/>
+      </c>
+      <c r="K66" s="22">
+        <f>IF(J66=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A66,开发任务!$L$5:$L$200,"暂缓")=J66,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A66,开发任务!$L$5:$L$200,"未开始")=J66,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A66,开发任务!$L$5:$L$200,"已完成")=J66,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A66,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A66,开发任务!$L$5:$L$200,"暂缓")=J66,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M66" s="22" t="inlineStr">
+        <is>
+          <t>需求见 docs/EcomCraft 界面改版需求.zh-CN.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="22" t="inlineStr">
+        <is>
+          <t>F66</t>
+        </is>
+      </c>
+      <c r="B67" s="22" t="inlineStr">
+        <is>
+          <t>改版：界面 v4</t>
+        </is>
+      </c>
+      <c r="C67" s="22" t="inlineStr">
+        <is>
+          <t>画廊与队列整理</t>
+        </is>
+      </c>
+      <c r="D67" s="22" t="inlineStr">
+        <is>
+          <t>画廊收藏筛选与按任务来源分组；队列把我的任务放在前面</t>
+        </is>
+      </c>
+      <c r="E67" s="22" t="inlineStr">
+        <is>
+          <t>Studio/studio.js；index.html</t>
+        </is>
+      </c>
+      <c r="F67" s="22" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G67" s="22" t="n"/>
+      <c r="H67" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-29 界面改版讨论（决策 A13）</t>
+        </is>
+      </c>
+      <c r="I67" s="22" t="inlineStr">
+        <is>
+          <t>T69</t>
+        </is>
+      </c>
+      <c r="J67" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A67)</f>
+        <v/>
+      </c>
+      <c r="K67" s="22">
+        <f>IF(J67=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A67,开发任务!$L$5:$L$200,"暂缓")=J67,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A67,开发任务!$L$5:$L$200,"未开始")=J67,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A67,开发任务!$L$5:$L$200,"已完成")=J67,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A67,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A67,开发任务!$L$5:$L$200,"暂缓")=J67,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M67" s="22" t="inlineStr">
+        <is>
+          <t>需求见 docs/EcomCraft 界面改版需求.zh-CN.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>F67</t>
+        </is>
+      </c>
+      <c r="B68" s="22" t="inlineStr">
+        <is>
+          <t>改版：界面 v4</t>
+        </is>
+      </c>
+      <c r="C68" s="22" t="inlineStr">
+        <is>
+          <t>收藏偏好分析与提示词反哺</t>
+        </is>
+      </c>
+      <c r="D68" s="22" t="inlineStr">
+        <is>
+          <t>按账号统计收藏率高的选项并预选；对比收藏与未收藏的提示词，提出“你可能喜欢的描述”由用户确认后加入；草案见需求文档第 6 节</t>
+        </is>
+      </c>
+      <c r="E68" s="22" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="F68" s="22" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G68" s="22" t="n"/>
+      <c r="H68" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-29 界面改版讨论（决策 A13）</t>
+        </is>
+      </c>
+      <c r="I68" s="22" t="inlineStr">
+        <is>
+          <t>T70</t>
+        </is>
+      </c>
+      <c r="J68" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A68)</f>
+        <v/>
+      </c>
+      <c r="K68" s="22">
+        <f>IF(J68=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A68,开发任务!$L$5:$L$200,"暂缓")=J68,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A68,开发任务!$L$5:$L$200,"未开始")=J68,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A68,开发任务!$L$5:$L$200,"已完成")=J68,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A68,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A68,开发任务!$L$5:$L$200,"暂缓")=J68,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M68" s="22" t="inlineStr">
+        <is>
+          <t>需求见 docs/EcomCraft 界面改版需求.zh-CN.md</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:M31"/>
@@ -4282,7 +4690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:N74"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="22" min="1" max="1"/>
@@ -8629,7 +9037,7 @@
         </is>
       </c>
     </row>
-    <row r="66">
+    <row r="66" s="23">
       <c r="A66" s="22" t="n">
         <v>62</v>
       </c>
@@ -8640,7 +9048,7 @@
       </c>
       <c r="C66" s="22" t="inlineStr">
         <is>
-          <t>后续：功能增强</t>
+          <t>改版：界面 v4</t>
         </is>
       </c>
       <c r="D66" s="22" t="inlineStr">
@@ -8670,7 +9078,7 @@
       </c>
       <c r="I66" s="22" t="inlineStr">
         <is>
-          <t>普通账号导航出现“专业模式”并能打开 #create 正常出图；默认仍进入简易模式；简易模式仍没有专业参数；专业模式生成仍只走已登记执行服务器和服务端校验；审核、服务器、存储、设置向导等管理视图仍只对管理员可见</t>
+          <t>普通账号导航出现“专业模式”并能打开 #create 正常出图；默认仍进入简易模式；简易模式仍没有专业参数；专业模式生成仍只走已登记执行服务器和服务端校验；审核、服务器、存储、设置向导等管理视图仍只对管理员可见；任何账号可在专业模式里上传 ComfyUI 工作流 JSON，上传后进入工作流审核，发布前不能用于出图</t>
         </is>
       </c>
       <c r="J66" s="22" t="inlineStr">
@@ -8681,7 +9089,7 @@
       <c r="K66" s="22" t="inlineStr">
         <is>
           <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
-任务：按决策 A2 把专业模式开放给所有账号（平面设计人员在专业模式里调整模型、采样器、LoRA、步数等参数）。去掉 studio.js / simple.js 里“专业模式只给管理员”的前端限制，核对专业模式用到的 SwarmUI 与 EcomCraft 接口对普通账号的权限是否足够，只放开出图所需的权限，不放开服务器设置、后端管理等管理员功能。同步 README（中英文）、工作台界面设计文档（中英文）和 ecomcraft-studio-ui 技能。
+任务：按决策 A2 把专业模式开放给所有账号（平面设计人员在专业模式里调整模型、采样器、LoRA、步数等参数）。去掉 studio.js / simple.js 里“专业模式只给管理员”的前端限制，核对专业模式用到的 SwarmUI 与 EcomCraft 接口对普通账号的权限是否足够，只放开出图所需的权限，不放开服务器设置、后端管理等管理员功能。在专业模式里加入“上传工作流”入口，复用现有工作流提交与审核接口（上传的 JSON 只进入审核，不能直接出图）。同步 README（中英文）、工作台界面设计文档（中英文）和 ecomcraft-studio-ui 技能。
 请先进入计划模式给出设计方案（改哪些文件、权限变化、风险），我确认后再实现。
 完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
         </is>
@@ -8699,7 +9107,466 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="40" t="inlineStr">
+      <c r="A67" s="22" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="22" t="inlineStr">
+        <is>
+          <t>T64</t>
+        </is>
+      </c>
+      <c r="C67" s="22" t="inlineStr">
+        <is>
+          <t>改版：界面 v4</t>
+        </is>
+      </c>
+      <c r="D67" s="22" t="inlineStr">
+        <is>
+          <t>F61</t>
+        </is>
+      </c>
+      <c r="E67" s="22" t="inlineStr">
+        <is>
+          <t>简易模式先选任务：任务卡片、按任务显示第 2 步、更多选项折叠</t>
+        </is>
+      </c>
+      <c r="F67" s="22" t="inlineStr">
+        <is>
+          <t>Studio/simple.js、index.html、studio.css、lang/en.js、Tests/simple-mode.test.cjs</t>
+        </is>
+      </c>
+      <c r="G67" s="22" t="inlineStr">
+        <is>
+          <t>T61</t>
+        </is>
+      </c>
+      <c r="H67" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I67" s="22" t="inlineStr">
+        <is>
+          <t>顶部三个任务卡片（照参考图做默认且排第一）；照参考图做只显示平台、参考图与逐张提示词和“按参考出图”；做一张图显示平台、图片类型、产品类型、更多选项（默认收起）、张数和“开始出图”；出一整套显示平台与可选槽位、产品类型、更多选项、张数、卖点分镜和一键出整套；任务与更多选项的展开状态记在浏览器；切换任务不清空商品图和参考图</t>
+        </is>
+      </c>
+      <c r="J67" s="22" t="inlineStr">
+        <is>
+          <t>node --test simple-mode / studio-i18n；三个任务各出一次图手动验证；中英文界面</t>
+        </is>
+      </c>
+      <c r="K67" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+界面改版需求以 docs/EcomCraft 界面改版需求.zh-CN.md 为准，需求有变化先改该文档（中英文）。
+任务：按需求文档第 5 节实现简易模式“先选任务，再填内容”。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L67" s="22" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="M67" s="22" t="n"/>
+      <c r="N67" s="22" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="22" t="inlineStr">
+        <is>
+          <t>T65</t>
+        </is>
+      </c>
+      <c r="C68" s="22" t="inlineStr">
+        <is>
+          <t>改版：界面 v4</t>
+        </is>
+      </c>
+      <c r="D68" s="22" t="inlineStr">
+        <is>
+          <t>F62</t>
+        </is>
+      </c>
+      <c r="E68" s="22" t="inlineStr">
+        <is>
+          <t>导航、管理菜单与用词统一</t>
+        </is>
+      </c>
+      <c r="F68" s="22" t="inlineStr">
+        <is>
+          <t>Studio/index.html、studio.js、studio.css、lang/en.js</t>
+        </is>
+      </c>
+      <c r="G68" s="22" t="inlineStr">
+        <is>
+          <t>T64</t>
+        </is>
+      </c>
+      <c r="H68" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I68" s="22" t="inlineStr">
+        <is>
+          <t>顶栏为出图 / 专业模式 / 画廊 / 队列；管理员看到“管理”菜单（工作流审核、设置向导、提示词设置、存储与备份、原生引擎），普通账号看不到；原生引擎只给管理员；界面用词符合需求文档第 3 节</t>
+        </is>
+      </c>
+      <c r="J68" s="22" t="inlineStr">
+        <is>
+          <t>node --test；管理员与普通账号各登录一次检查导航</t>
+        </is>
+      </c>
+      <c r="K68" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+界面改版需求以 docs/EcomCraft 界面改版需求.zh-CN.md 为准，需求有变化先改该文档（中英文）。
+任务：按需求文档第 3、4 节整理导航、管理菜单和用词。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L68" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="M68" s="22" t="n"/>
+      <c r="N68" s="22" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="22" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="22" t="inlineStr">
+        <is>
+          <t>T66</t>
+        </is>
+      </c>
+      <c r="C69" s="22" t="inlineStr">
+        <is>
+          <t>改版：界面 v4</t>
+        </is>
+      </c>
+      <c r="D69" s="22" t="inlineStr">
+        <is>
+          <t>F63</t>
+        </is>
+      </c>
+      <c r="E69" s="22" t="inlineStr">
+        <is>
+          <t>手机只做简易模式</t>
+        </is>
+      </c>
+      <c r="F69" s="22" t="inlineStr">
+        <is>
+          <t>Studio/studio.css、studio.js、Tests/mobile.test.cjs</t>
+        </is>
+      </c>
+      <c r="G69" s="22" t="inlineStr">
+        <is>
+          <t>T65</t>
+        </is>
+      </c>
+      <c r="H69" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I69" s="22" t="inlineStr">
+        <is>
+          <t>窄屏不显示专业模式入口；手机打开 #create 时说明请到电脑上使用并回到出图；简易模式、画廊、队列在手机上无横向滚动</t>
+        </is>
+      </c>
+      <c r="J69" s="22" t="inlineStr">
+        <is>
+          <t>node --test mobile；手机浏览器手动检查</t>
+        </is>
+      </c>
+      <c r="K69" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+界面改版需求以 docs/EcomCraft 界面改版需求.zh-CN.md 为准，需求有变化先改该文档（中英文）。
+任务：按决策 U9 实现手机只做简易模式。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L69" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="M69" s="22" t="n"/>
+      <c r="N69" s="22" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="22" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="22" t="inlineStr">
+        <is>
+          <t>T67</t>
+        </is>
+      </c>
+      <c r="C70" s="22" t="inlineStr">
+        <is>
+          <t>改版：界面 v4</t>
+        </is>
+      </c>
+      <c r="D70" s="22" t="inlineStr">
+        <is>
+          <t>F64</t>
+        </is>
+      </c>
+      <c r="E70" s="22" t="inlineStr">
+        <is>
+          <t>简易模式到专业模式单向衔接</t>
+        </is>
+      </c>
+      <c r="F70" s="22" t="inlineStr">
+        <is>
+          <t>Studio/simple.js、studio.js</t>
+        </is>
+      </c>
+      <c r="G70" s="22" t="inlineStr">
+        <is>
+          <t>T63</t>
+        </is>
+      </c>
+      <c r="H70" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I70" s="22" t="inlineStr">
+        <is>
+          <t>候选图上“在专业模式里精修”打开专业模式，带上这张图（作为图生图初始图）和实际发送的英文提示词；专业模式的修改不回写简易模式；普通账号同样可用</t>
+        </is>
+      </c>
+      <c r="J70" s="22" t="inlineStr">
+        <is>
+          <t>手动验证：简易模式出图后点精修，专业模式参数已带入并能出图</t>
+        </is>
+      </c>
+      <c r="K70" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+界面改版需求以 docs/EcomCraft 界面改版需求.zh-CN.md 为准，需求有变化先改该文档（中英文）。
+任务：按决策 U7 实现简易模式到专业模式的单向衔接；先进入计划模式说明带入哪些字段、如何复用专业模式现有的初始图入口，我确认后再实现。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L70" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="M70" s="22" t="n"/>
+      <c r="N70" s="22" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="22" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>T68</t>
+        </is>
+      </c>
+      <c r="C71" s="22" t="inlineStr">
+        <is>
+          <t>改版：界面 v4</t>
+        </is>
+      </c>
+      <c r="D71" s="22" t="inlineStr">
+        <is>
+          <t>F65</t>
+        </is>
+      </c>
+      <c r="E71" s="22" t="inlineStr">
+        <is>
+          <t>候选图收藏（初筛）</t>
+        </is>
+      </c>
+      <c r="F71" s="22" t="inlineStr">
+        <is>
+          <t>Studio/simple.js、Generation/（候选清理）</t>
+        </is>
+      </c>
+      <c r="G71" s="22" t="inlineStr">
+        <is>
+          <t>T64</t>
+        </is>
+      </c>
+      <c r="H71" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I71" s="22" t="inlineStr">
+        <is>
+          <t>候选图上有收藏按钮，状态与画廊收藏一致；收藏的候选图不会被候选清理删除</t>
+        </is>
+      </c>
+      <c r="J71" s="22" t="inlineStr">
+        <is>
+          <t>手动验证收藏后画廊“已收藏”可见；C# 测试候选清理跳过已收藏</t>
+        </is>
+      </c>
+      <c r="K71" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+界面改版需求以 docs/EcomCraft 界面改版需求.zh-CN.md 为准，需求有变化先改该文档（中英文）。
+任务：按决策 U5 在候选图上加入收藏，复用 ToggleImageStarred 与候选保留（EcomCraftStudioMarkKept）。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L71" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="M71" s="22" t="n"/>
+      <c r="N71" s="22" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="22" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="22" t="inlineStr">
+        <is>
+          <t>T69</t>
+        </is>
+      </c>
+      <c r="C72" s="22" t="inlineStr">
+        <is>
+          <t>改版：界面 v4</t>
+        </is>
+      </c>
+      <c r="D72" s="22" t="inlineStr">
+        <is>
+          <t>F66</t>
+        </is>
+      </c>
+      <c r="E72" s="22" t="inlineStr">
+        <is>
+          <t>画廊与队列整理</t>
+        </is>
+      </c>
+      <c r="F72" s="22" t="inlineStr">
+        <is>
+          <t>Studio/studio.js、index.html、studio.css</t>
+        </is>
+      </c>
+      <c r="G72" s="22" t="inlineStr">
+        <is>
+          <t>T68</t>
+        </is>
+      </c>
+      <c r="H72" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I72" s="22" t="inlineStr">
+        <is>
+          <t>画廊可按收藏筛选并区分简易模式与专业模式作品；队列把当前账号的任务放在前面；用词符合需求文档第 3 节</t>
+        </is>
+      </c>
+      <c r="J72" s="22" t="inlineStr">
+        <is>
+          <t>node --test；手动检查画廊与队列</t>
+        </is>
+      </c>
+      <c r="K72" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+界面改版需求以 docs/EcomCraft 界面改版需求.zh-CN.md 为准，需求有变化先改该文档（中英文）。
+任务：按需求文档整理画廊与队列。先进入计划模式给出改动方案，我确认后再实现。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L72" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="M72" s="22" t="n"/>
+      <c r="N72" s="22" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="22" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="22" t="inlineStr">
+        <is>
+          <t>T70</t>
+        </is>
+      </c>
+      <c r="C73" s="22" t="inlineStr">
+        <is>
+          <t>改版：界面 v4</t>
+        </is>
+      </c>
+      <c r="D73" s="22" t="inlineStr">
+        <is>
+          <t>F67</t>
+        </is>
+      </c>
+      <c r="E73" s="22" t="inlineStr">
+        <is>
+          <t>收藏偏好分析与提示词反哺</t>
+        </is>
+      </c>
+      <c r="F73" s="22" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="G73" s="22" t="inlineStr">
+        <is>
+          <t>T68</t>
+        </is>
+      </c>
+      <c r="H73" s="22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I73" s="22" t="inlineStr">
+        <is>
+          <t>待定：方案确认后补充</t>
+        </is>
+      </c>
+      <c r="J73" s="22" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="K73" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+界面改版需求以 docs/EcomCraft 界面改版需求.zh-CN.md 为准，需求有变化先改该文档（中英文）。
+任务：按需求文档第 6 节草案设计收藏偏好分析与提示词反哺；先补 AGENTS.md 数据规则并进入计划模式，我确认后再实现。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L73" s="22" t="inlineStr">
+        <is>
+          <t>暂缓</t>
+        </is>
+      </c>
+      <c r="M73" s="22" t="n"/>
+      <c r="N73" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-29 用户：不急，留待办，方案未定</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="40" t="inlineStr">
         <is>
           <t>规模：S 约半天以内，M 约 1–2 天，L 3 天以上（含你的验证时间，仅供粗略估计）。原 T03、T26 已分别并入 T13、T34。</t>
         </is>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -1040,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="22" min="1" max="1"/>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
-          <t>平面设计人员用专业模式调整模型、采样器、LoRA、步数等参数（决策 A2）：任何账号都可以从导航切换到专业模式，默认仍进入简易模式；管理视图仍只对管理员可见；设计师可在专业模式里上传 ComfyUI 工作流 JSON，进入工作流审核，管理员发布后才能用（决策 A13）</t>
+          <t>平面设计人员用专业模式调整模型、采样器、LoRA、步数等参数（决策 A2）：任何账号都可以从导航切换到专业模式，默认仍进入简易模式；管理视图仍只对管理员可见；设计师可在专业模式里上传 ComfyUI 工作流 JSON，经服务端校验后上传者自己马上能用，其他账号要经审核发布（决策 U6，2026-10-29 修订）</t>
         </is>
       </c>
       <c r="E61" s="22" t="inlineStr">
@@ -4612,7 +4612,7 @@
         </is>
       </c>
     </row>
-    <row r="68">
+    <row r="68" s="23">
       <c r="A68" s="22" t="inlineStr">
         <is>
           <t>F67</t>
@@ -4663,6 +4663,122 @@
         <v/>
       </c>
       <c r="M68" s="22" t="inlineStr">
+        <is>
+          <t>需求见 docs/EcomCraft 界面改版需求.zh-CN.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="22" t="inlineStr">
+        <is>
+          <t>F68</t>
+        </is>
+      </c>
+      <c r="B69" s="22" t="inlineStr">
+        <is>
+          <t>改版：界面 v4</t>
+        </is>
+      </c>
+      <c r="C69" s="22" t="inlineStr">
+        <is>
+          <t>看图描述默认开启与配置引导</t>
+        </is>
+      </c>
+      <c r="D69" s="22" t="inlineStr">
+        <is>
+          <t>看图描述默认开启（只用于参考图，商品图描述仍默认关闭）；新增视觉模型状态检查，没有可用视觉模型时“照参考图做”说明缺什么：管理员看到处理步骤，普通账号看到请联系管理员</t>
+        </is>
+      </c>
+      <c r="E69" s="22" t="inlineStr">
+        <is>
+          <t>Prompting/PromptService.cs；Studio/simple.js</t>
+        </is>
+      </c>
+      <c r="F69" s="22" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G69" s="22" t="inlineStr">
+        <is>
+          <t>运营友好</t>
+        </is>
+      </c>
+      <c r="H69" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-29 用户确认（决策 U12、A5 修订）</t>
+        </is>
+      </c>
+      <c r="I69" s="22" t="inlineStr">
+        <is>
+          <t>T71</t>
+        </is>
+      </c>
+      <c r="J69" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A69)</f>
+        <v/>
+      </c>
+      <c r="K69" s="22">
+        <f>IF(J69=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A69,开发任务!$L$5:$L$200,"暂缓")=J69,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A69,开发任务!$L$5:$L$200,"未开始")=J69,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A69,开发任务!$L$5:$L$200,"已完成")=J69,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A69,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A69,开发任务!$L$5:$L$200,"暂缓")=J69,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M69" s="22" t="inlineStr">
+        <is>
+          <t>需求见 docs/EcomCraft 界面改版需求.zh-CN.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="22" t="inlineStr">
+        <is>
+          <t>F69</t>
+        </is>
+      </c>
+      <c r="B70" s="22" t="inlineStr">
+        <is>
+          <t>改版：界面 v4</t>
+        </is>
+      </c>
+      <c r="C70" s="22" t="inlineStr">
+        <is>
+          <t>看图模型一键安装脚本</t>
+        </is>
+      </c>
+      <c r="D70" s="22" t="inlineStr">
+        <is>
+          <t>管理员运行脚本自动安装 Ollama 并拉取默认视觉模型；Windows 与 Linux 各一份</t>
+        </is>
+      </c>
+      <c r="E70" s="22" t="inlineStr">
+        <is>
+          <t>新增脚本；docs/EcomCraft Prompt Enhancement</t>
+        </is>
+      </c>
+      <c r="F70" s="22" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G70" s="22" t="n"/>
+      <c r="H70" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-29 用户确认（决策 U12、A5 修订）</t>
+        </is>
+      </c>
+      <c r="I70" s="22" t="inlineStr">
+        <is>
+          <t>T72</t>
+        </is>
+      </c>
+      <c r="J70" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A70)</f>
+        <v/>
+      </c>
+      <c r="K70" s="22">
+        <f>IF(J70=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A70,开发任务!$L$5:$L$200,"暂缓")=J70,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A70,开发任务!$L$5:$L$200,"未开始")=J70,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A70,开发任务!$L$5:$L$200,"已完成")=J70,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A70,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A70,开发任务!$L$5:$L$200,"暂缓")=J70,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M70" s="22" t="inlineStr">
         <is>
           <t>需求见 docs/EcomCraft 界面改版需求.zh-CN.md</t>
         </is>
@@ -4690,7 +4806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N74"/>
+  <dimension ref="A1:N76"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="22" min="1" max="1"/>
@@ -9078,7 +9194,7 @@
       </c>
       <c r="I66" s="22" t="inlineStr">
         <is>
-          <t>普通账号导航出现“专业模式”并能打开 #create 正常出图；默认仍进入简易模式；简易模式仍没有专业参数；专业模式生成仍只走已登记执行服务器和服务端校验；审核、服务器、存储、设置向导等管理视图仍只对管理员可见；任何账号可在专业模式里上传 ComfyUI 工作流 JSON，上传后进入工作流审核，发布前不能用于出图</t>
+          <t>普通账号导航出现“专业模式”并能打开 #create 正常出图；默认仍进入简易模式；简易模式仍没有专业参数；专业模式生成仍只走已登记执行服务器和服务端校验；审核、服务器、存储、设置向导等管理视图仍只对管理员可见；任何账号可在专业模式里上传 ComfyUI 工作流 JSON，经服务端校验后上传者自己马上能用（只对上传者可见、拒绝禁用节点），其他账号要经审核发布</t>
         </is>
       </c>
       <c r="J66" s="22" t="inlineStr">
@@ -9089,7 +9205,7 @@
       <c r="K66" s="22" t="inlineStr">
         <is>
           <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
-任务：按决策 A2 把专业模式开放给所有账号（平面设计人员在专业模式里调整模型、采样器、LoRA、步数等参数）。去掉 studio.js / simple.js 里“专业模式只给管理员”的前端限制，核对专业模式用到的 SwarmUI 与 EcomCraft 接口对普通账号的权限是否足够，只放开出图所需的权限，不放开服务器设置、后端管理等管理员功能。在专业模式里加入“上传工作流”入口，复用现有工作流提交与审核接口（上传的 JSON 只进入审核，不能直接出图）。同步 README（中英文）、工作台界面设计文档（中英文）和 ecomcraft-studio-ui 技能。
+任务：按决策 A2 把专业模式开放给所有账号（平面设计人员在专业模式里调整模型、采样器、LoRA、步数等参数）。去掉 studio.js / simple.js 里“专业模式只给管理员”的前端限制，核对专业模式用到的 SwarmUI 与 EcomCraft 接口对普通账号的权限是否足够，只放开出图所需的权限，不放开服务器设置、后端管理等管理员功能。在专业模式里加入“上传工作流”入口，上传的 JSON 经与导入相同的校验并生成参数白名单后作为上传者的自用工作流立即可用，其他账号要经审核发布；按 AGENTS.md 的自用工作流规则实现禁用节点列表。同步 README（中英文）、工作台界面设计文档（中英文）和 ecomcraft-studio-ui 技能。
 请先进入计划模式给出设计方案（改哪些文件、权限变化、风险），我确认后再实现。
 完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
         </is>
@@ -9169,7 +9285,11 @@
         </is>
       </c>
       <c r="M67" s="22" t="n"/>
-      <c r="N67" s="22" t="n"/>
+      <c r="N67" s="22" t="inlineStr">
+        <is>
+          <t>代码已提交（0d562bef，只改前端）；待浏览器验收</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="22" t="n">
@@ -9496,7 +9616,7 @@
       <c r="M72" s="22" t="n"/>
       <c r="N72" s="22" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" s="23">
       <c r="A73" s="22" t="n">
         <v>69</v>
       </c>
@@ -9566,7 +9686,137 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="40" t="inlineStr">
+      <c r="A74" s="22" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="22" t="inlineStr">
+        <is>
+          <t>T71</t>
+        </is>
+      </c>
+      <c r="C74" s="22" t="inlineStr">
+        <is>
+          <t>改版：界面 v4</t>
+        </is>
+      </c>
+      <c r="D74" s="22" t="inlineStr">
+        <is>
+          <t>F68</t>
+        </is>
+      </c>
+      <c r="E74" s="22" t="inlineStr">
+        <is>
+          <t>看图描述默认开启与配置引导</t>
+        </is>
+      </c>
+      <c r="F74" s="22" t="inlineStr">
+        <is>
+          <t>Prompting/PromptService.cs、Studio/simple.js、lang/en.js</t>
+        </is>
+      </c>
+      <c r="G74" s="22" t="inlineStr">
+        <is>
+          <t>T64</t>
+        </is>
+      </c>
+      <c r="H74" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I74" s="22" t="inlineStr">
+        <is>
+          <t>未设置过开关时看图描述为开启，商品图描述仍需管理员明确开启；视觉模型状态接口返回 ready / off / unreachable / model_missing / no_model 与服务类型、模型名称（不含地址）；“照参考图做”在不可用时说明原因，管理员看到处理步骤，普通账号看到请联系管理员</t>
+        </is>
+      </c>
+      <c r="J74" s="22" t="inlineStr">
+        <is>
+          <t>C# 测试开关默认值；node --test；关掉 Ollama、删除模型、关闭开关各验证一次提示</t>
+        </is>
+      </c>
+      <c r="K74" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+界面改版需求以 docs/EcomCraft 界面改版需求.zh-CN.md 为准，需求有变化先改该文档（中英文）。
+任务：按决策 U12 实现看图描述默认开启与配置引导。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L74" s="22" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="M74" s="22" t="n"/>
+      <c r="N74" s="22" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="22" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="22" t="inlineStr">
+        <is>
+          <t>T72</t>
+        </is>
+      </c>
+      <c r="C75" s="22" t="inlineStr">
+        <is>
+          <t>改版：界面 v4</t>
+        </is>
+      </c>
+      <c r="D75" s="22" t="inlineStr">
+        <is>
+          <t>F69</t>
+        </is>
+      </c>
+      <c r="E75" s="22" t="inlineStr">
+        <is>
+          <t>看图模型一键安装脚本</t>
+        </is>
+      </c>
+      <c r="F75" s="22" t="inlineStr">
+        <is>
+          <t>新增 Windows / Linux 脚本；docs/EcomCraft Prompt Enhancement（中英文）</t>
+        </is>
+      </c>
+      <c r="G75" s="22" t="inlineStr">
+        <is>
+          <t>T71</t>
+        </is>
+      </c>
+      <c r="H75" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I75" s="22" t="inlineStr">
+        <is>
+          <t>管理员运行脚本后：未安装 Ollama 时自动安装，启动服务并拉取设置中的视觉模型；已安装时只拉取模型；每一步输出白话结果，失败时说明原因和手动步骤</t>
+        </is>
+      </c>
+      <c r="J75" s="22" t="inlineStr">
+        <is>
+          <t>全新 Windows 机器运行一次；已装 Ollama 的机器运行一次</t>
+        </is>
+      </c>
+      <c r="K75" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+界面改版需求以 docs/EcomCraft 界面改版需求.zh-CN.md 为准，需求有变化先改该文档（中英文）。
+任务：按决策 U12 编写看图模型一键安装脚本，先进入计划模式说明安装来源、模型选择和失败处理，我确认后再实现。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L75" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="M75" s="22" t="n"/>
+      <c r="N75" s="22" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="40" t="inlineStr">
         <is>
           <t>规模：S 约半天以内，M 约 1–2 天，L 3 天以上（含你的验证时间，仅供粗略估计）。原 T03、T26 已分别并入 T13、T34。</t>
         </is>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -9748,7 +9748,11 @@
         </is>
       </c>
       <c r="M74" s="22" t="n"/>
-      <c r="N74" s="22" t="n"/>
+      <c r="N74" s="22" t="inlineStr">
+        <is>
+          <t>代码已提交（01d90430）；待编译与验收</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="22" t="n">
@@ -9776,7 +9780,7 @@
       </c>
       <c r="F75" s="22" t="inlineStr">
         <is>
-          <t>新增 Windows / Linux 脚本；docs/EcomCraft Prompt Enhancement（中英文）</t>
+          <t>launchtools/install-vision-model-windows.ps1、launchtools/install-vision-model-linux.sh、Studio/simple.js、docs/EcomCraft Prompt Enhancement（中英文）</t>
         </is>
       </c>
       <c r="G75" s="22" t="inlineStr">
@@ -9809,11 +9813,15 @@
       </c>
       <c r="L75" s="22" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="M75" s="22" t="n"/>
-      <c r="N75" s="22" t="n"/>
+      <c r="N75" s="22" t="inlineStr">
+        <is>
+          <t>安装来源：Windows 用 winget（Ollama.Ollama），否则官方 OllamaSetup.exe 且校验数字签名；Linux 用官方 install.sh；模型名默认 llama3.2-vision:latest，可传参；待真机验收</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="40" t="inlineStr">

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -9350,11 +9350,15 @@
       </c>
       <c r="L68" s="22" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="M68" s="22" t="n"/>
-      <c r="N68" s="22" t="n"/>
+      <c r="N68" s="22" t="inlineStr">
+        <is>
+          <t>代码已提交；待浏览器验收（管理员与普通账号各看一次）</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="22" t="n">

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -4247,7 +4247,7 @@
       </c>
       <c r="I61" s="22" t="inlineStr">
         <is>
-          <t>T63</t>
+          <t>T63、T73</t>
         </is>
       </c>
       <c r="J61" s="22">
@@ -4806,7 +4806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N76"/>
+  <dimension ref="A1:N77"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="22" min="1" max="1"/>
@@ -9212,13 +9212,13 @@
       </c>
       <c r="L66" s="22" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="M66" s="22" t="n"/>
       <c r="N66" s="22" t="inlineStr">
         <is>
-          <t>2026-10-29 新增（决策 A2、A12）</t>
+          <t>第 1、2 步代码已提交：专业模式对所有账号开放、上传自用工作流（三层禁用规则、每账号 20 个、2 MB）；提交审核发布拆为 T73；待编译与验收</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,72 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="40" t="inlineStr">
+      <c r="A76" s="22" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" s="22" t="inlineStr">
+        <is>
+          <t>T73</t>
+        </is>
+      </c>
+      <c r="C76" s="22" t="inlineStr">
+        <is>
+          <t>改版：界面 v4</t>
+        </is>
+      </c>
+      <c r="D76" s="22" t="inlineStr">
+        <is>
+          <t>F60</t>
+        </is>
+      </c>
+      <c r="E76" s="22" t="inlineStr">
+        <is>
+          <t>自用工作流提交审核、发布给全员</t>
+        </is>
+      </c>
+      <c r="F76" s="22" t="inlineStr">
+        <is>
+          <t>OwnWorkflowApi.cs、WorkflowReview.cs、WorkflowReviewApi.cs、studio.js</t>
+        </is>
+      </c>
+      <c r="G76" s="22" t="inlineStr">
+        <is>
+          <t>T63</t>
+        </is>
+      </c>
+      <c r="H76" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I76" s="22" t="inlineStr">
+        <is>
+          <t>“我的工作流”可提交审核（附说明）；管理员在“管理 → 工作流审核”看到并可配置参数、通过或驳回；通过后复制为正式发布快照，所有账号可用，原自用工作流保留给上传者；驳回原因只给上传者</t>
+        </is>
+      </c>
+      <c r="J76" s="22" t="inlineStr">
+        <is>
+          <t>C# 测试状态流转；管理员与普通账号各操作一次</t>
+        </is>
+      </c>
+      <c r="K76" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+界面改版需求以 docs/EcomCraft 界面改版需求.zh-CN.md 为准，需求有变化先改该文档（中英文）。
+任务：按需求文档 5.1 与决策 U6 实现自用工作流提交审核与发布。先进入计划模式给出状态流转和接口设计，我确认后再实现。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L76" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="M76" s="22" t="n"/>
+      <c r="N76" s="22" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="40" t="inlineStr">
         <is>
           <t>规模：S 约半天以内，M 约 1–2 天，L 3 天以上（含你的验证时间，仅供粗略估计）。原 T03、T26 已分别并入 T13、T34。</t>
         </is>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -9484,11 +9484,15 @@
       </c>
       <c r="L70" s="22" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="M70" s="22" t="n"/>
-      <c r="N70" s="22" t="n"/>
+      <c r="N70" s="22" t="inlineStr">
+        <is>
+          <t>代码已提交：只选中一张候选图时“在专业模式里精修”，图作为图生图初始图，提示词由 EcomCraftStudioWorkRecipe 从作品元数据读取；窄屏隐藏；待编译与验收</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="22" t="n">

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -9553,11 +9553,15 @@
       </c>
       <c r="L71" s="22" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="M71" s="22" t="n"/>
-      <c r="N71" s="22" t="n"/>
+      <c r="N71" s="22" t="inlineStr">
+        <is>
+          <t>代码已提交（只改前端）：候选图左上角收藏，调用 ToggleImageStarred，收藏时同时 EcomCraftStudioMarkKept 以免原图被清理；待浏览器验收</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="22" t="n">

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -9419,11 +9419,15 @@
       </c>
       <c r="L69" s="22" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="M69" s="22" t="n"/>
-      <c r="N69" s="22" t="n"/>
+      <c r="N69" s="22" t="inlineStr">
+        <is>
+          <t>代码已提交（只改前端）：≤720px 隐藏专业模式入口与相关按钮（.pro-only），#create 回到出图并提示；待手机浏览器验收</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="22" t="n">

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -9626,11 +9626,15 @@
       </c>
       <c r="L72" s="22" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="M72" s="22" t="n"/>
-      <c r="N72" s="22" t="n"/>
+      <c r="N72" s="22" t="inlineStr">
+        <is>
+          <t>代码已提交（只改前端）：画廊来源筛选（按元数据 ecomcraft_template 判断），队列顺序为我的请求 → 服务器任务 → 他人请求；收藏筛选沿用已有“已收藏”；待浏览器验收</t>
+        </is>
+      </c>
     </row>
     <row r="73" s="23">
       <c r="A73" s="22" t="n">

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -9902,11 +9902,15 @@
       </c>
       <c r="L76" s="22" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="M76" s="22" t="n"/>
-      <c r="N76" s="22" t="n"/>
+      <c r="N76" s="22" t="inlineStr">
+        <is>
+          <t>代码已提交：EcomCraftStudioWorkflowSubmitOwn；审核列表显示待审核上传项，通过后 PublishOwn 复制为“上传/&lt;名称&gt;”发布快照；驳回原因只给上传者；待编译与验收</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="40" t="inlineStr">

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -8856,12 +8856,12 @@
       </c>
       <c r="L61" s="22" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="N61" s="22" t="inlineStr">
         <is>
-          <t>N01 已完成（2026-10-28，默认模型见非开发事项 N01），取消暂缓；初版只做文生图，图生图见 N10</t>
+          <t>代码已提交：StandardWorkflows 生成器、系统生成发布、启动检查、管理员状态弹窗；蓝图文件 Templates/blueprints/text-to-image.json 待用户提供已验证的 Qwen-Image 2.1 文生图工作流；待编译与验收</t>
         </is>
       </c>
     </row>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -1040,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="22" min="1" max="1"/>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" s="23">
       <c r="A70" s="22" t="inlineStr">
         <is>
           <t>F69</t>
@@ -4783,6 +4783,62 @@
           <t>需求见 docs/EcomCraft 界面改版需求.zh-CN.md</t>
         </is>
       </c>
+    </row>
+    <row r="71" s="23">
+      <c r="A71" s="22" t="inlineStr">
+        <is>
+          <t>F70</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>后续：功能增强</t>
+        </is>
+      </c>
+      <c r="C71" s="22" t="inlineStr">
+        <is>
+          <t>预计剩余时间</t>
+        </is>
+      </c>
+      <c r="D71" s="22" t="inlineStr">
+        <is>
+          <t>生成提示词、写分镜、看图描述、优化提示词和出图显示“预计还需约多久”；按最近 20 次实际耗时的中位数估算（只记秒数、不记内容、存内存重启清空）；出图按工作流 + 尺寸 + 执行服务器统计单张耗时，排队中的任务显示“约多久后开始”；超时显示“比平时慢，仍在处理”；没有历史数据时只显示已用时间</t>
+        </is>
+      </c>
+      <c r="E71" s="22" t="inlineStr">
+        <is>
+          <t>Generation/TaskTiming.cs、DurationRules.cs；StudioApi.cs；BatchService.cs；PromptService.cs；Studio/simple.js、studio.js</t>
+        </is>
+      </c>
+      <c r="F71" s="22" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G71" s="22" t="inlineStr">
+        <is>
+          <t>运营友好</t>
+        </is>
+      </c>
+      <c r="H71" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-29 用户确认</t>
+        </is>
+      </c>
+      <c r="I71" s="22" t="inlineStr">
+        <is>
+          <t>T74</t>
+        </is>
+      </c>
+      <c r="J71" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A71)</f>
+        <v/>
+      </c>
+      <c r="K71" s="22">
+        <f>IF(J71=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A71,开发任务!$L$5:$L$200,"暂缓")=J71,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A71,开发任务!$L$5:$L$200,"未开始")=J71,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A71,开发任务!$L$5:$L$200,"已完成")=J71,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A71,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A71,开发任务!$L$5:$L$200,"暂缓")=J71,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M71" s="22" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:M31"/>
@@ -4806,7 +4862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:N78"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="22" min="1" max="1"/>
@@ -8861,7 +8917,7 @@
       </c>
       <c r="N61" s="22" t="inlineStr">
         <is>
-          <t>代码已提交：StandardWorkflows 生成器、系统生成发布、启动检查、管理员状态弹窗；蓝图文件 Templates/blueprints/text-to-image.json 待用户提供已验证的 Qwen-Image 2.1 文生图工作流；待编译与验收</t>
+          <t>代码已提交：StandardWorkflows 生成器、系统生成发布、启动检查、管理员状态弹窗；蓝图 Templates/blueprints/text-to-image.json 已提交（69e495b9，来自用户验证过的 Qwen-Image 2.1 文生图工作流，去掉 ResolutionSelector）；待编译与验收</t>
         </is>
       </c>
     </row>
@@ -9843,7 +9899,7 @@
         </is>
       </c>
     </row>
-    <row r="76">
+    <row r="76" s="23">
       <c r="A76" s="22" t="n">
         <v>72</v>
       </c>
@@ -9912,8 +9968,76 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="40" t="inlineStr">
+    <row r="77" s="23">
+      <c r="A77" s="22" t="n">
+        <v>73</v>
+      </c>
+      <c r="B77" s="22" t="inlineStr">
+        <is>
+          <t>T74</t>
+        </is>
+      </c>
+      <c r="C77" s="22" t="inlineStr">
+        <is>
+          <t>后续：功能增强</t>
+        </is>
+      </c>
+      <c r="D77" s="22" t="inlineStr">
+        <is>
+          <t>F70</t>
+        </is>
+      </c>
+      <c r="E77" s="22" t="inlineStr">
+        <is>
+          <t>预计剩余时间</t>
+        </is>
+      </c>
+      <c r="F77" s="22" t="inlineStr">
+        <is>
+          <t>Generation/TaskTiming.cs、Generation/DurationRules.cs、ExecutionScheduler.cs、StudioApi.cs、BatchService.cs、Prompting/PromptService.cs、MagicPrompt/LLMAPICalls.cs、Studio/simple.js、studio.js、lang/en.js、Tests</t>
+        </is>
+      </c>
+      <c r="G77" s="22" t="inlineStr">
+        <is>
+          <t>T58</t>
+        </is>
+      </c>
+      <c r="H77" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I77" s="22" t="inlineStr">
+        <is>
+          <t>生成提示词、写分镜、看图描述、优化提示词和出图在等待时显示“预计还需约 X”并在两次刷新之间倒数；超出预计显示“比平时慢，仍在处理…”；没有历史数据时只显示已用时间；排队中的出图显示“约 X 后开始”；估算只用最近 20 次耗时的中位数，不保存提示词、图片或其他内容，重启后清空；队列与整套出图状态只给本账号的任务带估算</t>
+        </is>
+      </c>
+      <c r="J77" s="22" t="inlineStr">
+        <is>
+          <t>C# 测试中位数与剩余时间计算；node --test；连续出几张图后看估算是否接近实际，同时排队两张看“约多久后开始”</t>
+        </is>
+      </c>
+      <c r="K77" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+任务：实现 F70 预计剩余时间。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L77" s="22" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="M77" s="22" t="n"/>
+      <c r="N77" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-29 方案已确认：服务端按类别记录耗时中位数，出图按工作流 + 尺寸 + 服务器统计单张耗时，排队任务给出约多久后开始</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" s="23">
+      <c r="A78" s="40" t="inlineStr">
         <is>
           <t>规模：S 约半天以内，M 约 1–2 天，L 3 天以上（含你的验证时间，仅供粗略估计）。原 T03、T26 已分别并入 T13、T34。</t>
         </is>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -1040,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="22" min="1" max="1"/>
@@ -4839,6 +4839,66 @@
         <v/>
       </c>
       <c r="M71" s="22" t="n"/>
+    </row>
+    <row r="72" s="23">
+      <c r="A72" s="22" t="inlineStr">
+        <is>
+          <t>F71</t>
+        </is>
+      </c>
+      <c r="B72" s="22" t="inlineStr">
+        <is>
+          <t>后续：功能增强</t>
+        </is>
+      </c>
+      <c r="C72" s="22" t="inlineStr">
+        <is>
+          <t>看图模型自适应运行设备</t>
+        </is>
+      </c>
+      <c r="D72" s="22" t="inlineStr">
+        <is>
+          <t>客户电脑可能是 NVIDIA、AMD、Intel 显卡或 Mac；部分显卡（如走 Vulkan 的较老 AMD 卡）跑看图模型会卡住且让 Ollama 留下“假已加载”状态。P1：关闭思考模式、超时卸载模型、自动模式下第一次在 GPU 上限时 60 秒失败即改用 CPU，管理员可选“自动 / 只用 GPU / 只用 CPU”；P2：实测自检并保存结果；P3：按硬件推荐设备与模型、与 ComfyUI 共用显卡时让路</t>
+        </is>
+      </c>
+      <c r="E72" s="22" t="inlineStr">
+        <is>
+          <t>MagicPrompt/BackendSchema.cs、LLMAPICalls.cs；Prompting/PromptService.cs；Studio/studio.js</t>
+        </is>
+      </c>
+      <c r="F72" s="22" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G72" s="22" t="inlineStr">
+        <is>
+          <t>运营友好</t>
+        </is>
+      </c>
+      <c r="H72" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-29 用户确认（AMD RX 5600 XT 看图卡死报告）</t>
+        </is>
+      </c>
+      <c r="I72" s="22" t="inlineStr">
+        <is>
+          <t>T75、T76、T77</t>
+        </is>
+      </c>
+      <c r="J72" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A72)</f>
+        <v/>
+      </c>
+      <c r="K72" s="22">
+        <f>IF(J72=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A72,开发任务!$L$5:$L$200,"暂缓")=J72,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A72,开发任务!$L$5:$L$200,"未开始")=J72,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A72,开发任务!$L$5:$L$200,"已完成")=J72,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A72,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A72,开发任务!$L$5:$L$200,"暂缓")=J72,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M72" s="22" t="inlineStr">
+        <is>
+          <t>需求见 docs/EcomCraft 参考图需求.zh-CN.md 8.1 节</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:M31"/>
@@ -4862,7 +4922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N78"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="22" min="1" max="1"/>
@@ -10037,7 +10097,203 @@
       </c>
     </row>
     <row r="78" s="23">
-      <c r="A78" s="40" t="inlineStr">
+      <c r="A78" s="22" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="22" t="inlineStr">
+        <is>
+          <t>T75</t>
+        </is>
+      </c>
+      <c r="C78" s="22" t="inlineStr">
+        <is>
+          <t>后续：功能增强</t>
+        </is>
+      </c>
+      <c r="D78" s="22" t="inlineStr">
+        <is>
+          <t>F71</t>
+        </is>
+      </c>
+      <c r="E78" s="22" t="inlineStr">
+        <is>
+          <t>看图运行设备 P1：自动回退与手动选择</t>
+        </is>
+      </c>
+      <c r="F78" s="22" t="inlineStr">
+        <is>
+          <t>MagicPrompt/BackendSchema.cs、MagicPrompt/VisionDeviceRules.cs、MagicPrompt/WebAPI/LLMAPICalls.cs、Prompting/PromptService.cs、Studio/studio.js、index.html、lang/en.js、Tests</t>
+        </is>
+      </c>
+      <c r="G78" s="22" t="inlineStr">
+        <is>
+          <t>T71</t>
+        </is>
+      </c>
+      <c r="H78" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I78" s="22" t="inlineStr">
+        <is>
+          <t>Ollama 请求带 think:false；看图请求 num_ctx 4096；看图超时后向 Ollama 发送卸载请求，放弃等待时取消底层请求；“自动”模式第一次看图在 GPU 上最多 60 秒，超时即卸载并用 num_gpu 0 在 CPU 上重试并记住；“只用 GPU”不回退，“只用 CPU”始终 num_gpu 0；提示词优化设置可选三种设备并显示已自动改用 CPU；接口不返回 Ollama 地址</t>
+        </is>
+      </c>
+      <c r="J78" s="22" t="inlineStr">
+        <is>
+          <t>C# 测试设备规则；node --test；在 RX 5600 XT 机器上“自动”模式上传参考图：约 60 秒后改用 CPU 出描述，第二张十几秒完成，设置里显示已改用 CPU；NVIDIA 或 Mac 机器上描述仍走 GPU</t>
+        </is>
+      </c>
+      <c r="K78" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+任务：实现 F71 P1（docs/EcomCraft 参考图需求.zh-CN.md 8.1 节）。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L78" s="22" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="M78" s="22" t="n"/>
+      <c r="N78" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-29 用户确认方案</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" s="23">
+      <c r="A79" s="22" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="22" t="inlineStr">
+        <is>
+          <t>T76</t>
+        </is>
+      </c>
+      <c r="C79" s="22" t="inlineStr">
+        <is>
+          <t>后续：功能增强</t>
+        </is>
+      </c>
+      <c r="D79" s="22" t="inlineStr">
+        <is>
+          <t>F71</t>
+        </is>
+      </c>
+      <c r="E79" s="22" t="inlineStr">
+        <is>
+          <t>看图运行设备 P2：实测自检并保存结果</t>
+        </is>
+      </c>
+      <c r="F79" s="22" t="inlineStr">
+        <is>
+          <t>MagicPrompt/LLMAPICalls.cs、Prompting/PromptService.cs、Studio/studio.js、Tests</t>
+        </is>
+      </c>
+      <c r="G79" s="22" t="inlineStr">
+        <is>
+          <t>T75</t>
+        </is>
+      </c>
+      <c r="H79" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I79" s="22" t="inlineStr">
+        <is>
+          <t>首次配置、更换模型或 Ollama 版本、显卡变化时自动用内置测试图在 GPU、CPU 上限时实测并选设备；按实测速度设定超时；结果按“Ollama 版本 + 模型 + 显卡 + 驱动”保存在 Data/EcomCraft（只存设备和秒数）；设置显示“看图：GPU / CPU，单张约 X 秒”并可重新检测；运行中的自动回退也写入，重启不再卡一次</t>
+        </is>
+      </c>
+      <c r="J79" s="22" t="inlineStr">
+        <is>
+          <t>C# 测试保存与读取；更换模型后自动重新检测；重启服务后不再等待 60 秒</t>
+        </is>
+      </c>
+      <c r="K79" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+任务：实现 F71 P2（docs/EcomCraft 参考图需求.zh-CN.md 8.1 节）。先进入计划模式给出方案，我确认后再实现。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L79" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="M79" s="22" t="n"/>
+      <c r="N79" s="22" t="n"/>
+    </row>
+    <row r="80" s="23">
+      <c r="A80" s="22" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="22" t="inlineStr">
+        <is>
+          <t>T77</t>
+        </is>
+      </c>
+      <c r="C80" s="22" t="inlineStr">
+        <is>
+          <t>后续：功能增强</t>
+        </is>
+      </c>
+      <c r="D80" s="22" t="inlineStr">
+        <is>
+          <t>F71</t>
+        </is>
+      </c>
+      <c r="E80" s="22" t="inlineStr">
+        <is>
+          <t>看图运行设备 P3：按硬件推荐与显存共用</t>
+        </is>
+      </c>
+      <c r="F80" s="22" t="inlineStr">
+        <is>
+          <t>Studio/VisionModelInstall.cs、VisionInstallRules.cs、Prompting/PromptService.cs、Studio/studio.js</t>
+        </is>
+      </c>
+      <c r="G80" s="22" t="inlineStr">
+        <is>
+          <t>T76</t>
+        </is>
+      </c>
+      <c r="H80" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I80" s="22" t="inlineStr">
+        <is>
+          <t>Ollama 与本服务同机时读取显卡厂商、显存或内存，给出初始设备和推荐模型（NVIDIA 按显存、AMD 按 ROCm 支持列表、Intel 和无独显用 CPU、Apple Silicon 按内存）并用于一键安装；与 ComfyUI 共用显卡且显存较小时默认看图走 CPU 或描述完立即卸载</t>
+        </is>
+      </c>
+      <c r="J80" s="22" t="inlineStr">
+        <is>
+          <t>Windows NVIDIA / AMD、Mac 各验证一次推荐结果；6 GB 显卡上看图与出图交替进行不爆显存</t>
+        </is>
+      </c>
+      <c r="K80" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+任务：实现 F71 P3（docs/EcomCraft 参考图需求.zh-CN.md 8.1 节）。先进入计划模式给出方案，我确认后再实现。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L80" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="M80" s="22" t="n"/>
+      <c r="N80" s="22" t="n"/>
+    </row>
+    <row r="81" s="23">
+      <c r="A81" s="40" t="inlineStr">
         <is>
           <t>规模：S 约半天以内，M 约 1–2 天，L 3 天以上（含你的验证时间，仅供粗略估计）。原 T03、T26 已分别并入 T13、T34。</t>
         </is>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -10154,13 +10154,17 @@
       </c>
       <c r="L78" s="22" t="inlineStr">
         <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="M78" s="22" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M78" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="N78" s="22" t="inlineStr">
         <is>
-          <t>2026-10-29 用户确认方案</t>
+          <t>2026-10-29 用户确认方案；提交 0e180dd2、537706f8；RX 5600 XT 机器实测：自动模式 60 秒后改用 CPU，只用 CPU 模式单张约 15–19 秒；推荐改为 Qwen3-VL -instruct 版（原版 think:false 无效）</t>
         </is>
       </c>
     </row>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -1040,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="22" min="1" max="1"/>
@@ -4897,6 +4897,66 @@
       <c r="M72" s="22" t="inlineStr">
         <is>
           <t>需求见 docs/EcomCraft 参考图需求.zh-CN.md 8.1 节</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" s="23">
+      <c r="A73" s="22" t="inlineStr">
+        <is>
+          <t>F72</t>
+        </is>
+      </c>
+      <c r="B73" s="22" t="inlineStr">
+        <is>
+          <t>后续：功能增强</t>
+        </is>
+      </c>
+      <c r="C73" s="22" t="inlineStr">
+        <is>
+          <t>启动时清理残留的本机 ComfyUI</t>
+        </is>
+      </c>
+      <c r="D73" s="22" t="inlineStr">
+        <is>
+          <t>平台被强制结束、崩溃或断电时，自启动的 ComfyUI 会继续运行，占内存、显存和端口，下次启动又另开一个（一台服务器曾积累 17 个实例）；平台启动 ComfyUI 时记录进程号和启动时间，下次启动先结束仍在运行且启动时间一致的旧进程</t>
+        </is>
+      </c>
+      <c r="E73" s="22" t="inlineStr">
+        <is>
+          <t>src/Backends/NetworkBackendUtils.cs、src/Core/Program.cs</t>
+        </is>
+      </c>
+      <c r="F73" s="22" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G73" s="22" t="inlineStr">
+        <is>
+          <t>稳定性</t>
+        </is>
+      </c>
+      <c r="H73" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-30 用户确认</t>
+        </is>
+      </c>
+      <c r="I73" s="22" t="inlineStr">
+        <is>
+          <t>T78</t>
+        </is>
+      </c>
+      <c r="J73" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A73)</f>
+        <v/>
+      </c>
+      <c r="K73" s="22">
+        <f>IF(J73=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A73,开发任务!$L$5:$L$200,"暂缓")=J73,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A73,开发任务!$L$5:$L$200,"未开始")=J73,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A73,开发任务!$L$5:$L$200,"已完成")=J73,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A73,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A73,开发任务!$L$5:$L$200,"暂缓")=J73,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M73" s="22" t="inlineStr">
+        <is>
+          <t>需求见 docs/EcomCraft 局域网多服务器平台需求.zh-CN.md“可靠性”一节</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:N82"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="22" min="1" max="1"/>
@@ -10297,7 +10357,75 @@
       <c r="N80" s="22" t="n"/>
     </row>
     <row r="81" s="23">
-      <c r="A81" s="40" t="inlineStr">
+      <c r="A81" s="22" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="22" t="inlineStr">
+        <is>
+          <t>T78</t>
+        </is>
+      </c>
+      <c r="C81" s="22" t="inlineStr">
+        <is>
+          <t>后续：功能增强</t>
+        </is>
+      </c>
+      <c r="D81" s="22" t="inlineStr">
+        <is>
+          <t>F72</t>
+        </is>
+      </c>
+      <c r="E81" s="22" t="inlineStr">
+        <is>
+          <t>启动时清理残留的本机 ComfyUI</t>
+        </is>
+      </c>
+      <c r="F81" s="22" t="inlineStr">
+        <is>
+          <t>src/Backends/NetworkBackendUtils.cs、src/Core/Program.cs</t>
+        </is>
+      </c>
+      <c r="G81" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I81" s="22" t="inlineStr">
+        <is>
+          <t>自启动 ComfyUI 每次启动时把进程号和启动时间追加到数据目录的记录文件；服务启动、加载后端之前读取记录，结束仍在运行且启动时间一致的旧进程（连同子进程；记录里同时存启动它的服务进程，该服务仍在运行时不结束），然后清空记录；进程号被其他程序复用、无权结束或已退出时跳过并只记日志，不影响启动；不按进程名或命令行批量结束进程</t>
+        </is>
+      </c>
+      <c r="J81" s="22" t="inlineStr">
+        <is>
+          <t>强制结束 SwarmUI 后重启：旧 ComfyUI 被结束，端口仍为 7821，只有一组 ComfyUI 进程；正常关闭后重启无报错；记录文件损坏时照常启动；同一数据目录误开第二个服务时，第一个服务的 ComfyUI 不被结束</t>
+        </is>
+      </c>
+      <c r="K81" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+任务：实现 F72 启动时清理残留的本机 ComfyUI（docs/EcomCraft 局域网多服务器平台需求.zh-CN.md“可靠性”一节）。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L81" s="22" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="M81" s="22" t="n"/>
+      <c r="N81" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-30 用户确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" s="23">
+      <c r="A82" s="40" t="inlineStr">
         <is>
           <t>规模：S 约半天以内，M 约 1–2 天，L 3 天以上（含你的验证时间，仅供粗略估计）。原 T03、T26 已分别并入 T13、T34。</t>
         </is>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -4982,7 +4982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N82"/>
+  <dimension ref="A1:N83"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="22" min="1" max="1"/>
@@ -10425,7 +10425,75 @@
       </c>
     </row>
     <row r="82" s="23">
-      <c r="A82" s="40" t="inlineStr">
+      <c r="A82" s="22" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="22" t="inlineStr">
+        <is>
+          <t>T79</t>
+        </is>
+      </c>
+      <c r="C82" s="22" t="inlineStr">
+        <is>
+          <t>后续：功能增强</t>
+        </is>
+      </c>
+      <c r="D82" s="22" t="inlineStr">
+        <is>
+          <t>F59</t>
+        </is>
+      </c>
+      <c r="E82" s="22" t="inlineStr">
+        <is>
+          <t>按参考图摆放商品</t>
+        </is>
+      </c>
+      <c r="F82" s="22" t="inlineStr">
+        <is>
+          <t>Studio/simple.js、index.html、studio.css、lang/en.js、Generation/BatchService.cs</t>
+        </is>
+      </c>
+      <c r="G82" s="22" t="inlineStr">
+        <is>
+          <t>T61</t>
+        </is>
+      </c>
+      <c r="H82" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I82" s="22" t="inlineStr">
+        <is>
+          <t>参考模式下预览上方列出“按参考图 n 摆放”，选中后预览底图换成该参考图，拖动和大小只改这张参考的摆放并显示对照提示；整套出图提交 reference_placements，每张参考的任务按各自摆放出图，未调整的沿用商品摆放；服务端按商品摆放规则校验，长度不符或数值越界返回 invalid_parameters；不自动推算摆放</t>
+        </is>
+      </c>
+      <c r="J82" s="22" t="inlineStr">
+        <is>
+          <t>node --test；两张构图不同的参考图分别摆放后出图，商品位置和大小分别对应；不调整时与原行为一致</t>
+        </is>
+      </c>
+      <c r="K82" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+任务：实现 F59 按参考图摆放商品（docs/EcomCraft 参考图需求.zh-CN.md 第 4 节第 9 条）。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L82" s="22" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="M82" s="22" t="n"/>
+      <c r="N82" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-30 用户确认：只做提示、不自动摆放，每张参考各自摆放</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" s="23">
+      <c r="A83" s="40" t="inlineStr">
         <is>
           <t>规模：S 约半天以内，M 约 1–2 天，L 3 天以上（含你的验证时间，仅供粗略估计）。原 T03、T26 已分别并入 T13、T34。</t>
         </is>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -10414,13 +10414,17 @@
       </c>
       <c r="L81" s="22" t="inlineStr">
         <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="M81" s="22" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M81" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="N81" s="22" t="inlineStr">
         <is>
-          <t>2026-10-30 用户确认</t>
+          <t>2026-10-30 用户确认；提交 d8d82bfc、788bffeb；实测：强制结束 SwarmUI 后重启，日志出现 Ending backend process，只剩一组 ComfyUI；ShutdownServer 正常关闭后重启无误杀。偶发一次端口顺延到 7822（被结束进程的端口释放稍慢），低危</t>
         </is>
       </c>
     </row>
@@ -10482,13 +10486,17 @@
       </c>
       <c r="L82" s="22" t="inlineStr">
         <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="M82" s="22" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M82" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="N82" s="22" t="inlineStr">
         <is>
-          <t>2026-10-30 用户确认：只做提示、不自动摆放，每张参考各自摆放</t>
+          <t>2026-10-30 用户确认：只做提示、不自动摆放，每张参考各自摆放；提交 39497651、a9791b99、788bffeb；实测：摆放 {x:0.7,y:0.6,size:0.35} 实测中心 (0.70,0.60)、占比 0.35，未调整的居中约 0.71；长度不符、size=3 均返回 invalid_parameters</t>
         </is>
       </c>
     </row>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -10286,11 +10286,15 @@
       </c>
       <c r="L79" s="22" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="M79" s="22" t="n"/>
-      <c r="N79" s="22" t="n"/>
+      <c r="N79" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-30 用户确认开始</t>
+        </is>
+      </c>
     </row>
     <row r="80" s="23">
       <c r="A80" s="22" t="n">

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -1040,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="22" min="1" max="1"/>
@@ -4957,6 +4957,66 @@
       <c r="M73" s="22" t="inlineStr">
         <is>
           <t>需求见 docs/EcomCraft 局域网多服务器平台需求.zh-CN.md“可靠性”一节</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="22" t="inlineStr">
+        <is>
+          <t>F73</t>
+        </is>
+      </c>
+      <c r="B74" s="22" t="inlineStr">
+        <is>
+          <t>后续：功能增强</t>
+        </is>
+      </c>
+      <c r="C74" s="22" t="inlineStr">
+        <is>
+          <t>出图前选择出图尺寸</t>
+        </is>
+      </c>
+      <c r="D74" s="22" t="inlineStr">
+        <is>
+          <t>第 2 步选择出图尺寸：默认按平台图位自动（单张按所选图片类型，整套每种图片各用自己的图位尺寸），也可选常用尺寸或自定义宽高；模型按所选比例在约 100 万像素出图，出图后精确缩放到所选尺寸；出图后不再选择尺寸，打包下载保持出图尺寸，平台只决定格式和大小上限</t>
+        </is>
+      </c>
+      <c r="E74" s="22" t="inlineStr">
+        <is>
+          <t>Studio/Generation/OutputSizeRules.cs、PostProcess/OutputResize.cs、StudioApi.cs、Templates/TemplateApi.cs、Generation/BatchService.cs、Export/ExportService.cs、simple.js、index.html、lang/en.js</t>
+        </is>
+      </c>
+      <c r="F74" s="22" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G74" s="22" t="inlineStr">
+        <is>
+          <t>运营友好</t>
+        </is>
+      </c>
+      <c r="H74" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-30 用户确认（按平台自动 + 可改；按比例出图再精确缩放；去掉出图后选尺寸）</t>
+        </is>
+      </c>
+      <c r="I74" s="22" t="inlineStr">
+        <is>
+          <t>T80</t>
+        </is>
+      </c>
+      <c r="J74" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A74)</f>
+        <v/>
+      </c>
+      <c r="K74" s="22">
+        <f>IF(J74=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A74,开发任务!$L$5:$L$200,"暂缓")=J74,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A74,开发任务!$L$5:$L$200,"未开始")=J74,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A74,开发任务!$L$5:$L$200,"已完成")=J74,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A74,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A74,开发任务!$L$5:$L$200,"暂缓")=J74,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M74" s="22" t="inlineStr">
+        <is>
+          <t>需求见 docs/EcomCraft 简易模式改版需求.zh-CN.md“出图尺寸”</t>
         </is>
       </c>
     </row>
@@ -4982,7 +5042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N83"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="22" min="1" max="1"/>
@@ -10505,7 +10565,79 @@
       </c>
     </row>
     <row r="83" s="23">
-      <c r="A83" s="40" t="inlineStr">
+      <c r="A83" s="22" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="22" t="inlineStr">
+        <is>
+          <t>T80</t>
+        </is>
+      </c>
+      <c r="C83" s="22" t="inlineStr">
+        <is>
+          <t>后续：功能增强</t>
+        </is>
+      </c>
+      <c r="D83" s="22" t="inlineStr">
+        <is>
+          <t>F73</t>
+        </is>
+      </c>
+      <c r="E83" s="22" t="inlineStr">
+        <is>
+          <t>出图前选择出图尺寸</t>
+        </is>
+      </c>
+      <c r="F83" s="22" t="inlineStr">
+        <is>
+          <t>Studio/Generation/OutputSizeRules.cs、PostProcess/OutputResize.cs、StudioApi.cs、Templates/TemplateApi.cs、Generation/BatchService.cs、Export/ExportService.cs、simple.js、index.html、lang/en.js</t>
+        </is>
+      </c>
+      <c r="G83" s="22" t="inlineStr">
+        <is>
+          <t>T79</t>
+        </is>
+      </c>
+      <c r="H83" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I83" s="22" t="inlineStr">
+        <is>
+          <t>第 2 步有“出图尺寸”：按平台自动（显示图位尺寸）、常用尺寸和自定义宽高；单张、整套、分镜和参考模式都按所选尺寸出图；结果图正好是所选尺寸；打包下载不再选平台和规格，保持出图尺寸</t>
+        </is>
+      </c>
+      <c r="J83" s="22" t="inlineStr">
+        <is>
+          <t>dotnet test（OutputSizeRulesTests）；node --test；淘宝场景图按 800×800、自定义 750×1000 各出一张，核对文件尺寸和画面没有变形</t>
+        </is>
+      </c>
+      <c r="K83" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md，遵守 EcomCraft 规则：客户端只提交模板 / 工作流 ID、服务端发布的参数白名单和各类 ID，不提交任意 ComfyUI JSON 或文件路径；生成只发往已登记的执行服务器（本机或局域网 ComfyUI），不向任何云端生成服务发送请求；接口遵守最小披露。用户可见文字走中英文翻译表；涉及的文档中英文同步更新。
+任务：实现 F59 按参考图摆放商品（docs/EcomCraft 参考图需求.zh-CN.md 第 4 节第 9 条）。
+完成后：运行相关测试，执行 git diff --check，按 ecomcraft-docs-sync 技能同步文档，并列出改动文件和你做过的验证。</t>
+        </is>
+      </c>
+      <c r="L83" s="22" t="inlineStr">
+        <is>
+          <t>待验收</t>
+        </is>
+      </c>
+      <c r="M83" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="N83" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-30 用户确认方案</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="40" t="inlineStr">
         <is>
           <t>规模：S 约半天以内，M 约 1–2 天，L 3 天以上（含你的验证时间，仅供粗略估计）。原 T03、T26 已分别并入 T13、T34。</t>
         </is>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -690,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="22" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="B3" s="42" t="inlineStr">
         <is>
-          <t>54 项功能，按 7 个阶段排列，其中 MVP（A 平台底座、B 电商出图、C 易用与运维）27 项；简易模式改版 v3（F52–F57）6 项中 5 项代码已完成、F57 暂缓；后续增强中 F25、F12、F47 代码已完成，F04 服务端已完成。“功能状态”根据开发任务自动计算，不用手填</t>
+          <t>63 项功能（2026-10-31 新增 F74–F82），按阶段排列，其中 MVP（A 平台底座、B 电商出图、C 易用与运维）27 项；简易模式改版 v3（F52–F57）6 项中 5 项代码已完成、F57 暂缓；后续增强中 F25、F12、F47 代码已完成，F04 服务端已完成；2026-10-31起新增阶段 0–6（规划落文、路线实测、参考图 v2、开箱即用、套图和详情、专业模式、发布）。“功能状态”根据开发任务自动计算，不用手填</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B4" s="42" t="inlineStr">
         <is>
-          <t>58 个可直接交给 Claude Code 的任务（MVP 30 个），按“顺序”列执行；每个任务都有涉及文件、依赖、验收标准、测试方式和可直接粘贴的提示词</t>
+          <t>88 个可直接交给 Claude Code 的任务（MVP 30 个；2026-10-31 新增 T81–T110），按“顺序”列执行；每个任务都有涉及文件、依赖、验收标准、测试方式和可直接粘贴的提示词</t>
         </is>
       </c>
     </row>
@@ -839,189 +839,213 @@
       </c>
     </row>
     <row r="14" ht="19.4" customHeight="1" s="23">
-      <c r="A14" s="43" t="inlineStr">
-        <is>
-          <t>本表位置</t>
-        </is>
-      </c>
-      <c r="B14" s="42" t="inlineStr">
-        <is>
-          <t>docs/EcomCraft 开发总表.xlsx，随仓库提交到 dev 分支</t>
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>实施计划</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>docs/EcomCraft 实施计划.zh-CN.md（英文版 docs/EcomCraft Implementation Plan.md）：新目标实施计划（2026-10-31）——参考图驱动的单入口、必须有显卡、Windows 和 Mac 优先；阶段 0–6 任务详情和 G1/G2 验收关卡</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19.5" customHeight="1" s="23">
-      <c r="A15" s="25" t="inlineStr">
-        <is>
-          <t>填写约定</t>
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>重构计划</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>docs/EcomCraft 重构计划.zh-CN.md（英文版 docs/EcomCraft Refactoring Plan.md）：基础重构计划（R00–R23），与实施计划按其第 7 节穿插执行</t>
         </is>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" s="23">
       <c r="A16" s="43" t="inlineStr">
         <is>
+          <t>本表位置</t>
+        </is>
+      </c>
+      <c r="B16" s="42" t="inlineStr">
+        <is>
+          <t>docs/EcomCraft 开发总表.xlsx，随仓库提交到 dev 分支</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="19.4" customHeight="1" s="23">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>填写约定</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="19.5" customHeight="1" s="23">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
           <t>黄色单元格</t>
         </is>
       </c>
-      <c r="B16" s="42" t="inlineStr">
+      <c r="B18" s="42" t="inlineStr">
         <is>
           <t>由你填写；“状态”列从下拉菜单选择（未开始 / 进行中 / 已完成 / 暂缓）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="19.4" customHeight="1" s="23">
-      <c r="A17" s="43" t="inlineStr">
-        <is>
-          <t>编号规则</t>
-        </is>
-      </c>
-      <c r="B17" s="42" t="inlineStr">
-        <is>
-          <t>F = 功能，T = 开发任务，N = 非开发事项，S = 痛点解决方案；编号不复用，合并或取消的项在备注中说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="19.5" customHeight="1" s="23">
-      <c r="A18" s="25" t="inlineStr">
-        <is>
-          <t>用 Claude Code 开发的流程</t>
         </is>
       </c>
     </row>
     <row r="19" ht="19.5" customHeight="1" s="23">
       <c r="A19" s="43" t="inlineStr">
         <is>
-          <t>第 1 步</t>
+          <t>编号规则</t>
         </is>
       </c>
       <c r="B19" s="42" t="inlineStr">
         <is>
-          <t>先做 T00：在仓库根目录建 CLAUDE.md，并用 @AGENTS.md 导入现有规则</t>
+          <t>F = 功能，T = 开发任务，N = 非开发事项，S = 痛点解决方案；编号不复用，合并或取消的项在备注中说明</t>
         </is>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" s="23">
-      <c r="A20" s="43" t="inlineStr">
-        <is>
-          <t>第 2 步</t>
-        </is>
-      </c>
-      <c r="B20" s="42" t="inlineStr">
-        <is>
-          <t>按“顺序”列一次只做一个任务；每个任务开一个新会话，避免上下文混在一起</t>
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>用 Claude Code 开发的流程</t>
         </is>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1" s="23">
       <c r="A21" s="43" t="inlineStr">
         <is>
-          <t>第 3 步</t>
+          <t>第 1 步</t>
         </is>
       </c>
       <c r="B21" s="42" t="inlineStr">
         <is>
-          <t>复制该任务的“Claude Code 提示词”粘贴进去；大多数提示词会让 Claude 先进入计划模式出方案，你看过确认后再让它写代码</t>
+          <t>先做 T00：在仓库根目录建 CLAUDE.md，并用 @AGENTS.md 导入现有规则</t>
         </is>
       </c>
     </row>
     <row r="22" ht="19.5" customHeight="1" s="23">
       <c r="A22" s="43" t="inlineStr">
         <is>
-          <t>第 4 步</t>
+          <t>第 2 步</t>
         </is>
       </c>
       <c r="B22" s="42" t="inlineStr">
         <is>
-          <t>Claude 完成后，按“测试方式”列自己验证；涉及 GPU 生成的效果必须实际跑一遍，涉及多机的要在两台电脑上验证</t>
+          <t>按“顺序”列一次只做一个任务；每个任务开一个新会话，避免上下文混在一起</t>
         </is>
       </c>
     </row>
     <row r="23" ht="19.5" customHeight="1" s="23">
       <c r="A23" s="43" t="inlineStr">
         <is>
-          <t>第 5 步</t>
+          <t>第 3 步</t>
         </is>
       </c>
       <c r="B23" s="42" t="inlineStr">
         <is>
-          <t>验证通过后一个任务做一次提交（dev 分支），再把任务状态改为“已完成”</t>
+          <t>复制该任务的“Claude Code 提示词”粘贴进去；大多数提示词会让 Claude 先进入计划模式出方案，你看过确认后再让它写代码</t>
         </is>
       </c>
     </row>
     <row r="24" ht="19.5" customHeight="1" s="23">
       <c r="A24" s="43" t="inlineStr">
         <is>
-          <t>第 6 步</t>
+          <t>第 4 步</t>
         </is>
       </c>
       <c r="B24" s="42" t="inlineStr">
         <is>
-          <t>“依赖”列中的任务未完成前不要开始；N 开头的依赖是非开发事项</t>
+          <t>Claude 完成后，按“测试方式”列自己验证；涉及 GPU 生成的效果必须实际跑一遍，涉及多机的要在两台电脑上验证</t>
         </is>
       </c>
     </row>
     <row r="25" ht="19.4" customHeight="1" s="23">
       <c r="A25" s="43" t="inlineStr">
         <is>
-          <t>第 7 步</t>
+          <t>第 5 步</t>
         </is>
       </c>
       <c r="B25" s="42" t="inlineStr">
         <is>
-          <t>每个任务涉及的文档都要中英文同步更新</t>
+          <t>验证通过后一个任务做一次提交（dev 分支），再把任务状态改为“已完成”</t>
         </is>
       </c>
     </row>
     <row r="26" ht="35" customHeight="1" s="23">
-      <c r="A26" s="25" t="inlineStr">
-        <is>
-          <t>注意事项</t>
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>第 6 步</t>
+        </is>
+      </c>
+      <c r="B26" s="42" t="inlineStr">
+        <is>
+          <t>“依赖”列中的任务未完成前不要开始；N 开头的依赖是非开发事项</t>
         </is>
       </c>
     </row>
     <row r="27" ht="19.5" customHeight="1" s="23">
       <c r="A27" s="43" t="inlineStr">
         <is>
-          <t>重新构建</t>
+          <t>第 7 步</t>
         </is>
       </c>
       <c r="B27" s="42" t="inlineStr">
         <is>
-          <t>修改 src/Extensions/EcomCraft/ 的 C# 代码后，需按 AGENTS.md 重新构建扩展，否则会加载旧程序集</t>
+          <t>每个任务涉及的文档都要中英文同步更新</t>
         </is>
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1" s="23">
-      <c r="A28" s="43" t="inlineStr">
-        <is>
-          <t>用户数据</t>
-        </is>
-      </c>
-      <c r="B28" s="42" t="inlineStr">
-        <is>
-          <t>不要让 Claude 修改 Data/、Models/、Output/ 中的内容</t>
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>注意事项</t>
         </is>
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1" s="23">
       <c r="A29" s="43" t="inlineStr">
         <is>
-          <t>规则变更</t>
+          <t>重新构建</t>
         </is>
       </c>
       <c r="B29" s="42" t="inlineStr">
         <is>
-          <t>T08、T09、T29 会修改需求文档或 AGENTS.md 中的规则，务必自己审阅后再同意</t>
+          <t>修改 src/Extensions/EcomCraft/ 的 C# 代码后，需按 AGENTS.md 重新构建扩展，否则会加载旧程序集</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="43" t="inlineStr">
         <is>
+          <t>用户数据</t>
+        </is>
+      </c>
+      <c r="B30" s="42" t="inlineStr">
+        <is>
+          <t>不要让 Claude 修改 Data/、Models/、Output/ 中的内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="43" t="inlineStr">
+        <is>
+          <t>规则变更</t>
+        </is>
+      </c>
+      <c r="B31" s="42" t="inlineStr">
+        <is>
+          <t>T08、T09、T29 会修改需求文档或 AGENTS.md 中的规则，务必自己审阅后再同意</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
           <t>范围变更</t>
         </is>
       </c>
-      <c r="B30" s="42" t="inlineStr">
+      <c r="B32" s="42" t="inlineStr">
         <is>
           <t>先改架构文档和需求文档（中英文），再改本表，最后改代码</t>
         </is>
@@ -1040,7 +1064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="22" min="1" max="1"/>
@@ -2292,7 +2316,7 @@
       </c>
       <c r="I25" s="42" t="inlineStr">
         <is>
-          <t>T44</t>
+          <t>T44、T94</t>
         </is>
       </c>
       <c r="J25" s="47">
@@ -3308,7 +3332,7 @@
       </c>
       <c r="F44" s="33" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G44" s="42" t="inlineStr">
@@ -3335,7 +3359,11 @@
         <v/>
       </c>
       <c r="L44" s="44" t="n"/>
-      <c r="M44" s="44" t="n"/>
+      <c r="M44" s="44" t="inlineStr">
+        <is>
+          <t>2026-10-31 F23 提前：T95 在阶段 3「开箱即用」（决策 G2、D6）</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="35" customHeight="1" s="23">
       <c r="A45" s="47" t="inlineStr">
@@ -3659,7 +3687,7 @@
       <c r="L50" s="44" t="n"/>
       <c r="M50" s="44" t="inlineStr">
         <is>
-          <t>2026-10-29 按决策 A12 改为按账号数授权</t>
+          <t>2026-10-29 按决策 A12 改为按账号数授权；2026-10-31 修订：开源核心 + 团队版拆分见 T109（A18）</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3742,11 @@
         <v/>
       </c>
       <c r="L51" s="44" t="n"/>
-      <c r="M51" s="44" t="n"/>
+      <c r="M51" s="44" t="inlineStr">
+        <is>
+          <t>2026-10-31 暂缓（决策 A6、A18 修订）：不做云端生成；T29 同步暂缓</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="35" customHeight="1" s="23">
       <c r="A52" s="47" t="inlineStr">
@@ -4127,7 +4159,7 @@
       </c>
       <c r="I59" s="22" t="inlineStr">
         <is>
-          <t>T60</t>
+          <t>T60、T97</t>
         </is>
       </c>
       <c r="J59" s="22">
@@ -4187,7 +4219,7 @@
       </c>
       <c r="I60" s="22" t="inlineStr">
         <is>
-          <t>T61、T62</t>
+          <t>T61、T84</t>
         </is>
       </c>
       <c r="J60" s="22">
@@ -4200,7 +4232,7 @@
       </c>
       <c r="M60" s="22" t="inlineStr">
         <is>
-          <t>需求见 docs/EcomCraft 参考图需求.zh-CN.md；P2（T62）依赖 N10</t>
+          <t>需求见 docs/EcomCraft 参考图需求.zh-CN.md；P2（T62）依赖 N10；2026-10-31：路线 v2（F74 / T83–T88）取代 P2，T62 被 T84 取代</t>
         </is>
       </c>
     </row>
@@ -4303,7 +4335,7 @@
       </c>
       <c r="I62" s="22" t="inlineStr">
         <is>
-          <t>T64</t>
+          <t>T64、T89、T90</t>
         </is>
       </c>
       <c r="J62" s="22">
@@ -4316,7 +4348,7 @@
       </c>
       <c r="M62" s="22" t="inlineStr">
         <is>
-          <t>需求见 docs/EcomCraft 界面改版需求.zh-CN.md</t>
+          <t>需求见 docs/EcomCraft 界面改版需求.zh-CN.md；2026-10-31 修订（A14）：改为单入口，见 T89、T90</t>
         </is>
       </c>
     </row>
@@ -5017,6 +5049,530 @@
       <c r="M74" s="22" t="inlineStr">
         <is>
           <t>需求见 docs/EcomCraft 简易模式改版需求.zh-CN.md“出图尺寸”</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="22" t="inlineStr">
+        <is>
+          <t>F74</t>
+        </is>
+      </c>
+      <c r="B75" s="22" t="inlineStr">
+        <is>
+          <t>阶段 2：参考图 v2</t>
+        </is>
+      </c>
+      <c r="C75" s="22" t="inlineStr">
+        <is>
+          <t>参考图融合路线（参考图 v2）</t>
+        </is>
+      </c>
+      <c r="D75" s="22" t="inlineStr">
+        <is>
+          <t>参考图 + 商品图直接输入编辑模型融合，生成后定位商品、贴回原商品细节并校验走样；参考图分析自动给出主体位置和图位；比例适配与异常参考图处理；取代「看图写提示词 + 局部重绘」旧路线（路线 E，待 G1 实测确定）</t>
+        </is>
+      </c>
+      <c r="E75" s="22" t="inlineStr">
+        <is>
+          <t>新增蓝图 reference-edit.json；StandardWorkflows、BatchService、PostProcess/、PromptRules</t>
+        </is>
+      </c>
+      <c r="F75" s="22" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G75" s="22" t="inlineStr">
+        <is>
+          <t>运营友好</t>
+        </is>
+      </c>
+      <c r="H75" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-31 实施计划（决策 A11 修订、A14、D2）</t>
+        </is>
+      </c>
+      <c r="I75" s="22" t="inlineStr">
+        <is>
+          <t>T83、T84、T85、T87、T88</t>
+        </is>
+      </c>
+      <c r="J75" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A75)</f>
+        <v/>
+      </c>
+      <c r="K75" s="22">
+        <f>IF(J75=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A75,开发任务!$L$5:$L$200,"暂缓")=J75,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A75,开发任务!$L$5:$L$200,"未开始")=J75,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A75,开发任务!$L$5:$L$200,"已完成")=J75,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A75,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A75,开发任务!$L$5:$L$200,"暂缓")=J75,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M75" s="22" t="inlineStr">
+        <is>
+          <t>需求见 docs/EcomCraft 参考图需求.zh-CN.md 第 3 节；T62 被 T84 取代</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="22" t="inlineStr">
+        <is>
+          <t>F75</t>
+        </is>
+      </c>
+      <c r="B76" s="22" t="inlineStr">
+        <is>
+          <t>阶段 2：参考图 v2</t>
+        </is>
+      </c>
+      <c r="C76" s="22" t="inlineStr">
+        <is>
+          <t>商品定位、贴回和走样校验</t>
+        </is>
+      </c>
+      <c r="D76" s="22" t="inlineStr">
+        <is>
+          <t>生成结果中定位商品区域：轮廓对得上时分频贴回原商品，对不上（角度变了）保留模型结果不硬贴；颜色结构差异过大重试一次（换种子），仍超限标记「商品可能走样」</t>
+        </is>
+      </c>
+      <c r="E76" s="22" t="inlineStr">
+        <is>
+          <t>新增 Studio/PostProcess/ProductAlign.cs、ProductAlignRules.cs；ProductComposite.PasteBlended</t>
+        </is>
+      </c>
+      <c r="F76" s="22" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G76" s="22" t="inlineStr">
+        <is>
+          <t>运营友好</t>
+        </is>
+      </c>
+      <c r="H76" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-31 实施计划</t>
+        </is>
+      </c>
+      <c r="I76" s="22" t="inlineStr">
+        <is>
+          <t>T86</t>
+        </is>
+      </c>
+      <c r="J76" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A76)</f>
+        <v/>
+      </c>
+      <c r="K76" s="22">
+        <f>IF(J76=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A76,开发任务!$L$5:$L$200,"暂缓")=J76,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A76,开发任务!$L$5:$L$200,"未开始")=J76,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A76,开发任务!$L$5:$L$200,"已完成")=J76,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A76,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A76,开发任务!$L$5:$L$200,"暂缓")=J76,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M76" s="22" t="inlineStr">
+        <is>
+          <t>阈值放配置，默认值用实测数据定</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="22" t="inlineStr">
+        <is>
+          <t>F76</t>
+        </is>
+      </c>
+      <c r="B77" s="22" t="inlineStr">
+        <is>
+          <t>阶段 3：开箱即用</t>
+        </is>
+      </c>
+      <c r="C77" s="22" t="inlineStr">
+        <is>
+          <t>硬件检测与模型一键配置</t>
+        </is>
+      </c>
+      <c r="D77" s="22" t="inlineStr">
+        <is>
+          <t>显卡和内存分档（推荐/最低/条件/不支持，接口仅管理员）；按配方扫描已有模型（含用户手放的，未识别的不自动设默认）、一键下载并自动配置（国内优先镜像、断点续传、校验、所需节点安装）</t>
+        </is>
+      </c>
+      <c r="E77" s="22" t="inlineStr">
+        <is>
+          <t>新增 Studio/Setup/HardwareProbe.cs、HardwareRules.cs；Templates/model-recipes.json</t>
+        </is>
+      </c>
+      <c r="F77" s="22" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G77" s="22" t="inlineStr">
+        <is>
+          <t>运营友好</t>
+        </is>
+      </c>
+      <c r="H77" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-31 实施计划（用户要求程序自动读取并配置已下载模型）</t>
+        </is>
+      </c>
+      <c r="I77" s="22" t="inlineStr">
+        <is>
+          <t>T91、T92、T93</t>
+        </is>
+      </c>
+      <c r="J77" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A77)</f>
+        <v/>
+      </c>
+      <c r="K77" s="22">
+        <f>IF(J77=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A77,开发任务!$L$5:$L$200,"暂缓")=J77,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A77,开发任务!$L$5:$L$200,"未开始")=J77,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A77,开发任务!$L$5:$L$200,"已完成")=J77,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A77,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A77,开发任务!$L$5:$L$200,"暂缓")=J77,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M77" s="22" t="inlineStr">
+        <is>
+          <t>数值和 ROCm 列表放配置；下载地址只来自服务端配方</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="22" t="inlineStr">
+        <is>
+          <t>F77</t>
+        </is>
+      </c>
+      <c r="B78" s="22" t="inlineStr">
+        <is>
+          <t>阶段 3：开箱即用</t>
+        </is>
+      </c>
+      <c r="C78" s="22" t="inlineStr">
+        <is>
+          <t>Windows 和 Mac 安装包</t>
+        </is>
+      </c>
+      <c r="D78" s="22" t="inlineStr">
+        <is>
+          <t>用户不需要自己装 .NET、Python、Git：Windows 安装包 + 桌面快捷方式，Mac .app/.dmg；升级保留 Data/、Models/、Output/；签名待用户决定</t>
+        </is>
+      </c>
+      <c r="E78" s="22" t="inlineStr">
+        <is>
+          <t>Desktop/、启动脚本、安装打包</t>
+        </is>
+      </c>
+      <c r="F78" s="22" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G78" s="22" t="inlineStr"/>
+      <c r="H78" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-31 实施计划</t>
+        </is>
+      </c>
+      <c r="I78" s="22" t="inlineStr">
+        <is>
+          <t>T96</t>
+        </is>
+      </c>
+      <c r="J78" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A78)</f>
+        <v/>
+      </c>
+      <c r="K78" s="22">
+        <f>IF(J78=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A78,开发任务!$L$5:$L$200,"暂缓")=J78,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A78,开发任务!$L$5:$L$200,"未开始")=J78,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A78,开发任务!$L$5:$L$200,"已完成")=J78,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A78,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A78,开发任务!$L$5:$L$200,"暂缓")=J78,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M78" s="22" t="inlineStr">
+        <is>
+          <t>未签名时文档写明 SmartScreen / Gatekeeper 放行步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="22" t="inlineStr">
+        <is>
+          <t>F78</t>
+        </is>
+      </c>
+      <c r="B79" s="22" t="inlineStr">
+        <is>
+          <t>阶段 4：套图和详情</t>
+        </is>
+      </c>
+      <c r="C79" s="22" t="inlineStr">
+        <is>
+          <t>按图位出整套</t>
+        </is>
+      </c>
+      <c r="D79" s="22" t="inlineStr">
+        <is>
+          <t>多张参考按图位（首图、卖点、场景、细节、白底、详情屏）分配生成整套图，用户可调整；重复图位允许、缺少的图位显示「未覆盖」；每张参考默认出 1 张、可单独再出；批次按图位分组；一套图风格一致（统一色调）选项</t>
+        </is>
+      </c>
+      <c r="E79" s="22" t="inlineStr">
+        <is>
+          <t>SetRules（MaxReferences 8→15，总上限 20 不变）、BatchService、前端批次视图</t>
+        </is>
+      </c>
+      <c r="F79" s="22" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G79" s="22" t="inlineStr">
+        <is>
+          <t>运营友好</t>
+        </is>
+      </c>
+      <c r="H79" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-31 实施计划</t>
+        </is>
+      </c>
+      <c r="I79" s="22" t="inlineStr">
+        <is>
+          <t>T98、T101</t>
+        </is>
+      </c>
+      <c r="J79" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A79)</f>
+        <v/>
+      </c>
+      <c r="K79" s="22">
+        <f>IF(J79=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A79,开发任务!$L$5:$L$200,"暂缓")=J79,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A79,开发任务!$L$5:$L$200,"未开始")=J79,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A79,开发任务!$L$5:$L$200,"已完成")=J79,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A79,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A79,开发任务!$L$5:$L$200,"暂缓")=J79,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M79" s="22" t="inlineStr">
+        <is>
+          <t>只有一张参考时只出单图并提示，不自动编造其他图位</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="22" t="inlineStr">
+        <is>
+          <t>F79</t>
+        </is>
+      </c>
+      <c r="B80" s="22" t="inlineStr">
+        <is>
+          <t>阶段 4：套图和详情</t>
+        </is>
+      </c>
+      <c r="C80" s="22" t="inlineStr">
+        <is>
+          <t>卖点信息和用语检查</t>
+        </is>
+      </c>
+      <c r="D80" s="22" t="inlineStr">
+        <is>
+          <t>出套图时填写商品名、3–5 条卖点、参数、尺寸，按商品保存到商品库不重复填；模型只建议卖点、用户确认，不得编造参数、认证、功效；广告法极限词提示（词表可配置，提示不强制）；海外平台按语言分别填写</t>
+        </is>
+      </c>
+      <c r="E80" s="22" t="inlineStr">
+        <is>
+          <t>商品库 ProductIndex；新增 Prompting/ClaimRules.cs</t>
+        </is>
+      </c>
+      <c r="F80" s="22" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G80" s="22" t="inlineStr"/>
+      <c r="H80" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-31 实施计划</t>
+        </is>
+      </c>
+      <c r="I80" s="22" t="inlineStr">
+        <is>
+          <t>T99</t>
+        </is>
+      </c>
+      <c r="J80" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A80)</f>
+        <v/>
+      </c>
+      <c r="K80" s="22">
+        <f>IF(J80=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A80,开发任务!$L$5:$L$200,"暂缓")=J80,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A80,开发任务!$L$5:$L$200,"未开始")=J80,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A80,开发任务!$L$5:$L$200,"已完成")=J80,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A80,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A80,开发任务!$L$5:$L$200,"暂缓")=J80,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M80" s="22" t="inlineStr">
+        <is>
+          <t>词表须对照官方规定核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="22" t="inlineStr">
+        <is>
+          <t>F80</t>
+        </is>
+      </c>
+      <c r="B81" s="22" t="inlineStr">
+        <is>
+          <t>阶段 4：套图和详情</t>
+        </is>
+      </c>
+      <c r="C81" s="22" t="inlineStr">
+        <is>
+          <t>卖点图和详情页版式</t>
+        </is>
+      </c>
+      <c r="D81" s="22" t="inlineStr">
+        <is>
+          <t>多种版式，文字始终由服务端绘制（思源黑体，不由 AI 生成）；按参考分析和商品位置选版式避开商品；详情页按图位排版，导出分屏切片和整张长图；按组（主图、详情）打包</t>
+        </is>
+      </c>
+      <c r="E81" s="22" t="inlineStr">
+        <is>
+          <t>Export/SellingImageService.cs、SellingImageRules.cs、ExportService</t>
+        </is>
+      </c>
+      <c r="F81" s="22" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G81" s="22" t="inlineStr"/>
+      <c r="H81" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-31 实施计划</t>
+        </is>
+      </c>
+      <c r="I81" s="22" t="inlineStr">
+        <is>
+          <t>T100</t>
+        </is>
+      </c>
+      <c r="J81" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A81)</f>
+        <v/>
+      </c>
+      <c r="K81" s="22">
+        <f>IF(J81=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A81,开发任务!$L$5:$L$200,"暂缓")=J81,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A81,开发任务!$L$5:$L$200,"未开始")=J81,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A81,开发任务!$L$5:$L$200,"已完成")=J81,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A81,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A81,开发任务!$L$5:$L$200,"暂缓")=J81,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M81" s="22" t="inlineStr">
+        <is>
+          <t>海外平台主图禁文字规则走 ComplianceRules</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="22" t="inlineStr">
+        <is>
+          <t>F81</t>
+        </is>
+      </c>
+      <c r="B82" s="22" t="inlineStr">
+        <is>
+          <t>阶段 4：套图和详情</t>
+        </is>
+      </c>
+      <c r="C82" s="22" t="inlineStr">
+        <is>
+          <t>内置参考图库</t>
+        </is>
+      </c>
+      <c r="D82" s="22" t="inlineStr">
+        <is>
+          <t>按品类和图位提供样图，解决手里没有参考图的情况并降低版权风险；图片来源必须有权使用（自己生成并审核、记录来源），竞品图和未授权图片不进库；基础包随版本提供，行业包归团队版</t>
+        </is>
+      </c>
+      <c r="E82" s="22" t="inlineStr">
+        <is>
+          <t>新增参考图库数据与界面</t>
+        </is>
+      </c>
+      <c r="F82" s="22" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G82" s="22" t="inlineStr"/>
+      <c r="H82" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-31 实施计划</t>
+        </is>
+      </c>
+      <c r="I82" s="22" t="inlineStr">
+        <is>
+          <t>T102</t>
+        </is>
+      </c>
+      <c r="J82" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A82)</f>
+        <v/>
+      </c>
+      <c r="K82" s="22">
+        <f>IF(J82=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A82,开发任务!$L$5:$L$200,"暂缓")=J82,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A82,开发任务!$L$5:$L$200,"未开始")=J82,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A82,开发任务!$L$5:$L$200,"已完成")=J82,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A82,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A82,开发任务!$L$5:$L$200,"暂缓")=J82,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M82" s="22" t="inlineStr">
+        <is>
+          <t>库内图片可长期保存，与「用户参考图不落盘」是两回事，文档分开说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="22" t="inlineStr">
+        <is>
+          <t>F82</t>
+        </is>
+      </c>
+      <c r="B83" s="22" t="inlineStr">
+        <is>
+          <t>阶段 5：专业模式</t>
+        </is>
+      </c>
+      <c r="C83" s="22" t="inlineStr">
+        <is>
+          <t>专业模式精修台</t>
+        </is>
+      </c>
+      <c r="D83" s="22" t="inlineStr">
+        <is>
+          <t>专业模式从参数面板改为精修台（模型和采样器收进「高级」）：版本历史、局部修改与商品锁定（默认锁定、贴回原商品）、消除物体、换背景、指令修图、改比例和放大接到平台尺寸、P1 文字层 / 换色 / 光影 / 批量应用</t>
+        </is>
+      </c>
+      <c r="E83" s="22" t="inlineStr">
+        <is>
+          <t>Studio/js 专业模式视图（重构 R19 后为 create-form.js、create-generate.js）</t>
+        </is>
+      </c>
+      <c r="F83" s="22" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G83" s="22" t="inlineStr">
+        <is>
+          <t>设计友好</t>
+        </is>
+      </c>
+      <c r="H83" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-31 实施计划</t>
+        </is>
+      </c>
+      <c r="I83" s="22" t="inlineStr">
+        <is>
+          <t>T103、T104、T105、T106、T107、T108</t>
+        </is>
+      </c>
+      <c r="J83" s="22">
+        <f>COUNTIF(开发任务!$D$5:$D$200,A83)</f>
+        <v/>
+      </c>
+      <c r="K83" s="22">
+        <f>IF(J83=0,"—",IF(COUNTIFS(开发任务!$D$5:$D$200,A83,开发任务!$L$5:$L$200,"暂缓")=J83,"暂缓",IF(COUNTIFS(开发任务!$D$5:$D$200,A83,开发任务!$L$5:$L$200,"未开始")=J83,"未开始",IF(COUNTIFS(开发任务!$D$5:$D$200,A83,开发任务!$L$5:$L$200,"已完成")=J83,"已完成",IF(COUNTIFS(开发任务!$D$5:$D$200,A83,开发任务!$L$5:$L$200,"已完成")+COUNTIFS(开发任务!$D$5:$D$200,A83,开发任务!$L$5:$L$200,"暂缓")=J83,"已完成（暂缓）","进行中")))))</f>
+        <v/>
+      </c>
+      <c r="M83" s="22" t="inlineStr">
+        <is>
+          <t>T108 开发前先分拆成独立任务</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N84"/>
+  <dimension ref="A1:N114"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="22" min="1" max="1"/>
@@ -8661,13 +9217,13 @@
       </c>
       <c r="L55" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>暂缓</t>
         </is>
       </c>
       <c r="M55" s="38" t="n"/>
       <c r="N55" s="44" t="inlineStr">
         <is>
-          <t>会修改 AGENTS.md 规则，务必审阅</t>
+          <t>会修改 AGENTS.md 规则，务必审阅；2026-10-31 暂缓：决策 A6、A18 修订，不做云端生成</t>
         </is>
       </c>
     </row>
@@ -9385,7 +9941,7 @@
       <c r="M65" s="22" t="n"/>
       <c r="N65" s="22" t="inlineStr">
         <is>
-          <t>依赖 N10（图生图方案未定）；工作流需 N02 或 F57 扩展</t>
+          <t>依赖 N10（图生图方案未定）；工作流需 N02 或 F57 扩展；2026-10-31：被 T84（参考图融合路线）取代，不再单独开发</t>
         </is>
       </c>
     </row>
@@ -10414,11 +10970,15 @@
       </c>
       <c r="L80" s="22" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>暂缓</t>
         </is>
       </c>
       <c r="M80" s="22" t="n"/>
-      <c r="N80" s="22" t="n"/>
+      <c r="N80" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-31 暂缓：路线 E 对看图的依赖变小（见实施计划 8.3）</t>
+        </is>
+      </c>
     </row>
     <row r="81" s="23">
       <c r="A81" s="22" t="n">
@@ -10636,8 +11196,1986 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="40" t="inlineStr">
+    <row r="84" s="23">
+      <c r="A84" s="22" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B84" s="22" t="inlineStr">
+        <is>
+          <t>T81</t>
+        </is>
+      </c>
+      <c r="C84" s="22" t="inlineStr">
+        <is>
+          <t>阶段 0：规划落文</t>
+        </is>
+      </c>
+      <c r="D84" s="22" t="inlineStr"/>
+      <c r="E84" s="22" t="inlineStr">
+        <is>
+          <t>规划落文：更新文档、总表、AGENTS.md，清理蓝图残留</t>
+        </is>
+      </c>
+      <c r="F84" s="22" t="inlineStr">
+        <is>
+          <t>docs/EcomCraft Architecture（中英）、参考图需求（中英）、界面改版需求（中英）、局域网需求（中英）、README、docs 索引、AGENTS.md、CLAUDE.md；开发总表.xlsx；Templates/blueprints/text-to-image.json；新增两份计划文档（中英）</t>
+        </is>
+      </c>
+      <c r="G84" s="22" t="inlineStr">
+        <is>
+          <t>0.2（工作区干净）</t>
+        </is>
+      </c>
+      <c r="H84" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I84" s="22" t="inlineStr">
+        <is>
+          <t>新会话只看仓库能答对产品目标、硬件门槛、目标平台和任务顺序；中英文决策编号一致；搜索「一键复刻」「云端生成」无旧规定残留；总表重新打开无错、公式和下拉都在；git diff --check 通过</t>
+        </is>
+      </c>
+      <c r="J84" s="22" t="inlineStr">
+        <is>
+          <t>按验收标准逐项检查；用 openpyxl 重新打开总表确认公式和下拉</t>
+        </is>
+      </c>
+      <c r="K84" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T81 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L84" s="22" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="N84" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-31 完成文档与总表更新（NativeWorkflowConverter 会读取 widgets_values_named，蓝图残留按规则改为中性商品提示词和当前模型名，未删除字段），待用户验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" s="23">
+      <c r="A85" s="22" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B85" s="22" t="inlineStr">
+        <is>
+          <t>T82</t>
+        </is>
+      </c>
+      <c r="C85" s="22" t="inlineStr">
+        <is>
+          <t>阶段 1：路线实测</t>
+        </is>
+      </c>
+      <c r="D85" s="22" t="inlineStr"/>
+      <c r="E85" s="22" t="inlineStr">
+        <is>
+          <t>编写参考图路线实测手册、提示词和记录表</t>
+        </is>
+      </c>
+      <c r="F85" s="22" t="inlineStr">
+        <is>
+          <t>新增 docs/EcomCraft 参考图路线实测.zh-CN.md 和英文版（含记录表模板 CSV 或 xlsx）</t>
+        </is>
+      </c>
+      <c r="G85" s="22" t="inlineStr">
+        <is>
+          <t>T81</t>
+        </is>
+      </c>
+      <c r="H85" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I85" s="22" t="inlineStr">
+        <is>
+          <t>手册含样本要求（约 15 个主攻品类透明底商品 × 2 参考）、R0–R5 方案、提示词起点、指标（构图相似、商品形状颜色、Logo 可辨、融合自然、可直接上架、耗时显存、平台）和记录表；不写平台代码</t>
+        </is>
+      </c>
+      <c r="J85" s="22" t="inlineStr">
+        <is>
+          <t>人工审阅手册；确认没有交付未运行过的节点图</t>
+        </is>
+      </c>
+      <c r="K85" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T82 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L85" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N85" s="22" t="inlineStr">
+        <is>
+          <t>优先使用 ComfyUI 官方模板；AI 跑不了 GPU，不得声称可用</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" s="23">
+      <c r="A86" s="22" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B86" s="22" t="inlineStr">
+        <is>
+          <t>T83</t>
+        </is>
+      </c>
+      <c r="C86" s="22" t="inlineStr">
+        <is>
+          <t>阶段 2：参考图 v2</t>
+        </is>
+      </c>
+      <c r="D86" s="22" t="inlineStr">
+        <is>
+          <t>F74</t>
+        </is>
+      </c>
+      <c r="E86" s="22" t="inlineStr">
+        <is>
+          <t>参考图分析（自动主体位置与图位）</t>
+        </is>
+      </c>
+      <c r="F86" s="22" t="inlineStr">
+        <is>
+          <t>新增 Studio/PostProcess/ReferenceAnalysis.cs、ReferenceRules.cs、Tests/ReferenceRulesTests.cs；PromptService（看图提示按固定行格式扩展）</t>
+        </is>
+      </c>
+      <c r="G86" s="22" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="H86" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I86" s="22" t="inlineStr">
+        <is>
+          <t>3 张不同构图参考图：预览中商品自动落在旧商品位置，误差肉眼可接受；手动拖动仍可覆盖；视觉模型不可用时位置仍走 SwarmRemBg、role 为 unknown 由用户选择</t>
+        </is>
+      </c>
+      <c r="J86" s="22" t="inlineStr">
+        <is>
+          <t>C# 测试：边界框换算、越界、空蒙版、模型输出解析（含胡乱输出）；真机预览验证</t>
+        </is>
+      </c>
+      <c r="K86" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T83 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L86" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N86" s="22" t="inlineStr">
+        <is>
+          <t>取代 T79 手动摆放（保留为修正）；参考图只在内存中，不返回服务器地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" s="23">
+      <c r="A87" s="22" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B87" s="22" t="inlineStr">
+        <is>
+          <t>T84</t>
+        </is>
+      </c>
+      <c r="C87" s="22" t="inlineStr">
+        <is>
+          <t>阶段 2：参考图 v2</t>
+        </is>
+      </c>
+      <c r="D87" s="22" t="inlineStr">
+        <is>
+          <t>F74</t>
+        </is>
+      </c>
+      <c r="E87" s="22" t="inlineStr">
+        <is>
+          <t>融合工作流和模板（取代 T62）</t>
+        </is>
+      </c>
+      <c r="F87" s="22" t="inlineStr">
+        <is>
+          <t>新增 Templates/blueprints/reference-edit.json、Templates/builtin/reference.json；StandardWorkflows.cs（按种类选蓝图，见重构 R13 接入点）；TemplateStore、模板校验、Settings.EcomCraftData</t>
+        </is>
+      </c>
+      <c r="G87" s="22" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="H87" s="22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I87" s="22" t="inlineStr">
+        <is>
+          <t>执行服务器有模型时自动发布；缺模型时 Unavailable() 说清缺什么；reference 槽位不与 brand_kit 指向同一参数；蓝图和模型名不来自客户端</t>
+        </is>
+      </c>
+      <c r="J87" s="22" t="inlineStr">
+        <is>
+          <t>BuiltinTemplateTests、TemplateValidatorTests 增用例；真机出图验证</t>
+        </is>
+      </c>
+      <c r="K87" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T84 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L87" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N87" s="22" t="inlineStr">
+        <is>
+          <t>ecproductimage 收裁好的商品图还是画布，按 G1 结论定；发布仍走 WorkflowReview</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" s="23">
+      <c r="A88" s="22" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B88" s="22" t="inlineStr">
+        <is>
+          <t>T85</t>
+        </is>
+      </c>
+      <c r="C88" s="22" t="inlineStr">
+        <is>
+          <t>阶段 2：参考图 v2</t>
+        </is>
+      </c>
+      <c r="D88" s="22" t="inlineStr">
+        <is>
+          <t>F74</t>
+        </is>
+      </c>
+      <c r="E88" s="22" t="inlineStr">
+        <is>
+          <t>出图流程接入（reference_mode 与 reference_strength）</t>
+        </is>
+      </c>
+      <c r="F88" s="22" t="inlineStr">
+        <is>
+          <t>Generation/BatchService.cs（任务负载填 ecreferenceimage）；提示词模板放 PromptRules；SetRules、TaskTiming、队列</t>
+        </is>
+      </c>
+      <c r="G88" s="22" t="inlineStr">
+        <is>
+          <t>T83、T84</t>
+        </is>
+      </c>
+      <c r="H88" s="22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I88" s="22" t="inlineStr">
+        <is>
+          <t>1 商品 × 3 参考出 3 张，各自贴合对应参考；取消、超时、服务器断开都有白话错误；队列和他人接口读不到参考图；reference_prompts 改为可选</t>
+        </is>
+      </c>
+      <c r="J88" s="22" t="inlineStr">
+        <is>
+          <t>SetRulesTests 增加模式、强度校验；真机全流程验证</t>
+        </is>
+      </c>
+      <c r="K88" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T85 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L88" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N88" s="22" t="inlineStr">
+        <is>
+          <t>必须核查后端上传图片是否留存（ComfyUI 输入目录）；若留存，任务结束后清理并在文档如实写明</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" s="23">
+      <c r="A89" s="22" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B89" s="22" t="inlineStr">
+        <is>
+          <t>T86</t>
+        </is>
+      </c>
+      <c r="C89" s="22" t="inlineStr">
+        <is>
+          <t>阶段 2：参考图 v2</t>
+        </is>
+      </c>
+      <c r="D89" s="22" t="inlineStr">
+        <is>
+          <t>F75</t>
+        </is>
+      </c>
+      <c r="E89" s="22" t="inlineStr">
+        <is>
+          <t>商品定位、贴回和走样校验</t>
+        </is>
+      </c>
+      <c r="F89" s="22" t="inlineStr">
+        <is>
+          <t>新增 Studio/PostProcess/ProductAlign.cs、ProductAlignRules.cs；ProductComposite.PasteBlended；接入 GenerationFinish（重构 R09 接入点），先保真后缩放</t>
+        </is>
+      </c>
+      <c r="G89" s="22" t="inlineStr">
+        <is>
+          <t>T85</t>
+        </is>
+      </c>
+      <c r="H89" s="22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I89" s="22" t="inlineStr">
+        <is>
+          <t>带 Logo 的商品出图后 Logo 清晰可读；模型转动商品时不出现重影；差异超限重试一次、仍超限标 product_warning 并在候选图显示「商品可能走样，请核对」</t>
+        </is>
+      </c>
+      <c r="J89" s="22" t="inlineStr">
+        <is>
+          <t>ProductAlignRulesTests：相同图、平移、缩放、旋转、不同商品；ProductCompositeTests 回归；真机验证</t>
+        </is>
+      </c>
+      <c r="K89" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T86 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L89" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N89" s="22" t="inlineStr">
+        <is>
+          <t>贴回阈值放配置，默认值用实测数据定</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" s="23">
+      <c r="A90" s="22" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B90" s="22" t="inlineStr">
+        <is>
+          <t>T87</t>
+        </is>
+      </c>
+      <c r="C90" s="22" t="inlineStr">
+        <is>
+          <t>阶段 2：参考图 v2</t>
+        </is>
+      </c>
+      <c r="D90" s="22" t="inlineStr">
+        <is>
+          <t>F74</t>
+        </is>
+      </c>
+      <c r="E90" s="22" t="inlineStr">
+        <is>
+          <t>比例适配（参考与图位比例不一致）</t>
+        </is>
+      </c>
+      <c r="F90" s="22" t="inlineStr">
+        <is>
+          <t>Studio/Generation/OutputSizeRules.cs、Tests/OutputSizeRulesTests.cs；必要时复用扩图能力</t>
+        </is>
+      </c>
+      <c r="G90" s="22" t="inlineStr">
+        <is>
+          <t>T85</t>
+        </is>
+      </c>
+      <c r="H90" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I90" s="22" t="inlineStr">
+        <is>
+          <t>1:1 参考、3:4 图位时主体完整、无拉伸；比例接近（差异 ≤5%）直接裁切，差异大时按目标比例扩图</t>
+        </is>
+      </c>
+      <c r="J90" s="22" t="inlineStr">
+        <is>
+          <t>OutputSizeRulesTests 增用例；真机验证</t>
+        </is>
+      </c>
+      <c r="K90" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T87 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L90" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N90" s="22" t="inlineStr">
+        <is>
+          <t>与 F73 衔接：按比例约 100 万像素出图后精确缩放</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" s="23">
+      <c r="A91" s="22" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B91" s="22" t="inlineStr">
+        <is>
+          <t>T88</t>
+        </is>
+      </c>
+      <c r="C91" s="22" t="inlineStr">
+        <is>
+          <t>阶段 2：参考图 v2</t>
+        </is>
+      </c>
+      <c r="D91" s="22" t="inlineStr">
+        <is>
+          <t>F74</t>
+        </is>
+      </c>
+      <c r="E91" s="22" t="inlineStr">
+        <is>
+          <t>异常参考图处理</t>
+        </is>
+      </c>
+      <c r="F91" s="22" t="inlineStr">
+        <is>
+          <t>ReferenceAnalysis 标记（subject_count、has_person、has_text、边界框、宽高比）；simple.js 白话提示；错误码</t>
+        </is>
+      </c>
+      <c r="G91" s="22" t="inlineStr">
+        <is>
+          <t>T83、T85</t>
+        </is>
+      </c>
+      <c r="H91" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I91" s="22" t="inlineStr">
+        <is>
+          <t>多商品（可点选要替换的主体）、含真人（首批提示不支持）、文字占比高（提示文字不保留）、主体过小、商品与参考差别过大（提示可能效果不佳不阻止）、分辨率过低，各有白话提示</t>
+        </is>
+      </c>
+      <c r="J91" s="22" t="inlineStr">
+        <is>
+          <t>Tests/error-codes.test.cjs；手动触发各情形</t>
+        </is>
+      </c>
+      <c r="K91" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T88 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L91" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N91" s="22" t="inlineStr"/>
+    </row>
+    <row r="92" s="23">
+      <c r="A92" s="22" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B92" s="22" t="inlineStr">
+        <is>
+          <t>T89</t>
+        </is>
+      </c>
+      <c r="C92" s="22" t="inlineStr">
+        <is>
+          <t>阶段 2：参考图 v2</t>
+        </is>
+      </c>
+      <c r="D92" s="22" t="inlineStr">
+        <is>
+          <t>F61</t>
+        </is>
+      </c>
+      <c r="E92" s="22" t="inlineStr">
+        <is>
+          <t>出图页改为单入口（F61 修订）</t>
+        </is>
+      </c>
+      <c r="F92" s="22" t="inlineStr">
+        <is>
+          <t>Studio/simple.js（setTask 约 486 行、referenceMode 约 2746 行）、index.html、studio.css、lang/en.js</t>
+        </is>
+      </c>
+      <c r="G92" s="22" t="inlineStr">
+        <is>
+          <t>T85</t>
+        </is>
+      </c>
+      <c r="H92" s="22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I92" s="22" t="inlineStr">
+        <is>
+          <t>新用户打开页面只看到三步（传商品 → 平台尺寸 + 参考图 → 挑图导出）；不出现提示词框、模型或参数；中英文无残留；无视觉模型时不再整页阻塞，只提示「图位需手动选择」；窄屏可用</t>
+        </is>
+      </c>
+      <c r="J92" s="22" t="inlineStr">
+        <is>
+          <t>更新 simple-mode、studio-i18n、mobile 测试；真机走查</t>
+        </is>
+      </c>
+      <c r="K92" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T89 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L92" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N92" s="22" t="inlineStr">
+        <is>
+          <t>删除 simple-task-picker 任务卡片；旧控件代码保留不删，等 G2 决定</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" s="23">
+      <c r="A93" s="22" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B93" s="22" t="inlineStr">
+        <is>
+          <t>T90</t>
+        </is>
+      </c>
+      <c r="C93" s="22" t="inlineStr">
+        <is>
+          <t>阶段 2：参考图 v2</t>
+        </is>
+      </c>
+      <c r="D93" s="22" t="inlineStr">
+        <is>
+          <t>F61</t>
+        </is>
+      </c>
+      <c r="E93" s="22" t="inlineStr">
+        <is>
+          <t>旧入口的衔接功能迁移</t>
+        </is>
+      </c>
+      <c r="F93" s="22" t="inlineStr">
+        <is>
+          <t>simple.js（chosenTask、applyRecipe 回填）、studio.js（精修入口文案）；docs/EcomCraft 工作台界面设计（中英）</t>
+        </is>
+      </c>
+      <c r="G93" s="22" t="inlineStr">
+        <is>
+          <t>T89</t>
+        </is>
+      </c>
+      <c r="H93" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I93" s="22" t="inlineStr">
+        <is>
+          <t>浏览器记住的旧任务值（single、set）读取时回落新流程；旧作品「用相同参数重做」回填专业模式并提示「参考图未保存，请重新上传」；「在专业模式里精修」改为「修改这张」；分镜、风格接口无前端调用也不报错</t>
+        </is>
+      </c>
+      <c r="J93" s="22" t="inlineStr">
+        <is>
+          <t>手动验证各项；node --test</t>
+        </is>
+      </c>
+      <c r="K93" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T90 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L93" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N93" s="22" t="inlineStr">
+        <is>
+          <t>逐项见实施计划 T90 表格</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" s="23">
+      <c r="A94" s="22" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B94" s="22" t="inlineStr">
+        <is>
+          <t>T91</t>
+        </is>
+      </c>
+      <c r="C94" s="22" t="inlineStr">
+        <is>
+          <t>阶段 3：开箱即用</t>
+        </is>
+      </c>
+      <c r="D94" s="22" t="inlineStr">
+        <is>
+          <t>F76</t>
+        </is>
+      </c>
+      <c r="E94" s="22" t="inlineStr">
+        <is>
+          <t>硬件检测和分档</t>
+        </is>
+      </c>
+      <c r="F94" s="22" t="inlineStr">
+        <is>
+          <t>新增 Studio/Setup/HardwareProbe.cs（复用 VisionDeviceCheck 分系统读取）、HardwareRules.cs、Tests/HardwareRulesTests.cs；接口 EcomCraftStudioHardwareStatus（服务器设置权限）</t>
+        </is>
+      </c>
+      <c r="G94" s="22" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="H94" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I94" s="22" t="inlineStr">
+        <is>
+          <t>recommended / minimum / conditional / unsupported 四档判定正确；检测读不到显示「未知」不判不支持；接口只返回型号和档位，不含路径地址；局域网执行服务器只按节点和模型判断</t>
+        </is>
+      </c>
+      <c r="J94" s="22" t="inlineStr">
+        <is>
+          <t>HardwareRulesTests 覆盖全部档位边界；不同机器验证</t>
+        </is>
+      </c>
+      <c r="K94" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T91 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L94" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N94" s="22" t="inlineStr">
+        <is>
+          <t>数值和 ROCm 列表放配置，以 G1 实测为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" s="23">
+      <c r="A95" s="22" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B95" s="22" t="inlineStr">
+        <is>
+          <t>T92</t>
+        </is>
+      </c>
+      <c r="C95" s="22" t="inlineStr">
+        <is>
+          <t>阶段 3：开箱即用</t>
+        </is>
+      </c>
+      <c r="D95" s="22" t="inlineStr">
+        <is>
+          <t>F76</t>
+        </is>
+      </c>
+      <c r="E95" s="22" t="inlineStr">
+        <is>
+          <t>模型配方和扫描已有模型</t>
+        </is>
+      </c>
+      <c r="F95" s="22" t="inlineStr">
+        <is>
+          <t>新增 Templates/model-recipes.json（随版本发布，Data/EcomCraft/ 可覆盖）；扫描复用 SwarmUI 模型处理器；Tests/ModelRecipeRulesTests.cs</t>
+        </is>
+      </c>
+      <c r="G95" s="22" t="inlineStr">
+        <is>
+          <t>G2、T91</t>
+        </is>
+      </c>
+      <c r="H95" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I95" s="22" t="inlineStr">
+        <is>
+          <t>按硬件和平台选配方；按文件名和校验值匹配已安装模型，已有的不再下载；用户手放的不在配方内的列为「未识别」，专业模式可用、不自动设默认</t>
+        </is>
+      </c>
+      <c r="J95" s="22" t="inlineStr">
+        <is>
+          <t>ModelRecipeRulesTests：选配方、部分已安装、校验值不符、配方文件损坏</t>
+        </is>
+      </c>
+      <c r="K95" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T92 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L95" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N95" s="22" t="inlineStr">
+        <is>
+          <t>文件清单来自 G1 结论；大小和校验值以实际文件为准，不得编造</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" s="23">
+      <c r="A96" s="22" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B96" s="22" t="inlineStr">
+        <is>
+          <t>T93</t>
+        </is>
+      </c>
+      <c r="C96" s="22" t="inlineStr">
+        <is>
+          <t>阶段 3：开箱即用</t>
+        </is>
+      </c>
+      <c r="D96" s="22" t="inlineStr">
+        <is>
+          <t>F76</t>
+        </is>
+      </c>
+      <c r="E96" s="22" t="inlineStr">
+        <is>
+          <t>一键下载和自动配置</t>
+        </is>
+      </c>
+      <c r="F96" s="22" t="inlineStr">
+        <is>
+          <t>复用 / 扩展 DoModelDownloadWS（src/WebAPI/ModelsAPI.cs:626）；Settings.EcomCraftData 写入；StandardWorkflows.Ensure；节点自动安装；接口 EcomCraftStudioModelRecipes、EcomCraftStudioModelInstall</t>
+        </is>
+      </c>
+      <c r="G96" s="22" t="inlineStr">
+        <is>
+          <t>T92</t>
+        </is>
+      </c>
+      <c r="H96" s="22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I96" s="22" t="inlineStr">
+        <is>
+          <t>清空模型的电脑上一键完成（检查磁盘 → 逐个下载显示进度 → 校验 → 写配置 → 刷新模型列表 → 生成标准工作流）；中途断网续传成功；校验失败不启用；可取消，失败有白话说明</t>
+        </is>
+      </c>
+      <c r="J96" s="22" t="inlineStr">
+        <is>
+          <t>全新机器实测；断网重连续传；校验失败场景</t>
+        </is>
+      </c>
+      <c r="K96" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T93 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L96" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N96" s="22" t="inlineStr">
+        <is>
+          <t>国内优先 ModelScope 或镜像，失败自动换源；所需 ComfyUI 节点只装配方声明的固定来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" s="23">
+      <c r="A97" s="22" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B97" s="22" t="inlineStr">
+        <is>
+          <t>T94</t>
+        </is>
+      </c>
+      <c r="C97" s="22" t="inlineStr">
+        <is>
+          <t>阶段 3：开箱即用</t>
+        </is>
+      </c>
+      <c r="D97" s="22" t="inlineStr">
+        <is>
+          <t>F40</t>
+        </is>
+      </c>
+      <c r="E97" s="22" t="inlineStr">
+        <is>
+          <t>向导和样例自检（F40 修订）</t>
+        </is>
+      </c>
+      <c r="F97" s="22" t="inlineStr">
+        <is>
+          <t>管理视图首次设置向导改造；样例自检（内置测试商品和参考图）；VisionModelInstall 一并安装</t>
+        </is>
+      </c>
+      <c r="G97" s="22" t="inlineStr">
+        <is>
+          <t>T93</t>
+        </is>
+      </c>
+      <c r="H97" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I97" s="22" t="inlineStr">
+        <is>
+          <t>向导流程：语言 → 硬件检测结果 → 推荐配方（下载大小、预计速度）→ 下载 → 样例自检 → 选常用平台；不支持的硬件说明原因并给「局域网连接其他电脑」出口；自检通过才显示「安装完成」，失败给下一步和诊断包入口；自检不写入用户作品库</t>
+        </is>
+      </c>
+      <c r="J97" s="22" t="inlineStr">
+        <is>
+          <t>清理后的电脑全流程实测</t>
+        </is>
+      </c>
+      <c r="K97" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T94 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L97" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N97" s="22" t="inlineStr">
+        <is>
+          <t>样例图必须是我们有权使用的图</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" s="23">
+      <c r="A98" s="22" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B98" s="22" t="inlineStr">
+        <is>
+          <t>T95</t>
+        </is>
+      </c>
+      <c r="C98" s="22" t="inlineStr">
+        <is>
+          <t>阶段 3：开箱即用</t>
+        </is>
+      </c>
+      <c r="D98" s="22" t="inlineStr">
+        <is>
+          <t>F23</t>
+        </is>
+      </c>
+      <c r="E98" s="22" t="inlineStr">
+        <is>
+          <t>Mac 适配（F23，优先级已提高）</t>
+        </is>
+      </c>
+      <c r="F98" s="22" t="inlineStr">
+        <is>
+          <t>launch-macos.sh、src/Core/Installation.cs；新增 launchtools/install-vision-model-macos.sh；VisionModelInstall.cs:77-78、VisionInstallTests；路径 / 字体 / 进程清理检查</t>
+        </is>
+      </c>
+      <c r="G98" s="22" t="inlineStr">
+        <is>
+          <t>T84、T93</t>
+        </is>
+      </c>
+      <c r="H98" s="22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I98" s="22" t="inlineStr">
+        <is>
+          <t>清理后的 Apple 芯片 Mac 跑通 T94 全流程，全程无终端外手动步骤；连续出 20 张无崩溃、无黑图</t>
+        </is>
+      </c>
+      <c r="J98" s="22" t="inlineStr">
+        <is>
+          <t>用户在 Mac 上实测</t>
+        </is>
+      </c>
+      <c r="K98" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T95 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L98" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N98" s="22" t="inlineStr">
+        <is>
+          <t>原生 arm64 Python；确认量化格式和节点在 MPS 可用，必要时独立 Mac 配方</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" s="23">
+      <c r="A99" s="22" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B99" s="22" t="inlineStr">
+        <is>
+          <t>T96</t>
+        </is>
+      </c>
+      <c r="C99" s="22" t="inlineStr">
+        <is>
+          <t>阶段 3：开箱即用</t>
+        </is>
+      </c>
+      <c r="D99" s="22" t="inlineStr">
+        <is>
+          <t>F77</t>
+        </is>
+      </c>
+      <c r="E99" s="22" t="inlineStr">
+        <is>
+          <t>安装包和签名</t>
+        </is>
+      </c>
+      <c r="F99" s="22" t="inlineStr">
+        <is>
+          <t>Desktop/、启动脚本、src/wwwroot/ecomcraft.ico（按 AGENTS.md 同步检查名称路径）；打包脚本</t>
+        </is>
+      </c>
+      <c r="G99" s="22" t="inlineStr">
+        <is>
+          <t>T94、T95</t>
+        </is>
+      </c>
+      <c r="H99" s="22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I99" s="22" t="inlineStr">
+        <is>
+          <t>用户不需要自己装 .NET、Python、Git；Windows 安装包 + 桌面快捷方式，Mac .app/.dmg；升级保留 Data/、Models/、Output/；卸载询问是否删除模型</t>
+        </is>
+      </c>
+      <c r="J99" s="22" t="inlineStr">
+        <is>
+          <t>全新机器安装实测；升级保留数据实测</t>
+        </is>
+      </c>
+      <c r="K99" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T96 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L99" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N99" s="22" t="inlineStr">
+        <is>
+          <t>签名证书待用户决定；未签名时文档写明放行步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" s="23">
+      <c r="A100" s="22" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B100" s="22" t="inlineStr">
+        <is>
+          <t>T97</t>
+        </is>
+      </c>
+      <c r="C100" s="22" t="inlineStr">
+        <is>
+          <t>阶段 4：套图和详情</t>
+        </is>
+      </c>
+      <c r="D100" s="22" t="inlineStr">
+        <is>
+          <t>F58</t>
+        </is>
+      </c>
+      <c r="E100" s="22" t="inlineStr">
+        <is>
+          <t>平台和图位数据（F58 扩展）</t>
+        </is>
+      </c>
+      <c r="F100" s="22" t="inlineStr">
+        <is>
+          <t>Templates/platforms.json；SetRules、ExportRules、ComplianceRules；docs/EcomCraft 平台预设槽位设计（中英）</t>
+        </is>
+      </c>
+      <c r="G100" s="22" t="inlineStr">
+        <is>
+          <t>N06</t>
+        </is>
+      </c>
+      <c r="H100" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I100" s="22" t="inlineStr">
+        <is>
+          <t>第一二三批平台（含 Temu、速卖通、Shopee、Lazada、微信小店、快手、SHEIN、Walmart、Etsy、1688）和图位 first_main、selling、detail_page（宽度、单屏高度、拼接规则）核对官方规范；查不到的保持 verified: false</t>
+        </is>
+      </c>
+      <c r="J100" s="22" t="inlineStr">
+        <is>
+          <t>ExportTests、ComplianceTests</t>
+        </is>
+      </c>
+      <c r="K100" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T97 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L100" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N100" s="22" t="inlineStr">
+        <is>
+          <t>第三方资料矛盾，数值必须查官方，不得编造</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" s="23">
+      <c r="A101" s="22" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="B101" s="22" t="inlineStr">
+        <is>
+          <t>T98</t>
+        </is>
+      </c>
+      <c r="C101" s="22" t="inlineStr">
+        <is>
+          <t>阶段 4：套图和详情</t>
+        </is>
+      </c>
+      <c r="D101" s="22" t="inlineStr">
+        <is>
+          <t>F78</t>
+        </is>
+      </c>
+      <c r="E101" s="22" t="inlineStr">
+        <is>
+          <t>按图位出整套</t>
+        </is>
+      </c>
+      <c r="F101" s="22" t="inlineStr">
+        <is>
+          <t>SetRules（MaxReferences 8→15，BatchService 总上限 20 保持）、BatchService、simple.js 批次按图位分组</t>
+        </is>
+      </c>
+      <c r="G101" s="22" t="inlineStr">
+        <is>
+          <t>T89、T97</t>
+        </is>
+      </c>
+      <c r="H101" s="22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I101" s="22" t="inlineStr">
+        <is>
+          <t>上传多张参考按 role 分配到平台图位，用户可调整；重复图位允许；缺少的图位显示「未覆盖」；每张参考默认出 1 张，候选图可「再出一张」单独重做；只有一张参考时只出单图并提示</t>
+        </is>
+      </c>
+      <c r="J101" s="22" t="inlineStr">
+        <is>
+          <t>真机出一套图；node --test</t>
+        </is>
+      </c>
+      <c r="K101" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T98 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L101" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N101" s="22" t="inlineStr">
+        <is>
+          <t>套图结构见实施计划 T98（主图组 + 详情页组）</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" s="23">
+      <c r="A102" s="22" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B102" s="22" t="inlineStr">
+        <is>
+          <t>T99</t>
+        </is>
+      </c>
+      <c r="C102" s="22" t="inlineStr">
+        <is>
+          <t>阶段 4：套图和详情</t>
+        </is>
+      </c>
+      <c r="D102" s="22" t="inlineStr">
+        <is>
+          <t>F79</t>
+        </is>
+      </c>
+      <c r="E102" s="22" t="inlineStr">
+        <is>
+          <t>卖点信息和用语检查</t>
+        </is>
+      </c>
+      <c r="F102" s="22" t="inlineStr">
+        <is>
+          <t>商品库 ProductIndex（按商品保存）；新增 Prompting/ClaimRules.cs、Tests/ClaimRulesTests.cs</t>
+        </is>
+      </c>
+      <c r="G102" s="22" t="inlineStr">
+        <is>
+          <t>T97</t>
+        </is>
+      </c>
+      <c r="H102" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I102" s="22" t="inlineStr">
+        <is>
+          <t>出套图时填写商品名、3–5 条卖点、参数、尺寸；模型可建议卖点、用户确认后使用，不得编造参数认证功效；广告法极限词提示但不强制；海外平台按语言分别填写</t>
+        </is>
+      </c>
+      <c r="J102" s="22" t="inlineStr">
+        <is>
+          <t>ClaimRulesTests（词表命中、边界）；手动触发极限词提示</t>
+        </is>
+      </c>
+      <c r="K102" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T99 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L102" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N102" s="22" t="inlineStr">
+        <is>
+          <t>词表可配置，须对照官方规定核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" s="23">
+      <c r="A103" s="22" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B103" s="22" t="inlineStr">
+        <is>
+          <t>T100</t>
+        </is>
+      </c>
+      <c r="C103" s="22" t="inlineStr">
+        <is>
+          <t>阶段 4：套图和详情</t>
+        </is>
+      </c>
+      <c r="D103" s="22" t="inlineStr">
+        <is>
+          <t>F80</t>
+        </is>
+      </c>
+      <c r="E103" s="22" t="inlineStr">
+        <is>
+          <t>卖点图和详情页版式</t>
+        </is>
+      </c>
+      <c r="F103" s="22" t="inlineStr">
+        <is>
+          <t>Export/SellingImageService.cs、SellingImageRules.cs、ExportService（按组打包、文件名按顺序）；Tests/SellingImageRulesTests.cs</t>
+        </is>
+      </c>
+      <c r="G103" s="22" t="inlineStr">
+        <is>
+          <t>T98、T99</t>
+        </is>
+      </c>
+      <c r="H103" s="22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I103" s="22" t="inlineStr">
+        <is>
+          <t>多种版式，文字始终由服务端绘制（不由 AI 生成）；按 T83 分析和商品位置选版式避开商品；详情页按图位排版，导出分屏切片和整张长图，单屏大小按 T97 规格</t>
+        </is>
+      </c>
+      <c r="J103" s="22" t="inlineStr">
+        <is>
+          <t>SellingImageRulesTests：文字溢出、长文案、中英文</t>
+        </is>
+      </c>
+      <c r="K103" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T100 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L103" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N103" s="22" t="inlineStr">
+        <is>
+          <t>海外平台主图禁文字规则走 ComplianceRules 提示</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" s="23">
+      <c r="A104" s="22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B104" s="22" t="inlineStr">
+        <is>
+          <t>T101</t>
+        </is>
+      </c>
+      <c r="C104" s="22" t="inlineStr">
+        <is>
+          <t>阶段 4：套图和详情</t>
+        </is>
+      </c>
+      <c r="D104" s="22" t="inlineStr">
+        <is>
+          <t>F78</t>
+        </is>
+      </c>
+      <c r="E104" s="22" t="inlineStr">
+        <is>
+          <t>一套图的风格一致（统一色调）</t>
+        </is>
+      </c>
+      <c r="F104" s="22" t="inlineStr">
+        <is>
+          <t>本地色调匹配（不重新生成、不改商品区域）</t>
+        </is>
+      </c>
+      <c r="G104" s="22" t="inlineStr">
+        <is>
+          <t>T98</t>
+        </is>
+      </c>
+      <c r="H104" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I104" s="22" t="inlineStr">
+        <is>
+          <t>开启「统一色调」后整套图色调以用户选定的一张为基准；商品区域不变；默认关闭</t>
+        </is>
+      </c>
+      <c r="J104" s="22" t="inlineStr">
+        <is>
+          <t>真机对比开关效果</t>
+        </is>
+      </c>
+      <c r="K104" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T101 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L104" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N104" s="22" t="inlineStr">
+        <is>
+          <t>默认是否开启以实测结果定</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" s="23">
+      <c r="A105" s="22" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B105" s="22" t="inlineStr">
+        <is>
+          <t>T102</t>
+        </is>
+      </c>
+      <c r="C105" s="22" t="inlineStr">
+        <is>
+          <t>阶段 4：套图和详情</t>
+        </is>
+      </c>
+      <c r="D105" s="22" t="inlineStr">
+        <is>
+          <t>F81</t>
+        </is>
+      </c>
+      <c r="E105" s="22" t="inlineStr">
+        <is>
+          <t>内置参考图库</t>
+        </is>
+      </c>
+      <c r="F105" s="22" t="inlineStr">
+        <is>
+          <t>参考图库数据（按品类和图位）与选择界面</t>
+        </is>
+      </c>
+      <c r="G105" s="22" t="inlineStr">
+        <is>
+          <t>T98</t>
+        </is>
+      </c>
+      <c r="H105" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I105" s="22" t="inlineStr">
+        <is>
+          <t>按品类和图位提供样图；图片来源必须有权使用（自己生成并审核）并记录来源；基础包随版本、行业包团队版</t>
+        </is>
+      </c>
+      <c r="J105" s="22" t="inlineStr">
+        <is>
+          <t>人工核对来源记录；真机选择出图</t>
+        </is>
+      </c>
+      <c r="K105" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T102 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L105" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N105" s="22" t="inlineStr">
+        <is>
+          <t>竞品图和未授权图片一律不进库</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" s="23">
+      <c r="A106" s="22" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B106" s="22" t="inlineStr">
+        <is>
+          <t>T103</t>
+        </is>
+      </c>
+      <c r="C106" s="22" t="inlineStr">
+        <is>
+          <t>阶段 5：专业模式</t>
+        </is>
+      </c>
+      <c r="D106" s="22" t="inlineStr">
+        <is>
+          <t>F82</t>
+        </is>
+      </c>
+      <c r="E106" s="22" t="inlineStr">
+        <is>
+          <t>版本历史</t>
+        </is>
+      </c>
+      <c r="F106" s="22" t="inlineStr">
+        <is>
+          <t>专业模式版本数据与界面（只存版本之间的关系和文件引用）；AGENTS.md 先补保存规则</t>
+        </is>
+      </c>
+      <c r="G106" s="22" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="H106" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I106" s="22" t="inlineStr">
+        <is>
+          <t>每次修改产生新版本，不覆盖原图；可对比、回退；记录只给本人、可删除、写入经临时文件替换</t>
+        </is>
+      </c>
+      <c r="J106" s="22" t="inlineStr">
+        <is>
+          <t>手动验证；规则审阅</t>
+        </is>
+      </c>
+      <c r="K106" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T103 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L106" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N106" s="22" t="inlineStr">
+        <is>
+          <t>规则参照项目归档</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" s="23">
+      <c r="A107" s="22" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B107" s="22" t="inlineStr">
+        <is>
+          <t>T104</t>
+        </is>
+      </c>
+      <c r="C107" s="22" t="inlineStr">
+        <is>
+          <t>阶段 5：专业模式</t>
+        </is>
+      </c>
+      <c r="D107" s="22" t="inlineStr">
+        <is>
+          <t>F82</t>
+        </is>
+      </c>
+      <c r="E107" s="22" t="inlineStr">
+        <is>
+          <t>局部修改和商品锁定</t>
+        </is>
+      </c>
+      <c r="F107" s="22" t="inlineStr">
+        <is>
+          <t>复用 mask-canvas 蒙版控件；服务端中文转提示词；抠图蒙版保护商品区域 + 贴回</t>
+        </is>
+      </c>
+      <c r="G107" s="22" t="inlineStr">
+        <is>
+          <t>T103</t>
+        </is>
+      </c>
+      <c r="H107" s="22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I107" s="22" t="inlineStr">
+        <is>
+          <t>一句话写要求（可中文）即可局部修改；默认锁定商品，修改后贴回原商品；用户可手动解锁</t>
+        </is>
+      </c>
+      <c r="J107" s="22" t="inlineStr">
+        <is>
+          <t>真机验证</t>
+        </is>
+      </c>
+      <c r="K107" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T104 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L107" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N107" s="22" t="inlineStr">
+        <is>
+          <t>模型用 G1 选定的编辑模型</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" s="23">
+      <c r="A108" s="22" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B108" s="22" t="inlineStr">
+        <is>
+          <t>T105</t>
+        </is>
+      </c>
+      <c r="C108" s="22" t="inlineStr">
+        <is>
+          <t>阶段 5：专业模式</t>
+        </is>
+      </c>
+      <c r="D108" s="22" t="inlineStr">
+        <is>
+          <t>F82</t>
+        </is>
+      </c>
+      <c r="E108" s="22" t="inlineStr">
+        <is>
+          <t>消除物体、换背景</t>
+        </is>
+      </c>
+      <c r="F108" s="22" t="inlineStr">
+        <is>
+          <t>专业模式工具（涂抹移除；商品不动换场景）</t>
+        </is>
+      </c>
+      <c r="G108" s="22" t="inlineStr">
+        <is>
+          <t>T104</t>
+        </is>
+      </c>
+      <c r="H108" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I108" s="22" t="inlineStr">
+        <is>
+          <t>涂抹后移除杂物、文字、水印；换背景时商品不动，可用文字或参考图</t>
+        </is>
+      </c>
+      <c r="J108" s="22" t="inlineStr">
+        <is>
+          <t>真机验证</t>
+        </is>
+      </c>
+      <c r="K108" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T105 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L108" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N108" s="22" t="inlineStr"/>
+    </row>
+    <row r="109" s="23">
+      <c r="A109" s="22" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B109" s="22" t="inlineStr">
+        <is>
+          <t>T106</t>
+        </is>
+      </c>
+      <c r="C109" s="22" t="inlineStr">
+        <is>
+          <t>阶段 5：专业模式</t>
+        </is>
+      </c>
+      <c r="D109" s="22" t="inlineStr">
+        <is>
+          <t>F82</t>
+        </is>
+      </c>
+      <c r="E109" s="22" t="inlineStr">
+        <is>
+          <t>指令修图</t>
+        </is>
+      </c>
+      <c r="F109" s="22" t="inlineStr">
+        <is>
+          <t>编辑模型整图指令 + 贴回；常用指令按钮</t>
+        </is>
+      </c>
+      <c r="G109" s="22" t="inlineStr">
+        <is>
+          <t>T103</t>
+        </is>
+      </c>
+      <c r="H109" s="22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I109" s="22" t="inlineStr">
+        <is>
+          <t>「光线再暖一点」类整图指令生效，商品贴回；提供常用指令按钮降低输入门槛</t>
+        </is>
+      </c>
+      <c r="J109" s="22" t="inlineStr">
+        <is>
+          <t>真机验证</t>
+        </is>
+      </c>
+      <c r="K109" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T106 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L109" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N109" s="22" t="inlineStr"/>
+    </row>
+    <row r="110" s="23">
+      <c r="A110" s="22" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B110" s="22" t="inlineStr">
+        <is>
+          <t>T107</t>
+        </is>
+      </c>
+      <c r="C110" s="22" t="inlineStr">
+        <is>
+          <t>阶段 5：专业模式</t>
+        </is>
+      </c>
+      <c r="D110" s="22" t="inlineStr">
+        <is>
+          <t>F82</t>
+        </is>
+      </c>
+      <c r="E110" s="22" t="inlineStr">
+        <is>
+          <t>改比例和放大接到平台尺寸</t>
+        </is>
+      </c>
+      <c r="F110" s="22" t="inlineStr">
+        <is>
+          <t>扩图、放大与图位联动</t>
+        </is>
+      </c>
+      <c r="G110" s="22" t="inlineStr">
+        <is>
+          <t>T97</t>
+        </is>
+      </c>
+      <c r="H110" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I110" s="22" t="inlineStr">
+        <is>
+          <t>选图位后自动计算扩图方向和放大倍数</t>
+        </is>
+      </c>
+      <c r="J110" s="22" t="inlineStr">
+        <is>
+          <t>真机验证</t>
+        </is>
+      </c>
+      <c r="K110" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T107 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L110" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N110" s="22" t="inlineStr"/>
+    </row>
+    <row r="111" s="23">
+      <c r="A111" s="22" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B111" s="22" t="inlineStr">
+        <is>
+          <t>T108</t>
+        </is>
+      </c>
+      <c r="C111" s="22" t="inlineStr">
+        <is>
+          <t>阶段 5：专业模式</t>
+        </is>
+      </c>
+      <c r="D111" s="22" t="inlineStr">
+        <is>
+          <t>F82</t>
+        </is>
+      </c>
+      <c r="E111" s="22" t="inlineStr">
+        <is>
+          <t>P1：文字层、换色、光影、批量应用（开发前先分拆）</t>
+        </is>
+      </c>
+      <c r="F111" s="22" t="inlineStr">
+        <is>
+          <t>专业模式工具；PSD 导出沿用 F26</t>
+        </is>
+      </c>
+      <c r="G111" s="22" t="inlineStr">
+        <is>
+          <t>T104</t>
+        </is>
+      </c>
+      <c r="H111" s="22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I111" s="22" t="inlineStr">
+        <is>
+          <t>文字层可编辑可增改；换色换材质提示「须与实物一致」；光影方向 / 阴影 / 重新打光；同一修改批量应用到多个 SKU 或整套图</t>
+        </is>
+      </c>
+      <c r="J111" s="22" t="inlineStr">
+        <is>
+          <t>真机验证</t>
+        </is>
+      </c>
+      <c r="K111" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T108 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L111" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N111" s="22" t="inlineStr">
+        <is>
+          <t>开发前先分拆成独立任务再排期</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" s="23">
+      <c r="A112" s="22" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B112" s="22" t="inlineStr">
+        <is>
+          <t>T109</t>
+        </is>
+      </c>
+      <c r="C112" s="22" t="inlineStr">
+        <is>
+          <t>阶段 6：发布</t>
+        </is>
+      </c>
+      <c r="D112" s="22" t="inlineStr">
+        <is>
+          <t>F16</t>
+        </is>
+      </c>
+      <c r="E112" s="22" t="inlineStr">
+        <is>
+          <t>开源和团队版拆分（F16 修订）</t>
+        </is>
+      </c>
+      <c r="F112" s="22" t="inlineStr">
+        <is>
+          <t>独立闭源扩展程序集 + 接口注册；依赖盘点与接口抽取（ExecutionScheduler、WorkSync、WorkflowReview）</t>
+        </is>
+      </c>
+      <c r="G112" s="22" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="H112" s="22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I112" s="22" t="inlineStr">
+        <is>
+          <t>开源版没有团队功能代码（不是开关隐藏）；离线授权文件只限账号数；两版本功能边界见实施计划 T109 表</t>
+        </is>
+      </c>
+      <c r="J112" s="22" t="inlineStr">
+        <is>
+          <t>架构审阅；两个版本分别实测</t>
+        </is>
+      </c>
+      <c r="K112" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T109 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L112" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N112" s="22" t="inlineStr">
+        <is>
+          <t>许可（MIT 上游、AGPL 建议、GPL ComfyUI、模型不随软件分发）需律师确认后才能发布</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" s="23">
+      <c r="A113" s="22" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B113" s="22" t="inlineStr">
+        <is>
+          <t>T110</t>
+        </is>
+      </c>
+      <c r="C113" s="22" t="inlineStr">
+        <is>
+          <t>阶段 6：发布</t>
+        </is>
+      </c>
+      <c r="D113" s="22" t="inlineStr"/>
+      <c r="E113" s="22" t="inlineStr">
+        <is>
+          <t>配置要求和发布文档</t>
+        </is>
+      </c>
+      <c r="F113" s="22" t="inlineStr">
+        <is>
+          <t>README、README.en、官网；「能否运行」检测工具复用 T91</t>
+        </is>
+      </c>
+      <c r="G113" s="22" t="inlineStr">
+        <is>
+          <t>T96</t>
+        </is>
+      </c>
+      <c r="H113" s="22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I113" s="22" t="inlineStr">
+        <is>
+          <t>写清最低配置并提供检测工具，减少装完才发现用不了；中英文同步</t>
+        </is>
+      </c>
+      <c r="J113" s="22" t="inlineStr">
+        <is>
+          <t>人工审阅</t>
+        </is>
+      </c>
+      <c r="K113" s="22" t="inlineStr">
+        <is>
+          <t>请先阅读 AGENTS.md 和 docs/EcomCraft Architecture.zh-CN.md 第 1、2 节，再读 docs/EcomCraft 实施计划.zh-CN.md （英文版 docs/EcomCraft Implementation Plan.md）中 T110 的章节，严格按其步骤执行；只做任务写明的内容，发现范围外问题只记录不顺手改；完成后按实施计划第 9 节格式汇报，未运行的检查如实写「未运行」。</t>
+        </is>
+      </c>
+      <c r="L113" s="22" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="N113" s="22" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="40" t="inlineStr">
         <is>
           <t>规模：S 约半天以内，M 约 1–2 天，L 3 天以上（含你的验证时间，仅供粗略估计）。原 T03、T26 已分别并入 T13、T34。</t>
         </is>
@@ -10670,7 +13208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="22" min="1" max="1"/>
@@ -10761,7 +13299,7 @@
       <c r="F5" s="44" t="n"/>
       <c r="G5" s="44" t="inlineStr">
         <is>
-          <t>2026-10-28 选定（用户已在执行服务器部署并试用）：UNet qwen-image-2.1-UC-Q4_K_M.gguf（GGUF 量化，需 ComfyUI-GGUF 节点）、文本编码器 qwen3vl_8b_int8_convrot.safetensors、VAE qwen_image_2.1_vae_bf16.safetensors；先用于文生图。该具体版本的商用许可待对照模型发布页核对。</t>
+          <t>2026-10-28 选定（用户已在执行服务器部署并试用）：UNet qwen-image-2.1-UC-Q4_K_M.gguf（GGUF 量化，需 ComfyUI-GGUF 节点）、文本编码器 qwen3vl_8b_int8_convrot.safetensors、VAE qwen_image_2.1_vae_bf16.safetensors；先用于文生图。该具体版本的商用许可待对照模型发布页核对。；2026-10-31：Qwen-Image 2.1 官方许可为仅研究和评估，用户决定先不考虑，发布前处理（见实施计划 8.1）</t>
         </is>
       </c>
     </row>
@@ -11031,7 +13569,7 @@
       </c>
       <c r="D14" s="42" t="inlineStr">
         <is>
-          <t>T59 后续、T07 商品保真效果、T62</t>
+          <t>T82（参考图路线实测）、T84</t>
         </is>
       </c>
       <c r="E14" s="46" t="inlineStr">
@@ -11042,7 +13580,61 @@
       <c r="F14" s="44" t="n"/>
       <c r="G14" s="44" t="inlineStr">
         <is>
-          <t>2026-10-28 用户：图生图暂无好方案，先放待办</t>
+          <t>2026-10-28 用户：图生图暂无好方案，先放待办；2026-10-31：模型选型并入 G1 实测</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="47" t="inlineStr">
+        <is>
+          <t>N11</t>
+        </is>
+      </c>
+      <c r="B15" s="40" t="inlineStr">
+        <is>
+          <t>准备测试机</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="inlineStr">
+        <is>
+          <t>一台 Windows + NVIDIA 8GB 以上、一台 Apple 芯片 Mac（24GB 以上）；记录在案的 RX 5600 XT（6GB）不在 ROCm 支持列表内，不能作基准</t>
+        </is>
+      </c>
+      <c r="D15" s="42" t="inlineStr">
+        <is>
+          <t>T82、N12</t>
+        </is>
+      </c>
+      <c r="E15" s="46" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="47" t="inlineStr">
+        <is>
+          <t>N12</t>
+        </is>
+      </c>
+      <c r="B16" s="40" t="inlineStr">
+        <is>
+          <t>跑参考图路线实测</t>
+        </is>
+      </c>
+      <c r="C16" s="40" t="inlineStr">
+        <is>
+          <t>按 T82 产出的实测手册，用约 15 个主攻品类商品 × 2 张参考跑 R0–R5 方案，填写记录表，供 G1 决策（建议通过线：可直接上架 ≥60%、明显优于 R0、Windows 单张 ≤3 分钟 / Mac ≤10 分钟、无崩溃黑图）</t>
+        </is>
+      </c>
+      <c r="D16" s="42" t="inlineStr">
+        <is>
+          <t>T82、N11、N03</t>
+        </is>
+      </c>
+      <c r="E16" s="46" t="inlineStr">
+        <is>
+          <t>未开始</t>
         </is>
       </c>
     </row>
@@ -12095,7 +14687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="22" min="1" max="1"/>
@@ -12350,54 +14942,278 @@
     <row r="11" ht="17.15" customHeight="1" s="23">
       <c r="A11" s="43" t="inlineStr">
         <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B11" s="51">
-        <f>SUM(B5:B10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="51">
-        <f>SUM(C5:C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="51">
-        <f>SUM(D5:D10)</f>
-        <v/>
-      </c>
-      <c r="E11" s="51">
-        <f>SUM(E5:E10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="52">
+          <t>阶段 0：规划落文</t>
+        </is>
+      </c>
+      <c r="B11" s="47">
+        <f>COUNTIF(功能总表!$B$5:$B$200,A11)</f>
+        <v/>
+      </c>
+      <c r="C11" s="47">
+        <f>COUNTIF(开发任务!$C$5:$C$200,A11)</f>
+        <v/>
+      </c>
+      <c r="D11" s="47">
+        <f>COUNTIFS(开发任务!$C$5:$C$200,A11,开发任务!$L$5:$L$200,"已完成")</f>
+        <v/>
+      </c>
+      <c r="E11" s="47">
+        <f>COUNTIFS(开发任务!$C$5:$C$200,A11,开发任务!$L$5:$L$200,"进行中")</f>
+        <v/>
+      </c>
+      <c r="F11" s="50">
         <f>IF(C11=0,0,D11/C11)</f>
         <v/>
+      </c>
+      <c r="G11" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="17.15" customHeight="1" s="23">
       <c r="A12" s="43" t="inlineStr">
         <is>
+          <t>阶段 1：路线实测</t>
+        </is>
+      </c>
+      <c r="B12" s="47">
+        <f>COUNTIF(功能总表!$B$5:$B$200,A12)</f>
+        <v/>
+      </c>
+      <c r="C12" s="47">
+        <f>COUNTIF(开发任务!$C$5:$C$200,A12)</f>
+        <v/>
+      </c>
+      <c r="D12" s="47">
+        <f>COUNTIFS(开发任务!$C$5:$C$200,A12,开发任务!$L$5:$L$200,"已完成")</f>
+        <v/>
+      </c>
+      <c r="E12" s="47">
+        <f>COUNTIFS(开发任务!$C$5:$C$200,A12,开发任务!$L$5:$L$200,"进行中")</f>
+        <v/>
+      </c>
+      <c r="F12" s="50">
+        <f>IF(C12=0,0,D12/C12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>—（G1 决策关卡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="19.5" customHeight="1" s="23">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>阶段 2：参考图 v2</t>
+        </is>
+      </c>
+      <c r="B13" s="47">
+        <f>COUNTIF(功能总表!$B$5:$B$200,A13)</f>
+        <v/>
+      </c>
+      <c r="C13" s="47">
+        <f>COUNTIF(开发任务!$C$5:$C$200,A13)</f>
+        <v/>
+      </c>
+      <c r="D13" s="47">
+        <f>COUNTIFS(开发任务!$C$5:$C$200,A13,开发任务!$L$5:$L$200,"已完成")</f>
+        <v/>
+      </c>
+      <c r="E13" s="47">
+        <f>COUNTIFS(开发任务!$C$5:$C$200,A13,开发任务!$L$5:$L$200,"进行中")</f>
+        <v/>
+      </c>
+      <c r="F13" s="50">
+        <f>IF(C13=0,0,D13/C13)</f>
+        <v/>
+      </c>
+      <c r="G13" s="40" t="inlineStr">
+        <is>
+          <t>软件销售（参考图驱动的单入口出图）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="19.5" customHeight="1" s="23">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>阶段 3：开箱即用</t>
+        </is>
+      </c>
+      <c r="B14" s="47">
+        <f>COUNTIF(功能总表!$B$5:$B$200,A14)</f>
+        <v/>
+      </c>
+      <c r="C14" s="47">
+        <f>COUNTIF(开发任务!$C$5:$C$200,A14)</f>
+        <v/>
+      </c>
+      <c r="D14" s="47">
+        <f>COUNTIFS(开发任务!$C$5:$C$200,A14,开发任务!$L$5:$L$200,"已完成")</f>
+        <v/>
+      </c>
+      <c r="E14" s="47">
+        <f>COUNTIFS(开发任务!$C$5:$C$200,A14,开发任务!$L$5:$L$200,"进行中")</f>
+        <v/>
+      </c>
+      <c r="F14" s="50">
+        <f>IF(C14=0,0,D14/C14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>软件销售、部署安装服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="19.5" customHeight="1" s="23">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>阶段 4：套图和详情</t>
+        </is>
+      </c>
+      <c r="B15" s="47">
+        <f>COUNTIF(功能总表!$B$5:$B$200,A15)</f>
+        <v/>
+      </c>
+      <c r="C15" s="47">
+        <f>COUNTIF(开发任务!$C$5:$C$200,A15)</f>
+        <v/>
+      </c>
+      <c r="D15" s="47">
+        <f>COUNTIFS(开发任务!$C$5:$C$200,A15,开发任务!$L$5:$L$200,"已完成")</f>
+        <v/>
+      </c>
+      <c r="E15" s="47">
+        <f>COUNTIFS(开发任务!$C$5:$C$200,A15,开发任务!$L$5:$L$200,"进行中")</f>
+        <v/>
+      </c>
+      <c r="F15" s="50">
+        <f>IF(C15=0,0,D15/C15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>软件销售、行业模板包（团队版）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="19.5" customHeight="1" s="23">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>阶段 5：专业模式</t>
+        </is>
+      </c>
+      <c r="B16" s="47">
+        <f>COUNTIF(功能总表!$B$5:$B$200,A16)</f>
+        <v/>
+      </c>
+      <c r="C16" s="47">
+        <f>COUNTIF(开发任务!$C$5:$C$200,A16)</f>
+        <v/>
+      </c>
+      <c r="D16" s="47">
+        <f>COUNTIFS(开发任务!$C$5:$C$200,A16,开发任务!$L$5:$L$200,"已完成")</f>
+        <v/>
+      </c>
+      <c r="E16" s="47">
+        <f>COUNTIFS(开发任务!$C$5:$C$200,A16,开发任务!$L$5:$L$200,"进行中")</f>
+        <v/>
+      </c>
+      <c r="F16" s="50">
+        <f>IF(C16=0,0,D16/C16)</f>
+        <v/>
+      </c>
+      <c r="G16" s="40" t="inlineStr">
+        <is>
+          <t>团队版</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="19.5" customHeight="1" s="23">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>阶段 6：发布</t>
+        </is>
+      </c>
+      <c r="B17" s="47">
+        <f>COUNTIF(功能总表!$B$5:$B$200,A17)</f>
+        <v/>
+      </c>
+      <c r="C17" s="47">
+        <f>COUNTIF(开发任务!$C$5:$C$200,A17)</f>
+        <v/>
+      </c>
+      <c r="D17" s="47">
+        <f>COUNTIFS(开发任务!$C$5:$C$200,A17,开发任务!$L$5:$L$200,"已完成")</f>
+        <v/>
+      </c>
+      <c r="E17" s="47">
+        <f>COUNTIFS(开发任务!$C$5:$C$200,A17,开发任务!$L$5:$L$200,"进行中")</f>
+        <v/>
+      </c>
+      <c r="F17" s="50">
+        <f>IF(C17=0,0,D17/C17)</f>
+        <v/>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
+        <is>
+          <t>团队版、部署安装服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B18" s="51">
+        <f>SUM(B5:B17)</f>
+        <v/>
+      </c>
+      <c r="C18" s="51">
+        <f>SUM(C5:C17)</f>
+        <v/>
+      </c>
+      <c r="D18" s="51">
+        <f>SUM(D5:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="51">
+        <f>SUM(E5:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="52">
+        <f>IF(C18=0,0,D18/C18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
           <t>其中 MVP（A + B + C）</t>
         </is>
       </c>
-      <c r="B12" s="51">
+      <c r="B19" s="51">
         <f>SUM(B5:B7)</f>
         <v/>
       </c>
-      <c r="C12" s="51">
+      <c r="C19" s="51">
         <f>SUM(C5:C7)</f>
         <v/>
       </c>
-      <c r="D12" s="51">
+      <c r="D19" s="51">
         <f>SUM(D5:D7)</f>
         <v/>
       </c>
-      <c r="E12" s="51">
+      <c r="E19" s="51">
         <f>SUM(E5:E7)</f>
         <v/>
       </c>
-      <c r="F12" s="52">
-        <f>IF(C12=0,0,D12/C12)</f>
+      <c r="F19" s="52">
+        <f>IF(C19=0,0,D19/C19)</f>
         <v/>
       </c>
     </row>
@@ -12414,7 +15230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="22" min="1" max="1"/>
@@ -12527,6 +15343,30 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="19.5" customHeight="1" s="23">
+      <c r="A12" s="40" t="inlineStr">
+        <is>
+          <t>无显卡和云端出图</t>
+        </is>
+      </c>
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>必须有显卡才能用（A15 / G1）；不做无显卡方案，不做云端生成（A6 修订），配置不够时明确告知不支持；看图和提示词模型的云端选项不受影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="19.5" customHeight="1" s="23">
+      <c r="A13" s="40" t="inlineStr">
+        <is>
+          <t>Linux 验证</t>
+        </is>
+      </c>
+      <c r="B13" s="40" t="inlineStr">
+        <is>
+          <t>重点支持 Windows 和 Mac（A16 / G2）；Linux 启动脚本保留，但暂不投入开发和验证</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="B3" s="42" t="inlineStr">
         <is>
-          <t>63 项功能（2026-10-31 新增 F74–F82），按阶段排列，其中 MVP（A 平台底座、B 电商出图、C 易用与运维）27 项；简易模式改版 v3（F52–F57）6 项中 5 项代码已完成、F57 暂缓；后续增强中 F25、F12、F47 代码已完成，F04 服务端已完成；2026-10-31起新增阶段 0–6（规划落文、路线实测、参考图 v2、开箱即用、套图和详情、专业模式、发布）。“功能状态”根据开发任务自动计算，不用手填</t>
+          <t>79 项功能（2026-10-31 新增 F74–F82；此前 70 项，旧说明写的 54 项已过期，本次一并更正），按阶段排列，其中 MVP（A 平台底座、B 电商出图、C 易用与运维）27 项；简易模式改版 v3（F52–F57）6 项中 5 项代码已完成、F57 暂缓；后续增强中 F25、F12、F47 代码已完成，F04 服务端已完成；2026-10-31 起新增阶段 0–6（规划落文、路线实测、参考图 v2、开箱即用、套图和详情、专业模式、发布）。“功能状态”根据开发任务自动计算，不用手填</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B4" s="42" t="inlineStr">
         <is>
-          <t>88 个可直接交给 Claude Code 的任务（MVP 30 个；2026-10-31 新增 T81–T110），按“顺序”列执行；每个任务都有涉及文件、依赖、验收标准、测试方式和可直接粘贴的提示词</t>
+          <t>109 个可直接交给 Claude Code 的任务（MVP 30 个；2026-10-31 新增 T81–T110；此前 79 个，旧说明写的 58 个已过期，本次一并更正），按“顺序”列执行；每个任务都有涉及文件、依赖、验收标准、测试方式和可直接粘贴的提示词</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="I44" s="42" t="inlineStr">
         <is>
-          <t>T21</t>
+          <t>T21、T95</t>
         </is>
       </c>
       <c r="J44" s="47">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="I50" s="42" t="inlineStr">
         <is>
-          <t>T27</t>
+          <t>T27、T109</t>
         </is>
       </c>
       <c r="J50" s="47">

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -3361,7 +3361,7 @@
       <c r="L44" s="44" t="n"/>
       <c r="M44" s="44" t="inlineStr">
         <is>
-          <t>2026-10-31 F23 提前：T95 在阶段 3「开箱即用」（决策 G2、D6）</t>
+          <t>2026-10-31 F23 提前：T95 在阶段 3「开箱即用」（决策 P2、D6）</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="B51" s="40" t="inlineStr">
         <is>
-          <t>预留：云端与定制</t>
+          <t>预留：定制服务</t>
         </is>
       </c>
       <c r="C51" s="40" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="D51" s="40" t="inlineStr">
         <is>
-          <t>保留执行方抽象和三段式流程；修订规则并确认后才开发</t>
+          <t>不做（2026-10-31 决策 A6 修订）：不做云端生成，原“保留执行方抽象和三段式流程、修订规则后开发”的规划作废；本行保留作历史记录</t>
         </is>
       </c>
       <c r="E51" s="40" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="B52" s="40" t="inlineStr">
         <is>
-          <t>预留：云端与定制</t>
+          <t>预留：定制服务</t>
         </is>
       </c>
       <c r="C52" s="40" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="C55" s="40" t="inlineStr">
         <is>
-          <t>预留：云端与定制</t>
+          <t>预留：定制服务</t>
         </is>
       </c>
       <c r="D55" s="33" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="C56" s="40" t="inlineStr">
         <is>
-          <t>预留：云端与定制</t>
+          <t>预留：定制服务</t>
         </is>
       </c>
       <c r="D56" s="33" t="inlineStr">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="L65" s="22" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>暂缓</t>
         </is>
       </c>
       <c r="M65" s="22" t="n"/>
@@ -14687,7 +14687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="22" min="1" max="1"/>
@@ -14910,7 +14910,7 @@
     <row r="10" ht="19.5" customHeight="1" s="23">
       <c r="A10" s="43" t="inlineStr">
         <is>
-          <t>预留：云端与定制</t>
+          <t>预留：定制服务</t>
         </is>
       </c>
       <c r="B10" s="47">
@@ -14935,14 +14935,14 @@
       </c>
       <c r="G10" s="40" t="inlineStr">
         <is>
-          <t>云端额度、品牌模型训练</t>
+          <t>品牌模型训练（定制服务）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17.15" customHeight="1" s="23">
       <c r="A11" s="43" t="inlineStr">
         <is>
-          <t>阶段 0：规划落文</t>
+          <t>改版：简易模式 v3</t>
         </is>
       </c>
       <c r="B11" s="47">
@@ -14974,7 +14974,7 @@
     <row r="12" ht="17.15" customHeight="1" s="23">
       <c r="A12" s="43" t="inlineStr">
         <is>
-          <t>阶段 1：路线实测</t>
+          <t>改版：界面 v4</t>
         </is>
       </c>
       <c r="B12" s="47">
@@ -14999,14 +14999,14 @@
       </c>
       <c r="G12" s="40" t="inlineStr">
         <is>
-          <t>—（G1 决策关卡）</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19.5" customHeight="1" s="23">
       <c r="A13" s="43" t="inlineStr">
         <is>
-          <t>阶段 2：参考图 v2</t>
+          <t>阶段 0：规划落文</t>
         </is>
       </c>
       <c r="B13" s="47">
@@ -15031,14 +15031,14 @@
       </c>
       <c r="G13" s="40" t="inlineStr">
         <is>
-          <t>软件销售（参考图驱动的单入口出图）</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="14" ht="19.5" customHeight="1" s="23">
       <c r="A14" s="43" t="inlineStr">
         <is>
-          <t>阶段 3：开箱即用</t>
+          <t>阶段 1：路线实测</t>
         </is>
       </c>
       <c r="B14" s="47">
@@ -15063,14 +15063,14 @@
       </c>
       <c r="G14" s="40" t="inlineStr">
         <is>
-          <t>软件销售、部署安装服务</t>
+          <t>—（G1 决策关卡）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19.5" customHeight="1" s="23">
       <c r="A15" s="43" t="inlineStr">
         <is>
-          <t>阶段 4：套图和详情</t>
+          <t>阶段 2：参考图 v2</t>
         </is>
       </c>
       <c r="B15" s="47">
@@ -15095,14 +15095,14 @@
       </c>
       <c r="G15" s="40" t="inlineStr">
         <is>
-          <t>软件销售、行业模板包（团队版）</t>
+          <t>软件销售（参考图驱动的单入口出图）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1" s="23">
       <c r="A16" s="43" t="inlineStr">
         <is>
-          <t>阶段 5：专业模式</t>
+          <t>阶段 3：开箱即用</t>
         </is>
       </c>
       <c r="B16" s="47">
@@ -15127,14 +15127,14 @@
       </c>
       <c r="G16" s="40" t="inlineStr">
         <is>
-          <t>团队版</t>
+          <t>软件销售、部署安装服务</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19.5" customHeight="1" s="23">
       <c r="A17" s="43" t="inlineStr">
         <is>
-          <t>阶段 6：发布</t>
+          <t>阶段 4：套图和详情</t>
         </is>
       </c>
       <c r="B17" s="47">
@@ -15159,61 +15159,125 @@
       </c>
       <c r="G17" s="40" t="inlineStr">
         <is>
-          <t>团队版、部署安装服务</t>
+          <t>软件销售、行业模板包（团队版）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="43" t="inlineStr">
         <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B18" s="51">
-        <f>SUM(B5:B17)</f>
-        <v/>
-      </c>
-      <c r="C18" s="51">
-        <f>SUM(C5:C17)</f>
-        <v/>
-      </c>
-      <c r="D18" s="51">
-        <f>SUM(D5:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="51">
-        <f>SUM(E5:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="52">
+          <t>阶段 5：专业模式</t>
+        </is>
+      </c>
+      <c r="B18" s="47">
+        <f>COUNTIF(功能总表!$B$5:$B$200,A18)</f>
+        <v/>
+      </c>
+      <c r="C18" s="47">
+        <f>COUNTIF(开发任务!$C$5:$C$200,A18)</f>
+        <v/>
+      </c>
+      <c r="D18" s="47">
+        <f>COUNTIFS(开发任务!$C$5:$C$200,A18,开发任务!$L$5:$L$200,"已完成")</f>
+        <v/>
+      </c>
+      <c r="E18" s="47">
+        <f>COUNTIFS(开发任务!$C$5:$C$200,A18,开发任务!$L$5:$L$200,"进行中")</f>
+        <v/>
+      </c>
+      <c r="F18" s="50">
         <f>IF(C18=0,0,D18/C18)</f>
         <v/>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>团队版</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="43" t="inlineStr">
         <is>
+          <t>阶段 6：发布</t>
+        </is>
+      </c>
+      <c r="B19" s="47">
+        <f>COUNTIF(功能总表!$B$5:$B$200,A19)</f>
+        <v/>
+      </c>
+      <c r="C19" s="47">
+        <f>COUNTIF(开发任务!$C$5:$C$200,A19)</f>
+        <v/>
+      </c>
+      <c r="D19" s="47">
+        <f>COUNTIFS(开发任务!$C$5:$C$200,A19,开发任务!$L$5:$L$200,"已完成")</f>
+        <v/>
+      </c>
+      <c r="E19" s="47">
+        <f>COUNTIFS(开发任务!$C$5:$C$200,A19,开发任务!$L$5:$L$200,"进行中")</f>
+        <v/>
+      </c>
+      <c r="F19" s="50">
+        <f>IF(C19=0,0,D19/C19)</f>
+        <v/>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>团队版、部署安装服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B20" s="51">
+        <f>SUM(B5:B19)</f>
+        <v/>
+      </c>
+      <c r="C20" s="51">
+        <f>SUM(C5:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="51">
+        <f>SUM(D5:D19)</f>
+        <v/>
+      </c>
+      <c r="E20" s="51">
+        <f>SUM(E5:E19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="52">
+        <f>IF(C20=0,0,D20/C20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="43" t="inlineStr">
+        <is>
           <t>其中 MVP（A + B + C）</t>
         </is>
       </c>
-      <c r="B19" s="51">
+      <c r="B21" s="51">
         <f>SUM(B5:B7)</f>
         <v/>
       </c>
-      <c r="C19" s="51">
+      <c r="C21" s="51">
         <f>SUM(C5:C7)</f>
         <v/>
       </c>
-      <c r="D19" s="51">
+      <c r="D21" s="51">
         <f>SUM(D5:D7)</f>
         <v/>
       </c>
-      <c r="E19" s="51">
+      <c r="E21" s="51">
         <f>SUM(E5:E7)</f>
         <v/>
       </c>
-      <c r="F19" s="52">
-        <f>IF(C19=0,0,D19/C19)</f>
+      <c r="F21" s="52">
+        <f>IF(C21=0,0,D21/C21)</f>
         <v/>
       </c>
     </row>
@@ -15279,7 +15343,7 @@
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>按软件销售、按账号数收费（A12）；将来云端额度先用团队预算和每人额度管理</t>
+          <t>按软件销售、按账号数收费（A12、A18）；不做云端出图（A6 修订），不存在云端额度</t>
         </is>
       </c>
     </row>
@@ -15310,12 +15374,12 @@
     <row r="9" ht="35" customHeight="1" s="23">
       <c r="A9" s="40" t="inlineStr">
         <is>
-          <t>MVP 阶段的云端生成</t>
+          <t>云端生成</t>
         </is>
       </c>
       <c r="B9" s="40" t="inlineStr">
         <is>
-          <t>保留执行方抽象和三段式流程；修订 AGENTS.md 规则并确认后再开发（F18）</t>
+          <t>不做云端生成（A6、D11 修订，2026-10-31）：生成只在本机自启动和已登记的局域网 ComfyUI 上执行；原“保留执行方抽象、修订规则后再开发”的规划作废（F18、T29 已暂缓）</t>
         </is>
       </c>
     </row>
@@ -15351,7 +15415,7 @@
       </c>
       <c r="B12" s="40" t="inlineStr">
         <is>
-          <t>必须有显卡才能用（A15 / G1）；不做无显卡方案，不做云端生成（A6 修订），配置不够时明确告知不支持；看图和提示词模型的云端选项不受影响</t>
+          <t>必须有显卡才能用（A15 / P1）；不做无显卡方案，不做云端生成（A6 修订），配置不够时明确告知不支持；看图和提示词模型的云端选项不受影响</t>
         </is>
       </c>
     </row>
@@ -15363,7 +15427,7 @@
       </c>
       <c r="B13" s="40" t="inlineStr">
         <is>
-          <t>重点支持 Windows 和 Mac（A16 / G2）；Linux 启动脚本保留，但暂不投入开发和验证</t>
+          <t>重点支持 Windows 和 Mac（A16 / P2）；Linux 启动脚本保留，但暂不投入开发和验证</t>
         </is>
       </c>
     </row>

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -858,7 +858,7 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>docs/EcomCraft 重构计划.zh-CN.md（英文版 docs/EcomCraft Refactoring Plan.md）：基础重构计划（R00–R23），与实施计划按其第 7 节穿插执行</t>
+          <t>docs/EcomCraft 重构计划.zh-CN.md（英文版 docs/EcomCraft Refactoring Plan.md）：基础重构计划（R00–R24），与实施计划按其第 7 节穿插执行</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>规则 1：分派到排队最少且具备所需节点和模型的执行服务器；执行方抽象预留云端类型（不实现）</t>
+          <t>规则 1：分派到排队最少且具备所需节点和模型的执行服务器；执行方抽象只产生本机和局域网执行方（2026-10-31 起不预留云端类型）</t>
         </is>
       </c>
       <c r="E6" s="40" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="E51" s="40" t="inlineStr">
         <is>
-          <t>需求文档 D11、R10；与 AGENTS.md 现行规则冲突</t>
+          <t>需求文档 D11、R10（2026-10-31 起不做云端生成）</t>
         </is>
       </c>
       <c r="F51" s="33" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="I7" s="42" t="inlineStr">
         <is>
-          <t>按规则 1 选择排队最少且具备所需节点和模型的服务器；排队数计入他人直接提交到 ComfyUI 的任务；可限定服务器并在繁忙时提示；无可用服务器时说明原因；执行方抽象包含云端类型但不实现</t>
+          <t>按规则 1 选择排队最少且具备所需节点和模型的服务器；排队数计入他人直接提交到 ComfyUI 的任务；可限定服务器并在繁忙时提示；无可用服务器时说明原因；执行方只含本机和局域网（2026-10-31 起不预留云端类型）</t>
         </is>
       </c>
       <c r="J7" s="40" t="inlineStr">

--- a/docs/EcomCraft 开发总表.xlsx
+++ b/docs/EcomCraft 开发总表.xlsx
@@ -11313,12 +11313,12 @@
       </c>
       <c r="L85" s="22" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="N85" s="22" t="inlineStr">
         <is>
-          <t>优先使用 ComfyUI 官方模板；AI 跑不了 GPU，不得声称可用</t>
+          <t>优先使用 ComfyUI 官方模板；AI 跑不了 GPU，不得声称可用；2026-10-31 手册和记录表已写好（docs/EcomCraft 参考图路线实测.zh-CN.md），未实际运行，待用户验收</t>
         </is>
       </c>
     </row>
